--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Panhandle Express\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Panhandle Express\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3648A5-2F87-42BF-B73F-36C4135510FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D286FD-A23F-4DB3-A5BF-FBAE32300412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="18765" windowHeight="14745" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -46875,7 +46875,7 @@
         <v>46083.806250000001</v>
       </c>
       <c r="J1635">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1635" t="s">
         <v>11</v>
@@ -47127,7 +47127,7 @@
         <v>16</v>
       </c>
       <c r="G1644" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="H1644" s="2">
         <v>0</v>
@@ -47136,75 +47136,53 @@
         <v>46083.80972222222</v>
       </c>
       <c r="J1644">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1644" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1645" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1645" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1645">
+      <c r="H1645" s="2"/>
+      <c r="I1645" s="1"/>
+      <c r="K1645" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1646" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1646" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1646">
         <v>5131</v>
       </c>
-      <c r="D1645" t="s">
+      <c r="D1646" t="s">
         <v>206</v>
       </c>
-      <c r="F1645" t="s">
+      <c r="F1646" t="s">
         <v>16</v>
       </c>
-      <c r="G1645" t="s">
+      <c r="G1646" t="s">
         <v>34</v>
       </c>
-      <c r="H1645" s="2">
+      <c r="H1646" s="2">
         <v>1.8518518518518518E-4</v>
       </c>
-      <c r="I1645" s="1">
+      <c r="I1646" s="1">
         <v>46083.810416666667</v>
       </c>
-      <c r="J1645">
-        <v>0</v>
-      </c>
-      <c r="K1645" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1646" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1646" s="2"/>
-      <c r="I1646" s="1"/>
+      <c r="J1646">
+        <v>0</v>
+      </c>
       <c r="K1646" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1647" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1647" s="2"/>
+      <c r="I1647" s="1"/>
+      <c r="K1647" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="1647" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1647" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1647">
-        <v>1549</v>
-      </c>
-      <c r="D1647" t="s">
-        <v>52</v>
-      </c>
-      <c r="F1647" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1647" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1647" s="2">
-        <v>4.8842592592592592E-3</v>
-      </c>
-      <c r="I1647" s="1">
-        <v>46083.811111111114</v>
-      </c>
-      <c r="J1647">
-        <v>0</v>
-      </c>
-      <c r="K1647" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1648" spans="2:11" x14ac:dyDescent="0.25">
@@ -47212,35 +47190,57 @@
         <v>21</v>
       </c>
       <c r="C1648">
-        <v>3188</v>
+        <v>1549</v>
       </c>
       <c r="D1648" t="s">
-        <v>145</v>
+        <v>52</v>
       </c>
       <c r="F1648" t="s">
         <v>16</v>
       </c>
       <c r="G1648" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H1648" s="2">
-        <v>0.18012731481481481</v>
+        <v>4.8842592592592592E-3</v>
       </c>
       <c r="I1648" s="1">
         <v>46083.811111111114</v>
       </c>
       <c r="J1648">
+        <v>0</v>
+      </c>
+      <c r="K1648" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1649" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1649" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1649">
+        <v>3188</v>
+      </c>
+      <c r="D1649" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1649" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1649" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1649" s="2">
+        <v>0.18166666666666667</v>
+      </c>
+      <c r="I1649" s="1">
+        <v>46083.811111111114</v>
+      </c>
+      <c r="J1649">
         <v>2</v>
       </c>
-      <c r="K1648" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1649" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1649" s="2"/>
-      <c r="I1649" s="1"/>
       <c r="K1649" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1650" spans="2:11" x14ac:dyDescent="0.25">
@@ -47373,10 +47373,10 @@
         <v>16</v>
       </c>
       <c r="G1654" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1654">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1654" s="2">
+        <v>7.6967592592592591E-3</v>
       </c>
       <c r="I1654" s="1">
         <v>46083.813194444447</v>
@@ -47560,16 +47560,16 @@
         <v>16</v>
       </c>
       <c r="G1662" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1662" s="2">
-        <v>0</v>
+        <v>6.6087962962962966E-3</v>
       </c>
       <c r="I1662" s="1">
         <v>46083.815972222219</v>
       </c>
       <c r="J1662">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1662" t="s">
         <v>11</v>
@@ -47692,7 +47692,7 @@
         <v>46083.794560185182</v>
       </c>
       <c r="J1667">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1667" t="s">
         <v>11</v>
@@ -47712,10 +47712,10 @@
         <v>16</v>
       </c>
       <c r="G1668" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1668" s="2">
-        <v>0</v>
+        <v>5.347222222222222E-3</v>
       </c>
       <c r="I1668" s="1">
         <v>46083.795254629629</v>
@@ -47929,16 +47929,16 @@
         <v>16</v>
       </c>
       <c r="G1677" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1677" s="2">
-        <v>0</v>
+        <v>4.6643518518518518E-3</v>
       </c>
       <c r="I1677" s="1">
         <v>46083.798032407409</v>
       </c>
       <c r="J1677">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1677" t="s">
         <v>11</v>
@@ -48213,7 +48213,7 @@
         <v>46083.802199074074</v>
       </c>
       <c r="J1688">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1688" t="s">
         <v>11</v>
@@ -48349,16 +48349,16 @@
         <v>16</v>
       </c>
       <c r="G1693" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1693" s="2">
-        <v>0</v>
+        <v>4.409722222222222E-3</v>
       </c>
       <c r="I1693" s="1">
         <v>46083.804282407407</v>
       </c>
       <c r="J1693">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1693" t="s">
         <v>11</v>
@@ -48439,7 +48439,7 @@
         <v>34</v>
       </c>
       <c r="H1696" s="2">
-        <v>1.9675925925925926E-4</v>
+        <v>1.0995370370370371E-3</v>
       </c>
       <c r="I1696" s="1">
         <v>46083.805671296293</v>
@@ -48539,7 +48539,7 @@
         <v>46083.807060185187</v>
       </c>
       <c r="J1700">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1700" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Panhandle Express\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D286FD-A23F-4DB3-A5BF-FBAE32300412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765AE2B0-17D5-458B-ABAC-F1807AB49CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Panhandle Express\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765AE2B0-17D5-458B-ABAC-F1807AB49CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124671BC-6F17-4D64-A05D-3DDD83661490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8216" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8536" uniqueCount="224">
   <si>
     <t>Company Name</t>
   </si>
@@ -694,6 +694,24 @@
   <si>
     <t>Mario Rodriguez</t>
   </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>Adrian Hill</t>
+  </si>
+  <si>
+    <t>Brent King</t>
+  </si>
+  <si>
+    <t>Luis Cumpian</t>
+  </si>
+  <si>
+    <t>Mario Mendoza</t>
+  </si>
+  <si>
+    <t>Matthew Licon</t>
+  </si>
 </sst>
 </file>
 
@@ -47043,7 +47061,7 @@
         <v>10</v>
       </c>
       <c r="H1641" s="2">
-        <v>5.4282407407407404E-3</v>
+        <v>6.4583333333333333E-3</v>
       </c>
       <c r="I1641" s="1">
         <v>46083.809027777781</v>
@@ -47101,7 +47119,7 @@
         <v>10</v>
       </c>
       <c r="H1643" s="2">
-        <v>0.12785879629629629</v>
+        <v>0.12960648148148149</v>
       </c>
       <c r="I1643" s="1">
         <v>46083.80972222222</v>
@@ -48662,290 +48680,1880 @@
       </c>
     </row>
     <row r="1705" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1705" s="2"/>
-      <c r="I1705" s="1"/>
+      <c r="B1705" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1705">
+        <v>4858</v>
+      </c>
+      <c r="D1705" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1705" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1705" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1705" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1705" s="1">
+        <v>46122.587268518517</v>
+      </c>
+      <c r="J1705">
+        <v>0</v>
+      </c>
+      <c r="K1705" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1706" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1706" s="2"/>
-      <c r="I1706" s="1"/>
+      <c r="B1706" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1706">
+        <v>5411</v>
+      </c>
+      <c r="D1706" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1706" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1706" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1706" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1706" s="1">
+        <v>46122.587268518517</v>
+      </c>
+      <c r="J1706">
+        <v>0</v>
+      </c>
+      <c r="K1706" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1707" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1707" s="2"/>
-      <c r="I1707" s="1"/>
+      <c r="B1707" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1707">
+        <v>1873</v>
+      </c>
+      <c r="D1707" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1707" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1707" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1707" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1707" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1707" s="1">
+        <v>46122.587962962964</v>
+      </c>
+      <c r="J1707">
+        <v>0</v>
+      </c>
+      <c r="K1707" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1708" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1708" s="2"/>
-      <c r="I1708" s="1"/>
+      <c r="B1708" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1708">
+        <v>3245</v>
+      </c>
+      <c r="D1708" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1708" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1708" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1708" s="2">
+        <v>9.7916666666666673E-3</v>
+      </c>
+      <c r="I1708" s="1">
+        <v>46122.58865740741</v>
+      </c>
+      <c r="J1708">
+        <v>0</v>
+      </c>
+      <c r="K1708" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1709" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1709" s="2"/>
-      <c r="I1709" s="1"/>
+      <c r="B1709" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1709">
+        <v>4977</v>
+      </c>
+      <c r="D1709" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1709" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1709" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1709" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1709" s="1">
+        <v>46122.58865740741</v>
+      </c>
+      <c r="J1709">
+        <v>0</v>
+      </c>
+      <c r="K1709" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1710" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1710" s="2"/>
-      <c r="I1710" s="1"/>
+      <c r="B1710" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1710">
+        <v>5443</v>
+      </c>
+      <c r="D1710" t="s">
+        <v>220</v>
+      </c>
+      <c r="F1710" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1710" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1710" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1710" s="1">
+        <v>46122.58935185185</v>
+      </c>
+      <c r="J1710">
+        <v>0</v>
+      </c>
+      <c r="K1710" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1711" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1711" s="2"/>
-      <c r="I1711" s="1"/>
+      <c r="B1711" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1711">
+        <v>3802</v>
+      </c>
+      <c r="D1711" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1711" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1711" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1711" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1711" s="1">
+        <v>46122.58935185185</v>
+      </c>
+      <c r="J1711">
+        <v>0</v>
+      </c>
+      <c r="K1711" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1712" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1712" s="2"/>
-      <c r="I1712" s="1"/>
-    </row>
-    <row r="1713" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1713" s="2"/>
-      <c r="I1713" s="1"/>
-    </row>
-    <row r="1714" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1714" s="2"/>
-      <c r="I1714" s="1"/>
-    </row>
-    <row r="1715" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1715" s="2"/>
-      <c r="I1715" s="1"/>
-    </row>
-    <row r="1716" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1716" s="2"/>
-      <c r="I1716" s="1"/>
-    </row>
-    <row r="1717" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1717" s="2"/>
-      <c r="I1717" s="1"/>
-    </row>
-    <row r="1718" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1718" s="2"/>
-      <c r="I1718" s="1"/>
-    </row>
-    <row r="1719" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1719" s="2"/>
-      <c r="I1719" s="1"/>
-    </row>
-    <row r="1720" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1720" s="2"/>
-      <c r="I1720" s="1"/>
-    </row>
-    <row r="1721" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1721" s="2"/>
-      <c r="I1721" s="1"/>
-    </row>
-    <row r="1722" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1722" s="2"/>
-      <c r="I1722" s="1"/>
-    </row>
-    <row r="1723" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1723" s="2"/>
-      <c r="I1723" s="1"/>
-    </row>
-    <row r="1724" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1724" s="2"/>
-      <c r="I1724" s="1"/>
-    </row>
-    <row r="1725" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1725" s="2"/>
-      <c r="I1725" s="1"/>
-    </row>
-    <row r="1726" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1726" s="2"/>
-      <c r="I1726" s="1"/>
-    </row>
-    <row r="1727" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1727" s="2"/>
-      <c r="I1727" s="1"/>
-    </row>
-    <row r="1728" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1728" s="2"/>
-      <c r="I1728" s="1"/>
-    </row>
-    <row r="1729" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1729" s="2"/>
-      <c r="I1729" s="1"/>
-    </row>
-    <row r="1730" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B1712" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1712">
+        <v>4769</v>
+      </c>
+      <c r="D1712" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1712" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1712" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1712" s="2">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="I1712" s="1">
+        <v>46122.590046296296</v>
+      </c>
+      <c r="J1712">
+        <v>0</v>
+      </c>
+      <c r="K1712" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1713" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1713" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1713">
+        <v>3800</v>
+      </c>
+      <c r="D1713" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1713" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1713" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1713" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1713" s="1">
+        <v>46122.590046296296</v>
+      </c>
+      <c r="J1713">
+        <v>0</v>
+      </c>
+      <c r="K1713" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1714" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1714" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1714">
+        <v>1608</v>
+      </c>
+      <c r="D1714" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1714" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1714" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1714" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1714" s="1">
+        <v>46122.590740740743</v>
+      </c>
+      <c r="J1714">
+        <v>0</v>
+      </c>
+      <c r="K1714" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1715" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1715" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1715">
+        <v>3185</v>
+      </c>
+      <c r="D1715" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1715" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1715" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1715" s="2">
+        <v>6.3541666666666668E-3</v>
+      </c>
+      <c r="I1715" s="1">
+        <v>46122.590740740743</v>
+      </c>
+      <c r="J1715">
+        <v>0</v>
+      </c>
+      <c r="K1715" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1716" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1716" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1716">
+        <v>1556</v>
+      </c>
+      <c r="D1716" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1716" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1716" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1716" s="2">
+        <v>9.571759259259259E-3</v>
+      </c>
+      <c r="I1716" s="1">
+        <v>46122.591435185182</v>
+      </c>
+      <c r="J1716">
+        <v>0</v>
+      </c>
+      <c r="K1716" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1717" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1717" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1717">
+        <v>5133</v>
+      </c>
+      <c r="D1717" t="s">
+        <v>205</v>
+      </c>
+      <c r="F1717" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1717" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1717" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1717" s="1">
+        <v>46122.591435185182</v>
+      </c>
+      <c r="J1717">
+        <v>0</v>
+      </c>
+      <c r="K1717" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1718" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1718" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1718">
+        <v>1579</v>
+      </c>
+      <c r="D1718" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1718" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1718" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1718" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1718" s="1">
+        <v>46122.592129629629</v>
+      </c>
+      <c r="J1718">
+        <v>0</v>
+      </c>
+      <c r="K1718" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1719" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1719" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1719">
+        <v>1576</v>
+      </c>
+      <c r="D1719" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1719" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1719" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1719" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1719" s="1">
+        <v>46122.592824074076</v>
+      </c>
+      <c r="J1719">
+        <v>0</v>
+      </c>
+      <c r="K1719" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1720" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1720" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1720">
+        <v>1549</v>
+      </c>
+      <c r="D1720" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1720" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1720" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1720" s="2">
+        <v>7.7777777777777776E-3</v>
+      </c>
+      <c r="I1720" s="1">
+        <v>46122.592824074076</v>
+      </c>
+      <c r="J1720">
+        <v>0</v>
+      </c>
+      <c r="K1720" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1721" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1721" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1721">
+        <v>3188</v>
+      </c>
+      <c r="D1721" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1721" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1721" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1721" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1721" s="1">
+        <v>46122.593518518515</v>
+      </c>
+      <c r="J1721">
+        <v>0</v>
+      </c>
+      <c r="K1721" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1722" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1722" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1722">
+        <v>3181</v>
+      </c>
+      <c r="D1722" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1722" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1722" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1722" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1722" s="1">
+        <v>46122.593518518515</v>
+      </c>
+      <c r="J1722">
+        <v>0</v>
+      </c>
+      <c r="K1722" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1723" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1723" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1723">
+        <v>2670</v>
+      </c>
+      <c r="D1723" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1723" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1723" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1723" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1723" s="1">
+        <v>46122.594212962962</v>
+      </c>
+      <c r="J1723">
+        <v>0</v>
+      </c>
+      <c r="K1723" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1724" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1724" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1724">
+        <v>1592</v>
+      </c>
+      <c r="D1724" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1724" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1724" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1724" s="2">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="I1724" s="1">
+        <v>46122.594212962962</v>
+      </c>
+      <c r="J1724">
+        <v>0</v>
+      </c>
+      <c r="K1724" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1725" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1725" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1725">
+        <v>1561</v>
+      </c>
+      <c r="D1725" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1725" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1725" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1725" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1725" s="1">
+        <v>46122.594907407409</v>
+      </c>
+      <c r="J1725">
+        <v>0</v>
+      </c>
+      <c r="K1725" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1726" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1726" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1726">
+        <v>3187</v>
+      </c>
+      <c r="D1726" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1726" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1726" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1726" s="2">
+        <v>9.2245370370370363E-3</v>
+      </c>
+      <c r="I1726" s="1">
+        <v>46122.594907407409</v>
+      </c>
+      <c r="J1726">
+        <v>0</v>
+      </c>
+      <c r="K1726" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1727" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1727" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1727">
+        <v>1597</v>
+      </c>
+      <c r="D1727" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1727" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1727" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1727" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1727" s="1">
+        <v>46122.595601851855</v>
+      </c>
+      <c r="J1727">
+        <v>0</v>
+      </c>
+      <c r="K1727" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1728" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1728" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1728">
+        <v>1569</v>
+      </c>
+      <c r="D1728" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1728" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1728" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1728" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1728" s="1">
+        <v>46122.595601851855</v>
+      </c>
+      <c r="J1728">
+        <v>0</v>
+      </c>
+      <c r="K1728" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1729" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1729" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1729">
+        <v>5181</v>
+      </c>
+      <c r="D1729" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1729" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1729" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1729" s="2">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="I1729" s="1">
+        <v>46122.596296296295</v>
+      </c>
+      <c r="J1729">
+        <v>0</v>
+      </c>
+      <c r="K1729" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1730" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1730" s="2"/>
       <c r="I1730" s="1"/>
-    </row>
-    <row r="1731" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1731" s="2"/>
-      <c r="I1731" s="1"/>
-    </row>
-    <row r="1732" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1732" s="2"/>
-      <c r="I1732" s="1"/>
-    </row>
-    <row r="1733" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1733" s="2"/>
-      <c r="I1733" s="1"/>
-    </row>
-    <row r="1734" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1734" s="2"/>
-      <c r="I1734" s="1"/>
-    </row>
-    <row r="1735" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1735" s="2"/>
-      <c r="I1735" s="1"/>
-    </row>
-    <row r="1736" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1736" s="2"/>
-      <c r="I1736" s="1"/>
-    </row>
-    <row r="1737" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1737" s="2"/>
-      <c r="I1737" s="1"/>
-    </row>
-    <row r="1738" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1738" s="2"/>
-      <c r="I1738" s="1"/>
-    </row>
-    <row r="1739" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1739" s="2"/>
-      <c r="I1739" s="1"/>
-    </row>
-    <row r="1740" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1740" s="2"/>
-      <c r="I1740" s="1"/>
-    </row>
-    <row r="1741" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1741" s="2"/>
-      <c r="I1741" s="1"/>
-    </row>
-    <row r="1742" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1742" s="2"/>
-      <c r="I1742" s="1"/>
-    </row>
-    <row r="1743" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1743" s="2"/>
-      <c r="I1743" s="1"/>
-    </row>
-    <row r="1744" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1730" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1731" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1731" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1731">
+        <v>1538</v>
+      </c>
+      <c r="D1731" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1731" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1731" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1731" s="2">
+        <v>8.3449074074074068E-3</v>
+      </c>
+      <c r="I1731" s="1">
+        <v>46122.596990740742</v>
+      </c>
+      <c r="J1731">
+        <v>0</v>
+      </c>
+      <c r="K1731" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1732" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1732" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1732">
+        <v>1598</v>
+      </c>
+      <c r="D1732" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1732" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1732" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1732" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1732" s="1">
+        <v>46122.596990740742</v>
+      </c>
+      <c r="J1732">
+        <v>0</v>
+      </c>
+      <c r="K1732" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1733" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1733" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1733">
+        <v>3182</v>
+      </c>
+      <c r="D1733" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1733" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1733" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1733" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1733" s="1">
+        <v>46122.596990740742</v>
+      </c>
+      <c r="J1733">
+        <v>0</v>
+      </c>
+      <c r="K1733" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1734" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1734" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1734">
+        <v>1553</v>
+      </c>
+      <c r="D1734" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1734" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1734" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1734" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1734" s="1">
+        <v>46122.597685185188</v>
+      </c>
+      <c r="J1734">
+        <v>0</v>
+      </c>
+      <c r="K1734" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1735" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1735" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1735">
+        <v>3803</v>
+      </c>
+      <c r="D1735" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1735" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1735" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1735" s="2">
+        <v>7.5925925925925926E-3</v>
+      </c>
+      <c r="I1735" s="1">
+        <v>46122.597685185188</v>
+      </c>
+      <c r="J1735">
+        <v>0</v>
+      </c>
+      <c r="K1735" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1736" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1736" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1736">
+        <v>4635</v>
+      </c>
+      <c r="D1736" t="s">
+        <v>187</v>
+      </c>
+      <c r="F1736" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1736" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1736" s="2">
+        <v>7.789351851851852E-3</v>
+      </c>
+      <c r="I1736" s="1">
+        <v>46122.598379629628</v>
+      </c>
+      <c r="J1736">
+        <v>0</v>
+      </c>
+      <c r="K1736" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1737" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1737" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1737">
+        <v>5143</v>
+      </c>
+      <c r="D1737" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1737" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1737" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1737" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1737" s="1">
+        <v>46122.598379629628</v>
+      </c>
+      <c r="J1737">
+        <v>0</v>
+      </c>
+      <c r="K1737" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1738" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1738" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1738">
+        <v>4825</v>
+      </c>
+      <c r="D1738" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1738" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1738" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1738" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1738" s="1">
+        <v>46122.599074074074</v>
+      </c>
+      <c r="J1738">
+        <v>0</v>
+      </c>
+      <c r="K1738" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1739" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1739" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1739">
+        <v>1578</v>
+      </c>
+      <c r="D1739" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1739" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1739" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1739" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1739" s="1">
+        <v>46122.599074074074</v>
+      </c>
+      <c r="J1739">
+        <v>0</v>
+      </c>
+      <c r="K1739" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1740" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1740" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1740">
+        <v>1599</v>
+      </c>
+      <c r="D1740" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1740" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1740" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1740" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1740" s="1">
+        <v>46122.599768518521</v>
+      </c>
+      <c r="J1740">
+        <v>0</v>
+      </c>
+      <c r="K1740" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1741" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1741" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1741">
+        <v>5144</v>
+      </c>
+      <c r="D1741" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1741" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1741" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1741" s="2">
+        <v>7.6851851851851855E-3</v>
+      </c>
+      <c r="I1741" s="1">
+        <v>46122.600462962961</v>
+      </c>
+      <c r="J1741">
+        <v>0</v>
+      </c>
+      <c r="K1741" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1742" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1742" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1742">
+        <v>1555</v>
+      </c>
+      <c r="D1742" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1742" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1742" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1742" s="2">
+        <v>7.1990740740740739E-3</v>
+      </c>
+      <c r="I1742" s="1">
+        <v>46122.600462962961</v>
+      </c>
+      <c r="J1742">
+        <v>0</v>
+      </c>
+      <c r="K1742" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1743" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1743" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1743">
+        <v>5269</v>
+      </c>
+      <c r="D1743" t="s">
+        <v>216</v>
+      </c>
+      <c r="F1743" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1743" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1743" s="2">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="I1743" s="1">
+        <v>46122.601157407407</v>
+      </c>
+      <c r="J1743">
+        <v>0</v>
+      </c>
+      <c r="K1743" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1744" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1744" s="2"/>
       <c r="I1744" s="1"/>
-    </row>
-    <row r="1745" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1745" s="2"/>
-      <c r="I1745" s="1"/>
-    </row>
-    <row r="1746" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1746" s="2"/>
-      <c r="I1746" s="1"/>
-    </row>
-    <row r="1747" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1747" s="2"/>
-      <c r="I1747" s="1"/>
-    </row>
-    <row r="1748" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1748" s="2"/>
-      <c r="I1748" s="1"/>
-    </row>
-    <row r="1749" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1749" s="2"/>
-      <c r="I1749" s="1"/>
-    </row>
-    <row r="1750" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1750" s="2"/>
-      <c r="I1750" s="1"/>
-    </row>
-    <row r="1751" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1751" s="2"/>
-      <c r="I1751" s="1"/>
-    </row>
-    <row r="1752" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1744" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1745" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1745" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1745">
+        <v>2659</v>
+      </c>
+      <c r="D1745" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1745" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1745" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1745" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1745" s="1">
+        <v>46122.601157407407</v>
+      </c>
+      <c r="J1745">
+        <v>0</v>
+      </c>
+      <c r="K1745" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1746" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1746" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1746">
+        <v>5142</v>
+      </c>
+      <c r="D1746" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1746" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1746" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1746" s="2">
+        <v>1.5625000000000001E-3</v>
+      </c>
+      <c r="I1746" s="1">
+        <v>46122.601851851854</v>
+      </c>
+      <c r="J1746">
+        <v>0</v>
+      </c>
+      <c r="K1746" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1747" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1747" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1747">
+        <v>1572</v>
+      </c>
+      <c r="D1747" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1747" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1747" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1747" s="2">
+        <v>7.8009259259259256E-3</v>
+      </c>
+      <c r="I1747" s="1">
+        <v>46122.601851851854</v>
+      </c>
+      <c r="J1747">
+        <v>0</v>
+      </c>
+      <c r="K1747" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1748" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1748" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1748">
+        <v>1571</v>
+      </c>
+      <c r="D1748" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1748" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1748" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1748" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1748" s="1">
+        <v>46122.602546296293</v>
+      </c>
+      <c r="J1748">
+        <v>0</v>
+      </c>
+      <c r="K1748" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1749" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1749" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1749">
+        <v>2867</v>
+      </c>
+      <c r="D1749" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1749" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1749" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1749" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1749" s="1">
+        <v>46122.60324074074</v>
+      </c>
+      <c r="J1749">
+        <v>0</v>
+      </c>
+      <c r="K1749" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1750" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1750" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1750">
+        <v>4797</v>
+      </c>
+      <c r="D1750" t="s">
+        <v>197</v>
+      </c>
+      <c r="F1750" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1750" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1750" s="2">
+        <v>7.7314814814814815E-3</v>
+      </c>
+      <c r="I1750" s="1">
+        <v>46122.60324074074</v>
+      </c>
+      <c r="J1750">
+        <v>0</v>
+      </c>
+      <c r="K1750" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1751" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1751" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1751">
+        <v>5410</v>
+      </c>
+      <c r="D1751" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1751" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1751" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1751" s="2">
+        <v>2.1145833333333332E-2</v>
+      </c>
+      <c r="I1751" s="1">
+        <v>46122.603935185187</v>
+      </c>
+      <c r="J1751">
+        <v>0</v>
+      </c>
+      <c r="K1751" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1752" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1752" s="2"/>
       <c r="I1752" s="1"/>
-    </row>
-    <row r="1753" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1753" s="2"/>
-      <c r="I1753" s="1"/>
-    </row>
-    <row r="1754" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1754" s="2"/>
-      <c r="I1754" s="1"/>
-    </row>
-    <row r="1755" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1755" s="2"/>
-      <c r="I1755" s="1"/>
-    </row>
-    <row r="1756" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1756" s="2"/>
-      <c r="I1756" s="1"/>
-    </row>
-    <row r="1757" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1752" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1753" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1753" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1753">
+        <v>1596</v>
+      </c>
+      <c r="D1753" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1753" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1753" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1753" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1753" s="1">
+        <v>46122.585300925923</v>
+      </c>
+      <c r="J1753">
+        <v>0</v>
+      </c>
+      <c r="K1753" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1754" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1754" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1754">
+        <v>5203</v>
+      </c>
+      <c r="D1754" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1754" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1754" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1754" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1754" s="1">
+        <v>46122.585995370369</v>
+      </c>
+      <c r="J1754">
+        <v>0</v>
+      </c>
+      <c r="K1754" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1755" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1755" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1755">
+        <v>5444</v>
+      </c>
+      <c r="D1755" t="s">
+        <v>222</v>
+      </c>
+      <c r="F1755" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1755" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1755" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1755" s="1">
+        <v>46122.586689814816</v>
+      </c>
+      <c r="J1755">
+        <v>0</v>
+      </c>
+      <c r="K1755" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1756" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1756" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1756">
+        <v>5317</v>
+      </c>
+      <c r="D1756" t="s">
+        <v>223</v>
+      </c>
+      <c r="F1756" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1756" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1756" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1756" s="1">
+        <v>46122.586689814816</v>
+      </c>
+      <c r="J1756">
+        <v>0</v>
+      </c>
+      <c r="K1756" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1757" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1757" s="2"/>
       <c r="I1757" s="1"/>
-    </row>
-    <row r="1758" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1758" s="2"/>
-      <c r="I1758" s="1"/>
-    </row>
-    <row r="1759" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1759" s="2"/>
-      <c r="I1759" s="1"/>
-    </row>
-    <row r="1760" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1760" s="2"/>
-      <c r="I1760" s="1"/>
-    </row>
-    <row r="1761" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1761" s="2"/>
-      <c r="I1761" s="1"/>
-    </row>
-    <row r="1762" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1762" s="2"/>
-      <c r="I1762" s="1"/>
-    </row>
-    <row r="1763" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1763" s="2"/>
-      <c r="I1763" s="1"/>
-    </row>
-    <row r="1764" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1764" s="2"/>
-      <c r="I1764" s="1"/>
-    </row>
-    <row r="1765" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1765" s="2"/>
-      <c r="I1765" s="1"/>
-    </row>
-    <row r="1766" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1766" s="2"/>
-      <c r="I1766" s="1"/>
-    </row>
-    <row r="1767" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1767" s="2"/>
-      <c r="I1767" s="1"/>
-    </row>
-    <row r="1768" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1768" s="2"/>
-      <c r="I1768" s="1"/>
-    </row>
-    <row r="1769" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1769" s="2"/>
-      <c r="I1769" s="1"/>
-    </row>
-    <row r="1770" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1770" s="2"/>
-      <c r="I1770" s="1"/>
-    </row>
-    <row r="1771" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1771" s="2"/>
-      <c r="I1771" s="1"/>
-    </row>
-    <row r="1772" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1757" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1758" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1758" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1758">
+        <v>5140</v>
+      </c>
+      <c r="D1758" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1758" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1758" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1758" s="2">
+        <v>7.6041666666666671E-3</v>
+      </c>
+      <c r="I1758" s="1">
+        <v>46122.587384259263</v>
+      </c>
+      <c r="J1758">
+        <v>0</v>
+      </c>
+      <c r="K1758" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1759" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1759" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1759">
+        <v>3841</v>
+      </c>
+      <c r="D1759" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1759" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1759" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1759" s="2">
+        <v>1.4398148148148148E-2</v>
+      </c>
+      <c r="I1759" s="1">
+        <v>46122.588078703702</v>
+      </c>
+      <c r="J1759">
+        <v>0</v>
+      </c>
+      <c r="K1759" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1760" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1760" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1760">
+        <v>3047</v>
+      </c>
+      <c r="D1760" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1760" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1760" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1760" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1760" s="1">
+        <v>46122.588078703702</v>
+      </c>
+      <c r="J1760">
+        <v>0</v>
+      </c>
+      <c r="K1760" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1761" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1761" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1761">
+        <v>1552</v>
+      </c>
+      <c r="D1761" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1761" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1761" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1761" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1761" s="1">
+        <v>46122.588773148149</v>
+      </c>
+      <c r="J1761">
+        <v>0</v>
+      </c>
+      <c r="K1761" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1762" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1762" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1762">
+        <v>1588</v>
+      </c>
+      <c r="D1762" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1762" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1762" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1762" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1762" s="1">
+        <v>46122.588773148149</v>
+      </c>
+      <c r="J1762">
+        <v>0</v>
+      </c>
+      <c r="K1762" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1763" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1763" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1763">
+        <v>5228</v>
+      </c>
+      <c r="D1763" t="s">
+        <v>214</v>
+      </c>
+      <c r="F1763" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1763" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1763" s="2">
+        <v>9.8148148148148144E-3</v>
+      </c>
+      <c r="I1763" s="1">
+        <v>46122.589467592596</v>
+      </c>
+      <c r="J1763">
+        <v>0</v>
+      </c>
+      <c r="K1763" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1764" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1764" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1764">
+        <v>3659</v>
+      </c>
+      <c r="D1764" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1764" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1764" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1764" s="2">
+        <v>8.3217592592592596E-3</v>
+      </c>
+      <c r="I1764" s="1">
+        <v>46122.589467592596</v>
+      </c>
+      <c r="J1764">
+        <v>0</v>
+      </c>
+      <c r="K1764" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1765" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1765" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1765">
+        <v>1551</v>
+      </c>
+      <c r="D1765" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1765" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1765" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1765" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1765" s="1">
+        <v>46122.590162037035</v>
+      </c>
+      <c r="J1765">
+        <v>0</v>
+      </c>
+      <c r="K1765" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1766" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1766" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1766">
+        <v>1581</v>
+      </c>
+      <c r="D1766" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1766" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1766" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1766" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1766" s="1">
+        <v>46122.590856481482</v>
+      </c>
+      <c r="J1766">
+        <v>0</v>
+      </c>
+      <c r="K1766" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1767" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1767" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1767">
+        <v>1545</v>
+      </c>
+      <c r="D1767" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1767" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1767" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1767" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1767" s="1">
+        <v>46122.590856481482</v>
+      </c>
+      <c r="J1767">
+        <v>0</v>
+      </c>
+      <c r="K1767" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1768" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1768" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1768">
+        <v>1604</v>
+      </c>
+      <c r="D1768" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1768" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1768" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1768" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1768" s="1">
+        <v>46122.591550925928</v>
+      </c>
+      <c r="J1768">
+        <v>0</v>
+      </c>
+      <c r="K1768" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1769" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1769" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1769">
+        <v>4726</v>
+      </c>
+      <c r="D1769" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1769" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1769" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1769" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1769" s="1">
+        <v>46122.591550925928</v>
+      </c>
+      <c r="J1769">
+        <v>0</v>
+      </c>
+      <c r="K1769" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1770" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1770" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1770">
+        <v>1540</v>
+      </c>
+      <c r="D1770" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1770" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1770" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1770" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1770" s="1">
+        <v>46122.592245370368</v>
+      </c>
+      <c r="J1770">
+        <v>0</v>
+      </c>
+      <c r="K1770" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1771" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1771" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1771">
+        <v>1601</v>
+      </c>
+      <c r="D1771" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1771" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1771" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1771" s="2">
+        <v>7.6157407407407406E-3</v>
+      </c>
+      <c r="I1771" s="1">
+        <v>46122.592939814815</v>
+      </c>
+      <c r="J1771">
+        <v>0</v>
+      </c>
+      <c r="K1771" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1772" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1772" s="2"/>
       <c r="I1772" s="1"/>
     </row>
-    <row r="1773" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1773" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1773" s="2"/>
       <c r="I1773" s="1"/>
     </row>
-    <row r="1774" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1774" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1774" s="2"/>
       <c r="I1774" s="1"/>
     </row>
-    <row r="1775" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1775" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1775" s="2"/>
       <c r="I1775" s="1"/>
     </row>
-    <row r="1776" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1776" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1776" s="2"/>
       <c r="I1776" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Panhandle Express\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124671BC-6F17-4D64-A05D-3DDD83661490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF76067-B704-44DF-8FE8-E850138787BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8536" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8537" uniqueCount="224">
   <si>
     <t>Company Name</t>
   </si>
@@ -48702,7 +48702,7 @@
         <v>46122.587268518517</v>
       </c>
       <c r="J1705">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1705" t="s">
         <v>11</v>
@@ -48731,7 +48731,7 @@
         <v>46122.587268518517</v>
       </c>
       <c r="J1706">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1706" t="s">
         <v>11</v>
@@ -48754,16 +48754,16 @@
         <v>218</v>
       </c>
       <c r="G1707" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1707" s="2">
-        <v>0</v>
+        <v>1.5787037037037037E-2</v>
       </c>
       <c r="I1707" s="1">
         <v>46122.587962962964</v>
       </c>
       <c r="J1707">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1707" t="s">
         <v>11</v>
@@ -48821,7 +48821,7 @@
         <v>46122.58865740741</v>
       </c>
       <c r="J1709">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1709" t="s">
         <v>11</v>
@@ -48850,7 +48850,7 @@
         <v>46122.58935185185</v>
       </c>
       <c r="J1710">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1710" t="s">
         <v>11</v>
@@ -48879,7 +48879,7 @@
         <v>46122.58935185185</v>
       </c>
       <c r="J1711">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1711" t="s">
         <v>11</v>
@@ -48928,16 +48928,16 @@
         <v>218</v>
       </c>
       <c r="G1713" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1713" s="2">
-        <v>0</v>
+        <v>8.4490740740740741E-3</v>
       </c>
       <c r="I1713" s="1">
         <v>46122.590046296296</v>
       </c>
       <c r="J1713">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1713" t="s">
         <v>11</v>
@@ -48966,7 +48966,7 @@
         <v>46122.590740740743</v>
       </c>
       <c r="J1714">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1714" t="s">
         <v>11</v>
@@ -49053,7 +49053,7 @@
         <v>46122.591435185182</v>
       </c>
       <c r="J1717">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1717" t="s">
         <v>11</v>
@@ -49073,16 +49073,16 @@
         <v>218</v>
       </c>
       <c r="G1718" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1718" s="2">
-        <v>0</v>
+        <v>8.6226851851851846E-3</v>
       </c>
       <c r="I1718" s="1">
         <v>46122.592129629629</v>
       </c>
       <c r="J1718">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1718" t="s">
         <v>11</v>
@@ -49111,7 +49111,7 @@
         <v>46122.592824074076</v>
       </c>
       <c r="J1719">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1719" t="s">
         <v>11</v>
@@ -49169,7 +49169,7 @@
         <v>46122.593518518515</v>
       </c>
       <c r="J1721">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1721" t="s">
         <v>11</v>
@@ -49198,7 +49198,7 @@
         <v>46122.593518518515</v>
       </c>
       <c r="J1722">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1722" t="s">
         <v>11</v>
@@ -49218,16 +49218,16 @@
         <v>218</v>
       </c>
       <c r="G1723" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1723" s="2">
-        <v>0</v>
+        <v>6.7245370370370367E-3</v>
       </c>
       <c r="I1723" s="1">
         <v>46122.594212962962</v>
       </c>
       <c r="J1723">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1723" t="s">
         <v>11</v>
@@ -49285,7 +49285,7 @@
         <v>46122.594907407409</v>
       </c>
       <c r="J1725">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1725" t="s">
         <v>11</v>
@@ -49343,7 +49343,7 @@
         <v>46122.595601851855</v>
       </c>
       <c r="J1727">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1727" t="s">
         <v>11</v>
@@ -49363,10 +49363,10 @@
         <v>218</v>
       </c>
       <c r="G1728" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1728" s="2">
-        <v>0</v>
+        <v>8.4953703703703701E-3</v>
       </c>
       <c r="I1728" s="1">
         <v>46122.595601851855</v>
@@ -49466,7 +49466,7 @@
         <v>46122.596990740742</v>
       </c>
       <c r="J1732">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1732" t="s">
         <v>11</v>
@@ -49486,16 +49486,16 @@
         <v>218</v>
       </c>
       <c r="G1733" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1733" s="2">
-        <v>0</v>
+        <v>8.9467592592592585E-3</v>
       </c>
       <c r="I1733" s="1">
         <v>46122.596990740742</v>
       </c>
       <c r="J1733">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1733" t="s">
         <v>11</v>
@@ -49524,7 +49524,7 @@
         <v>46122.597685185188</v>
       </c>
       <c r="J1734">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1734" t="s">
         <v>11</v>
@@ -49611,7 +49611,7 @@
         <v>46122.598379629628</v>
       </c>
       <c r="J1737">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1737" t="s">
         <v>11</v>
@@ -49640,7 +49640,7 @@
         <v>46122.599074074074</v>
       </c>
       <c r="J1738">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1738" t="s">
         <v>11</v>
@@ -49660,10 +49660,10 @@
         <v>218</v>
       </c>
       <c r="G1739" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="H1739" s="2">
-        <v>0</v>
+        <v>1.7361111111111112E-4</v>
       </c>
       <c r="I1739" s="1">
         <v>46122.599074074074</v>
@@ -49676,32 +49676,10 @@
       </c>
     </row>
     <row r="1740" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1740" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1740">
-        <v>1599</v>
-      </c>
-      <c r="D1740" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1740" t="s">
-        <v>218</v>
-      </c>
-      <c r="G1740" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1740" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1740" s="1">
-        <v>46122.599768518521</v>
-      </c>
-      <c r="J1740">
-        <v>0</v>
-      </c>
+      <c r="H1740" s="2"/>
+      <c r="I1740" s="1"/>
       <c r="K1740" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1741" spans="2:11" x14ac:dyDescent="0.25">
@@ -49709,10 +49687,10 @@
         <v>21</v>
       </c>
       <c r="C1741">
-        <v>5144</v>
+        <v>1599</v>
       </c>
       <c r="D1741" t="s">
-        <v>208</v>
+        <v>67</v>
       </c>
       <c r="F1741" t="s">
         <v>218</v>
@@ -49721,13 +49699,13 @@
         <v>10</v>
       </c>
       <c r="H1741" s="2">
-        <v>7.6851851851851855E-3</v>
+        <v>9.2939814814814812E-3</v>
       </c>
       <c r="I1741" s="1">
-        <v>46122.600462962961</v>
+        <v>46122.599768518521</v>
       </c>
       <c r="J1741">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1741" t="s">
         <v>11</v>
@@ -49738,10 +49716,10 @@
         <v>21</v>
       </c>
       <c r="C1742">
-        <v>1555</v>
+        <v>5144</v>
       </c>
       <c r="D1742" t="s">
-        <v>74</v>
+        <v>208</v>
       </c>
       <c r="F1742" t="s">
         <v>218</v>
@@ -49750,7 +49728,7 @@
         <v>10</v>
       </c>
       <c r="H1742" s="2">
-        <v>7.1990740740740739E-3</v>
+        <v>7.6851851851851855E-3</v>
       </c>
       <c r="I1742" s="1">
         <v>46122.600462962961</v>
@@ -49767,64 +49745,64 @@
         <v>21</v>
       </c>
       <c r="C1743">
-        <v>5269</v>
+        <v>1555</v>
       </c>
       <c r="D1743" t="s">
-        <v>216</v>
+        <v>74</v>
       </c>
       <c r="F1743" t="s">
         <v>218</v>
       </c>
       <c r="G1743" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1743" s="2">
+        <v>7.1990740740740739E-3</v>
+      </c>
+      <c r="I1743" s="1">
+        <v>46122.600462962961</v>
+      </c>
+      <c r="J1743">
+        <v>0</v>
+      </c>
+      <c r="K1743" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1744" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1744" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1744">
+        <v>5269</v>
+      </c>
+      <c r="D1744" t="s">
+        <v>216</v>
+      </c>
+      <c r="F1744" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1744" t="s">
         <v>34</v>
       </c>
-      <c r="H1743" s="2">
+      <c r="H1744" s="2">
         <v>8.1018518518518516E-5</v>
       </c>
-      <c r="I1743" s="1">
+      <c r="I1744" s="1">
         <v>46122.601157407407</v>
       </c>
-      <c r="J1743">
-        <v>0</v>
-      </c>
-      <c r="K1743" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1744" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1744" s="2"/>
-      <c r="I1744" s="1"/>
+      <c r="J1744">
+        <v>0</v>
+      </c>
       <c r="K1744" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1745" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1745" s="2"/>
+      <c r="I1745" s="1"/>
+      <c r="K1745" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="1745" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1745" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1745">
-        <v>2659</v>
-      </c>
-      <c r="D1745" t="s">
-        <v>126</v>
-      </c>
-      <c r="F1745" t="s">
-        <v>218</v>
-      </c>
-      <c r="G1745" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1745" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1745" s="1">
-        <v>46122.601157407407</v>
-      </c>
-      <c r="J1745">
-        <v>0</v>
-      </c>
-      <c r="K1745" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1746" spans="2:11" x14ac:dyDescent="0.25">
@@ -49832,25 +49810,25 @@
         <v>21</v>
       </c>
       <c r="C1746">
-        <v>5142</v>
+        <v>2659</v>
       </c>
       <c r="D1746" t="s">
-        <v>209</v>
+        <v>126</v>
       </c>
       <c r="F1746" t="s">
         <v>218</v>
       </c>
       <c r="G1746" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1746" s="2">
-        <v>1.5625000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I1746" s="1">
-        <v>46122.601851851854</v>
+        <v>46122.601157407407</v>
       </c>
       <c r="J1746">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1746" t="s">
         <v>11</v>
@@ -49861,10 +49839,10 @@
         <v>21</v>
       </c>
       <c r="C1747">
-        <v>1572</v>
+        <v>5142</v>
       </c>
       <c r="D1747" t="s">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="F1747" t="s">
         <v>218</v>
@@ -49873,7 +49851,7 @@
         <v>10</v>
       </c>
       <c r="H1747" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>1.5625000000000001E-3</v>
       </c>
       <c r="I1747" s="1">
         <v>46122.601851851854</v>
@@ -49890,22 +49868,22 @@
         <v>21</v>
       </c>
       <c r="C1748">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="D1748" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F1748" t="s">
         <v>218</v>
       </c>
       <c r="G1748" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1748" s="2">
-        <v>0</v>
+        <v>7.8009259259259256E-3</v>
       </c>
       <c r="I1748" s="1">
-        <v>46122.602546296293</v>
+        <v>46122.601851851854</v>
       </c>
       <c r="J1748">
         <v>0</v>
@@ -49919,10 +49897,10 @@
         <v>21</v>
       </c>
       <c r="C1749">
-        <v>2867</v>
+        <v>1571</v>
       </c>
       <c r="D1749" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="F1749" t="s">
         <v>218</v>
@@ -49934,10 +49912,10 @@
         <v>0</v>
       </c>
       <c r="I1749" s="1">
-        <v>46122.60324074074</v>
+        <v>46122.602546296293</v>
       </c>
       <c r="J1749">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1749" t="s">
         <v>11</v>
@@ -49948,25 +49926,25 @@
         <v>21</v>
       </c>
       <c r="C1750">
-        <v>4797</v>
+        <v>2867</v>
       </c>
       <c r="D1750" t="s">
-        <v>197</v>
+        <v>131</v>
       </c>
       <c r="F1750" t="s">
         <v>218</v>
       </c>
       <c r="G1750" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1750" s="2">
-        <v>7.7314814814814815E-3</v>
+        <v>0</v>
       </c>
       <c r="I1750" s="1">
         <v>46122.60324074074</v>
       </c>
       <c r="J1750">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1750" t="s">
         <v>11</v>
@@ -49977,64 +49955,64 @@
         <v>21</v>
       </c>
       <c r="C1751">
-        <v>5410</v>
+        <v>4797</v>
       </c>
       <c r="D1751" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="F1751" t="s">
         <v>218</v>
       </c>
       <c r="G1751" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1751" s="2">
+        <v>7.7314814814814815E-3</v>
+      </c>
+      <c r="I1751" s="1">
+        <v>46122.60324074074</v>
+      </c>
+      <c r="J1751">
+        <v>0</v>
+      </c>
+      <c r="K1751" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1752" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1752" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1752">
+        <v>5410</v>
+      </c>
+      <c r="D1752" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1752" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1752" t="s">
         <v>34</v>
       </c>
-      <c r="H1751" s="2">
+      <c r="H1752" s="2">
         <v>2.1145833333333332E-2</v>
       </c>
-      <c r="I1751" s="1">
+      <c r="I1752" s="1">
         <v>46122.603935185187</v>
       </c>
-      <c r="J1751">
-        <v>0</v>
-      </c>
-      <c r="K1751" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1752" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1752" s="2"/>
-      <c r="I1752" s="1"/>
+      <c r="J1752">
+        <v>0</v>
+      </c>
       <c r="K1752" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1753" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1753" s="2"/>
+      <c r="I1753" s="1"/>
+      <c r="K1753" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="1753" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1753" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1753">
-        <v>1596</v>
-      </c>
-      <c r="D1753" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1753" t="s">
-        <v>218</v>
-      </c>
-      <c r="G1753" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1753" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1753" s="1">
-        <v>46122.585300925923</v>
-      </c>
-      <c r="J1753">
-        <v>0</v>
-      </c>
-      <c r="K1753" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1754" spans="2:11" x14ac:dyDescent="0.25">
@@ -50042,22 +50020,22 @@
         <v>21</v>
       </c>
       <c r="C1754">
-        <v>5203</v>
+        <v>1596</v>
       </c>
       <c r="D1754" t="s">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="F1754" t="s">
         <v>218</v>
       </c>
       <c r="G1754" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1754" s="2">
-        <v>0</v>
+        <v>9.0162037037037034E-3</v>
       </c>
       <c r="I1754" s="1">
-        <v>46122.585995370369</v>
+        <v>46122.585300925923</v>
       </c>
       <c r="J1754">
         <v>0</v>
@@ -50071,10 +50049,10 @@
         <v>21</v>
       </c>
       <c r="C1755">
-        <v>5444</v>
+        <v>5203</v>
       </c>
       <c r="D1755" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="F1755" t="s">
         <v>218</v>
@@ -50086,10 +50064,10 @@
         <v>0</v>
       </c>
       <c r="I1755" s="1">
-        <v>46122.586689814816</v>
+        <v>46122.585995370369</v>
       </c>
       <c r="J1755">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1755" t="s">
         <v>11</v>
@@ -50100,16 +50078,16 @@
         <v>21</v>
       </c>
       <c r="C1756">
-        <v>5317</v>
+        <v>5444</v>
       </c>
       <c r="D1756" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F1756" t="s">
         <v>218</v>
       </c>
       <c r="G1756" t="s">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="H1756" s="2">
         <v>0</v>
@@ -50118,46 +50096,46 @@
         <v>46122.586689814816</v>
       </c>
       <c r="J1756">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1756" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1757" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1757" s="2"/>
-      <c r="I1757" s="1"/>
+      <c r="B1757" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1757">
+        <v>5317</v>
+      </c>
+      <c r="D1757" t="s">
+        <v>223</v>
+      </c>
+      <c r="F1757" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1757" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1757" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1757" s="1">
+        <v>46122.586689814816</v>
+      </c>
+      <c r="J1757">
+        <v>0</v>
+      </c>
       <c r="K1757" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1758" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1758" s="2"/>
+      <c r="I1758" s="1"/>
+      <c r="K1758" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="1758" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1758" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1758">
-        <v>5140</v>
-      </c>
-      <c r="D1758" t="s">
-        <v>210</v>
-      </c>
-      <c r="F1758" t="s">
-        <v>218</v>
-      </c>
-      <c r="G1758" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1758" s="2">
-        <v>7.6041666666666671E-3</v>
-      </c>
-      <c r="I1758" s="1">
-        <v>46122.587384259263</v>
-      </c>
-      <c r="J1758">
-        <v>0</v>
-      </c>
-      <c r="K1758" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1759" spans="2:11" x14ac:dyDescent="0.25">
@@ -50165,10 +50143,10 @@
         <v>21</v>
       </c>
       <c r="C1759">
-        <v>3841</v>
+        <v>5140</v>
       </c>
       <c r="D1759" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="F1759" t="s">
         <v>218</v>
@@ -50177,10 +50155,10 @@
         <v>10</v>
       </c>
       <c r="H1759" s="2">
-        <v>1.4398148148148148E-2</v>
+        <v>7.6041666666666671E-3</v>
       </c>
       <c r="I1759" s="1">
-        <v>46122.588078703702</v>
+        <v>46122.587384259263</v>
       </c>
       <c r="J1759">
         <v>0</v>
@@ -50194,19 +50172,19 @@
         <v>21</v>
       </c>
       <c r="C1760">
-        <v>3047</v>
+        <v>3841</v>
       </c>
       <c r="D1760" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F1760" t="s">
         <v>218</v>
       </c>
       <c r="G1760" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1760" s="2">
-        <v>0</v>
+        <v>1.4398148148148148E-2</v>
       </c>
       <c r="I1760" s="1">
         <v>46122.588078703702</v>
@@ -50223,25 +50201,25 @@
         <v>21</v>
       </c>
       <c r="C1761">
-        <v>1552</v>
+        <v>3047</v>
       </c>
       <c r="D1761" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="F1761" t="s">
         <v>218</v>
       </c>
       <c r="G1761" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1761" s="2">
-        <v>0</v>
+        <v>6.898148148148148E-3</v>
       </c>
       <c r="I1761" s="1">
-        <v>46122.588773148149</v>
+        <v>46122.588078703702</v>
       </c>
       <c r="J1761">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1761" t="s">
         <v>11</v>
@@ -50252,19 +50230,19 @@
         <v>21</v>
       </c>
       <c r="C1762">
-        <v>1588</v>
+        <v>1552</v>
       </c>
       <c r="D1762" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F1762" t="s">
         <v>218</v>
       </c>
       <c r="G1762" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1762" s="2">
-        <v>0</v>
+        <v>8.0208333333333329E-3</v>
       </c>
       <c r="I1762" s="1">
         <v>46122.588773148149</v>
@@ -50281,25 +50259,25 @@
         <v>21</v>
       </c>
       <c r="C1763">
-        <v>5228</v>
+        <v>1588</v>
       </c>
       <c r="D1763" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="F1763" t="s">
         <v>218</v>
       </c>
       <c r="G1763" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1763" s="2">
-        <v>9.8148148148148144E-3</v>
+        <v>0</v>
       </c>
       <c r="I1763" s="1">
-        <v>46122.589467592596</v>
+        <v>46122.588773148149</v>
       </c>
       <c r="J1763">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1763" t="s">
         <v>11</v>
@@ -50310,10 +50288,10 @@
         <v>21</v>
       </c>
       <c r="C1764">
-        <v>3659</v>
+        <v>5228</v>
       </c>
       <c r="D1764" t="s">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="F1764" t="s">
         <v>218</v>
@@ -50322,7 +50300,7 @@
         <v>10</v>
       </c>
       <c r="H1764" s="2">
-        <v>8.3217592592592596E-3</v>
+        <v>9.8148148148148144E-3</v>
       </c>
       <c r="I1764" s="1">
         <v>46122.589467592596</v>
@@ -50339,22 +50317,22 @@
         <v>21</v>
       </c>
       <c r="C1765">
-        <v>1551</v>
+        <v>3659</v>
       </c>
       <c r="D1765" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="F1765" t="s">
         <v>218</v>
       </c>
       <c r="G1765" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1765" s="2">
-        <v>0</v>
+        <v>8.3217592592592596E-3</v>
       </c>
       <c r="I1765" s="1">
-        <v>46122.590162037035</v>
+        <v>46122.589467592596</v>
       </c>
       <c r="J1765">
         <v>0</v>
@@ -50368,10 +50346,10 @@
         <v>21</v>
       </c>
       <c r="C1766">
-        <v>1581</v>
+        <v>1551</v>
       </c>
       <c r="D1766" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F1766" t="s">
         <v>218</v>
@@ -50383,10 +50361,10 @@
         <v>0</v>
       </c>
       <c r="I1766" s="1">
-        <v>46122.590856481482</v>
+        <v>46122.590162037035</v>
       </c>
       <c r="J1766">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1766" t="s">
         <v>11</v>
@@ -50397,25 +50375,25 @@
         <v>21</v>
       </c>
       <c r="C1767">
-        <v>1545</v>
+        <v>1581</v>
       </c>
       <c r="D1767" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F1767" t="s">
         <v>218</v>
       </c>
       <c r="G1767" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1767" s="2">
-        <v>0</v>
+        <v>7.4652777777777781E-3</v>
       </c>
       <c r="I1767" s="1">
         <v>46122.590856481482</v>
       </c>
       <c r="J1767">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1767" t="s">
         <v>11</v>
@@ -50426,10 +50404,10 @@
         <v>21</v>
       </c>
       <c r="C1768">
-        <v>1604</v>
+        <v>1545</v>
       </c>
       <c r="D1768" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F1768" t="s">
         <v>218</v>
@@ -50441,10 +50419,10 @@
         <v>0</v>
       </c>
       <c r="I1768" s="1">
-        <v>46122.591550925928</v>
+        <v>46122.590856481482</v>
       </c>
       <c r="J1768">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1768" t="s">
         <v>11</v>
@@ -50455,10 +50433,10 @@
         <v>21</v>
       </c>
       <c r="C1769">
-        <v>4726</v>
+        <v>1604</v>
       </c>
       <c r="D1769" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="F1769" t="s">
         <v>218</v>
@@ -50473,7 +50451,7 @@
         <v>46122.591550925928</v>
       </c>
       <c r="J1769">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1769" t="s">
         <v>11</v>
@@ -50484,25 +50462,25 @@
         <v>21</v>
       </c>
       <c r="C1770">
-        <v>1540</v>
+        <v>4726</v>
       </c>
       <c r="D1770" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="F1770" t="s">
         <v>218</v>
       </c>
       <c r="G1770" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1770" s="2">
-        <v>0</v>
+        <v>1.6724537037037038E-2</v>
       </c>
       <c r="I1770" s="1">
-        <v>46122.592245370368</v>
+        <v>46122.591550925928</v>
       </c>
       <c r="J1770">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1770" t="s">
         <v>11</v>
@@ -50513,10 +50491,10 @@
         <v>21</v>
       </c>
       <c r="C1771">
-        <v>1601</v>
+        <v>1540</v>
       </c>
       <c r="D1771" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F1771" t="s">
         <v>218</v>
@@ -50525,21 +50503,46 @@
         <v>10</v>
       </c>
       <c r="H1771" s="2">
+        <v>9.3518518518518525E-3</v>
+      </c>
+      <c r="I1771" s="1">
+        <v>46122.592245370368</v>
+      </c>
+      <c r="J1771">
+        <v>1</v>
+      </c>
+      <c r="K1771" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1772" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1772" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1772">
+        <v>1601</v>
+      </c>
+      <c r="D1772" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1772" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1772" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1772" s="2">
         <v>7.6157407407407406E-3</v>
       </c>
-      <c r="I1771" s="1">
+      <c r="I1772" s="1">
         <v>46122.592939814815</v>
       </c>
-      <c r="J1771">
-        <v>0</v>
-      </c>
-      <c r="K1771" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1772" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1772" s="2"/>
-      <c r="I1772" s="1"/>
+      <c r="J1772">
+        <v>0</v>
+      </c>
+      <c r="K1772" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1773" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1773" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Panhandle Express\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF76067-B704-44DF-8FE8-E850138787BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2BFB19-7FEB-4F83-AC2F-B9A10BA60465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8537" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8538" uniqueCount="224">
   <si>
     <t>Company Name</t>
   </si>
@@ -48548,10 +48548,10 @@
         <v>16</v>
       </c>
       <c r="G1700" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1700" s="2">
-        <v>0</v>
+        <v>1.3715277777777778E-2</v>
       </c>
       <c r="I1700" s="1">
         <v>46083.807060185187</v>
@@ -48702,7 +48702,7 @@
         <v>46122.587268518517</v>
       </c>
       <c r="J1705">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1705" t="s">
         <v>11</v>
@@ -48731,7 +48731,7 @@
         <v>46122.587268518517</v>
       </c>
       <c r="J1706">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1706" t="s">
         <v>11</v>
@@ -48821,7 +48821,7 @@
         <v>46122.58865740741</v>
       </c>
       <c r="J1709">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1709" t="s">
         <v>11</v>
@@ -48850,7 +48850,7 @@
         <v>46122.58935185185</v>
       </c>
       <c r="J1710">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1710" t="s">
         <v>11</v>
@@ -48879,7 +48879,7 @@
         <v>46122.58935185185</v>
       </c>
       <c r="J1711">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1711" t="s">
         <v>11</v>
@@ -48957,16 +48957,16 @@
         <v>218</v>
       </c>
       <c r="G1714" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1714" s="2">
-        <v>0</v>
+        <v>6.8865740740740745E-3</v>
       </c>
       <c r="I1714" s="1">
         <v>46122.590740740743</v>
       </c>
       <c r="J1714">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1714" t="s">
         <v>11</v>
@@ -49044,10 +49044,10 @@
         <v>218</v>
       </c>
       <c r="G1717" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="H1717" s="2">
-        <v>0</v>
+        <v>3.6574074074074074E-3</v>
       </c>
       <c r="I1717" s="1">
         <v>46122.591435185182</v>
@@ -49060,32 +49060,10 @@
       </c>
     </row>
     <row r="1718" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1718" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1718">
-        <v>1579</v>
-      </c>
-      <c r="D1718" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1718" t="s">
-        <v>218</v>
-      </c>
-      <c r="G1718" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1718" s="2">
-        <v>8.6226851851851846E-3</v>
-      </c>
-      <c r="I1718" s="1">
-        <v>46122.592129629629</v>
-      </c>
-      <c r="J1718">
-        <v>1</v>
-      </c>
+      <c r="H1718" s="2"/>
+      <c r="I1718" s="1"/>
       <c r="K1718" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1719" spans="2:11" x14ac:dyDescent="0.25">
@@ -49093,22 +49071,22 @@
         <v>21</v>
       </c>
       <c r="C1719">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="D1719" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1719" t="s">
         <v>218</v>
       </c>
       <c r="G1719" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1719" s="2">
-        <v>0</v>
+        <v>8.6226851851851846E-3</v>
       </c>
       <c r="I1719" s="1">
-        <v>46122.592824074076</v>
+        <v>46122.592129629629</v>
       </c>
       <c r="J1719">
         <v>1</v>
@@ -49122,25 +49100,25 @@
         <v>21</v>
       </c>
       <c r="C1720">
-        <v>1549</v>
+        <v>1576</v>
       </c>
       <c r="D1720" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F1720" t="s">
         <v>218</v>
       </c>
       <c r="G1720" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1720" s="2">
-        <v>7.7777777777777776E-3</v>
+        <v>0</v>
       </c>
       <c r="I1720" s="1">
         <v>46122.592824074076</v>
       </c>
       <c r="J1720">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1720" t="s">
         <v>11</v>
@@ -49151,25 +49129,25 @@
         <v>21</v>
       </c>
       <c r="C1721">
-        <v>3188</v>
+        <v>1549</v>
       </c>
       <c r="D1721" t="s">
-        <v>145</v>
+        <v>52</v>
       </c>
       <c r="F1721" t="s">
         <v>218</v>
       </c>
       <c r="G1721" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1721" s="2">
-        <v>0</v>
+        <v>7.7777777777777776E-3</v>
       </c>
       <c r="I1721" s="1">
-        <v>46122.593518518515</v>
+        <v>46122.592824074076</v>
       </c>
       <c r="J1721">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1721" t="s">
         <v>11</v>
@@ -49180,10 +49158,10 @@
         <v>21</v>
       </c>
       <c r="C1722">
-        <v>3181</v>
+        <v>3188</v>
       </c>
       <c r="D1722" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F1722" t="s">
         <v>218</v>
@@ -49198,7 +49176,7 @@
         <v>46122.593518518515</v>
       </c>
       <c r="J1722">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1722" t="s">
         <v>11</v>
@@ -49209,10 +49187,10 @@
         <v>21</v>
       </c>
       <c r="C1723">
-        <v>2670</v>
+        <v>3181</v>
       </c>
       <c r="D1723" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="F1723" t="s">
         <v>218</v>
@@ -49221,10 +49199,10 @@
         <v>10</v>
       </c>
       <c r="H1723" s="2">
-        <v>6.7245370370370367E-3</v>
+        <v>7.2800925925925923E-3</v>
       </c>
       <c r="I1723" s="1">
-        <v>46122.594212962962</v>
+        <v>46122.593518518515</v>
       </c>
       <c r="J1723">
         <v>1</v>
@@ -49238,10 +49216,10 @@
         <v>21</v>
       </c>
       <c r="C1724">
-        <v>1592</v>
+        <v>2670</v>
       </c>
       <c r="D1724" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="F1724" t="s">
         <v>218</v>
@@ -49250,13 +49228,13 @@
         <v>10</v>
       </c>
       <c r="H1724" s="2">
-        <v>8.3333333333333332E-3</v>
+        <v>6.7245370370370367E-3</v>
       </c>
       <c r="I1724" s="1">
         <v>46122.594212962962</v>
       </c>
       <c r="J1724">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1724" t="s">
         <v>11</v>
@@ -49267,25 +49245,25 @@
         <v>21</v>
       </c>
       <c r="C1725">
-        <v>1561</v>
+        <v>1592</v>
       </c>
       <c r="D1725" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F1725" t="s">
         <v>218</v>
       </c>
       <c r="G1725" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1725" s="2">
-        <v>0</v>
+        <v>8.3333333333333332E-3</v>
       </c>
       <c r="I1725" s="1">
-        <v>46122.594907407409</v>
+        <v>46122.594212962962</v>
       </c>
       <c r="J1725">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1725" t="s">
         <v>11</v>
@@ -49296,10 +49274,10 @@
         <v>21</v>
       </c>
       <c r="C1726">
-        <v>3187</v>
+        <v>1561</v>
       </c>
       <c r="D1726" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="F1726" t="s">
         <v>218</v>
@@ -49308,13 +49286,13 @@
         <v>10</v>
       </c>
       <c r="H1726" s="2">
-        <v>9.2245370370370363E-3</v>
+        <v>3.0439814814814813E-3</v>
       </c>
       <c r="I1726" s="1">
         <v>46122.594907407409</v>
       </c>
       <c r="J1726">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1726" t="s">
         <v>11</v>
@@ -49325,25 +49303,25 @@
         <v>21</v>
       </c>
       <c r="C1727">
-        <v>1597</v>
+        <v>3187</v>
       </c>
       <c r="D1727" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="F1727" t="s">
         <v>218</v>
       </c>
       <c r="G1727" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1727" s="2">
-        <v>0</v>
+        <v>9.2245370370370363E-3</v>
       </c>
       <c r="I1727" s="1">
-        <v>46122.595601851855</v>
+        <v>46122.594907407409</v>
       </c>
       <c r="J1727">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1727" t="s">
         <v>11</v>
@@ -49354,25 +49332,25 @@
         <v>21</v>
       </c>
       <c r="C1728">
-        <v>1569</v>
+        <v>1597</v>
       </c>
       <c r="D1728" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="F1728" t="s">
         <v>218</v>
       </c>
       <c r="G1728" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1728" s="2">
-        <v>8.4953703703703701E-3</v>
+        <v>0</v>
       </c>
       <c r="I1728" s="1">
         <v>46122.595601851855</v>
       </c>
       <c r="J1728">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1728" t="s">
         <v>11</v>
@@ -49383,64 +49361,64 @@
         <v>21</v>
       </c>
       <c r="C1729">
-        <v>5181</v>
+        <v>1569</v>
       </c>
       <c r="D1729" t="s">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="F1729" t="s">
         <v>218</v>
       </c>
       <c r="G1729" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1729" s="2">
+        <v>8.4953703703703701E-3</v>
+      </c>
+      <c r="I1729" s="1">
+        <v>46122.595601851855</v>
+      </c>
+      <c r="J1729">
+        <v>0</v>
+      </c>
+      <c r="K1729" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1730" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1730" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1730">
+        <v>5181</v>
+      </c>
+      <c r="D1730" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1730" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1730" t="s">
         <v>34</v>
       </c>
-      <c r="H1729" s="2">
+      <c r="H1730" s="2">
         <v>1.0416666666666667E-4</v>
       </c>
-      <c r="I1729" s="1">
+      <c r="I1730" s="1">
         <v>46122.596296296295</v>
       </c>
-      <c r="J1729">
-        <v>0</v>
-      </c>
-      <c r="K1729" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1730" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1730" s="2"/>
-      <c r="I1730" s="1"/>
+      <c r="J1730">
+        <v>0</v>
+      </c>
       <c r="K1730" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1731" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1731" s="2"/>
+      <c r="I1731" s="1"/>
+      <c r="K1731" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="1731" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1731" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1731">
-        <v>1538</v>
-      </c>
-      <c r="D1731" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1731" t="s">
-        <v>218</v>
-      </c>
-      <c r="G1731" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1731" s="2">
-        <v>8.3449074074074068E-3</v>
-      </c>
-      <c r="I1731" s="1">
-        <v>46122.596990740742</v>
-      </c>
-      <c r="J1731">
-        <v>0</v>
-      </c>
-      <c r="K1731" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1732" spans="2:11" x14ac:dyDescent="0.25">
@@ -49448,25 +49426,25 @@
         <v>21</v>
       </c>
       <c r="C1732">
-        <v>1598</v>
+        <v>1538</v>
       </c>
       <c r="D1732" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F1732" t="s">
         <v>218</v>
       </c>
       <c r="G1732" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1732" s="2">
-        <v>0</v>
+        <v>8.3449074074074068E-3</v>
       </c>
       <c r="I1732" s="1">
         <v>46122.596990740742</v>
       </c>
       <c r="J1732">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1732" t="s">
         <v>11</v>
@@ -49477,10 +49455,10 @@
         <v>21</v>
       </c>
       <c r="C1733">
-        <v>3182</v>
+        <v>1598</v>
       </c>
       <c r="D1733" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="F1733" t="s">
         <v>218</v>
@@ -49489,13 +49467,13 @@
         <v>10</v>
       </c>
       <c r="H1733" s="2">
-        <v>8.9467592592592585E-3</v>
+        <v>6.7708333333333336E-3</v>
       </c>
       <c r="I1733" s="1">
         <v>46122.596990740742</v>
       </c>
       <c r="J1733">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1733" t="s">
         <v>11</v>
@@ -49506,22 +49484,22 @@
         <v>21</v>
       </c>
       <c r="C1734">
-        <v>1553</v>
+        <v>3182</v>
       </c>
       <c r="D1734" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="F1734" t="s">
         <v>218</v>
       </c>
       <c r="G1734" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1734" s="2">
-        <v>0</v>
+        <v>8.9467592592592585E-3</v>
       </c>
       <c r="I1734" s="1">
-        <v>46122.597685185188</v>
+        <v>46122.596990740742</v>
       </c>
       <c r="J1734">
         <v>1</v>
@@ -49535,25 +49513,25 @@
         <v>21</v>
       </c>
       <c r="C1735">
-        <v>3803</v>
+        <v>1553</v>
       </c>
       <c r="D1735" t="s">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c r="F1735" t="s">
         <v>218</v>
       </c>
       <c r="G1735" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1735" s="2">
-        <v>7.5925925925925926E-3</v>
+        <v>0</v>
       </c>
       <c r="I1735" s="1">
         <v>46122.597685185188</v>
       </c>
       <c r="J1735">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1735" t="s">
         <v>11</v>
@@ -49564,10 +49542,10 @@
         <v>21</v>
       </c>
       <c r="C1736">
-        <v>4635</v>
+        <v>3803</v>
       </c>
       <c r="D1736" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="F1736" t="s">
         <v>218</v>
@@ -49576,10 +49554,10 @@
         <v>10</v>
       </c>
       <c r="H1736" s="2">
-        <v>7.789351851851852E-3</v>
+        <v>7.5925925925925926E-3</v>
       </c>
       <c r="I1736" s="1">
-        <v>46122.598379629628</v>
+        <v>46122.597685185188</v>
       </c>
       <c r="J1736">
         <v>0</v>
@@ -49593,25 +49571,25 @@
         <v>21</v>
       </c>
       <c r="C1737">
-        <v>5143</v>
+        <v>4635</v>
       </c>
       <c r="D1737" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="F1737" t="s">
         <v>218</v>
       </c>
       <c r="G1737" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1737" s="2">
-        <v>0</v>
+        <v>7.789351851851852E-3</v>
       </c>
       <c r="I1737" s="1">
         <v>46122.598379629628</v>
       </c>
       <c r="J1737">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1737" t="s">
         <v>11</v>
@@ -49622,10 +49600,10 @@
         <v>21</v>
       </c>
       <c r="C1738">
-        <v>4825</v>
+        <v>5143</v>
       </c>
       <c r="D1738" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F1738" t="s">
         <v>218</v>
@@ -49637,10 +49615,10 @@
         <v>0</v>
       </c>
       <c r="I1738" s="1">
-        <v>46122.599074074074</v>
+        <v>46122.598379629628</v>
       </c>
       <c r="J1738">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1738" t="s">
         <v>11</v>
@@ -49651,64 +49629,64 @@
         <v>21</v>
       </c>
       <c r="C1739">
-        <v>1578</v>
+        <v>4825</v>
       </c>
       <c r="D1739" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="F1739" t="s">
         <v>218</v>
       </c>
       <c r="G1739" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H1739" s="2">
-        <v>1.7361111111111112E-4</v>
+        <v>6.6550925925925927E-3</v>
       </c>
       <c r="I1739" s="1">
         <v>46122.599074074074</v>
       </c>
       <c r="J1739">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1739" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1740" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1740" s="2"/>
-      <c r="I1740" s="1"/>
+      <c r="B1740" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1740">
+        <v>1578</v>
+      </c>
+      <c r="D1740" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1740" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1740" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1740" s="2">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="I1740" s="1">
+        <v>46122.599074074074</v>
+      </c>
+      <c r="J1740">
+        <v>0</v>
+      </c>
       <c r="K1740" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1741" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1741" s="2"/>
+      <c r="I1741" s="1"/>
+      <c r="K1741" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="1741" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1741" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1741">
-        <v>1599</v>
-      </c>
-      <c r="D1741" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1741" t="s">
-        <v>218</v>
-      </c>
-      <c r="G1741" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1741" s="2">
-        <v>9.2939814814814812E-3</v>
-      </c>
-      <c r="I1741" s="1">
-        <v>46122.599768518521</v>
-      </c>
-      <c r="J1741">
-        <v>1</v>
-      </c>
-      <c r="K1741" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1742" spans="2:11" x14ac:dyDescent="0.25">
@@ -49716,10 +49694,10 @@
         <v>21</v>
       </c>
       <c r="C1742">
-        <v>5144</v>
+        <v>1599</v>
       </c>
       <c r="D1742" t="s">
-        <v>208</v>
+        <v>67</v>
       </c>
       <c r="F1742" t="s">
         <v>218</v>
@@ -49728,13 +49706,13 @@
         <v>10</v>
       </c>
       <c r="H1742" s="2">
-        <v>7.6851851851851855E-3</v>
+        <v>9.2939814814814812E-3</v>
       </c>
       <c r="I1742" s="1">
-        <v>46122.600462962961</v>
+        <v>46122.599768518521</v>
       </c>
       <c r="J1742">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1742" t="s">
         <v>11</v>
@@ -49745,10 +49723,10 @@
         <v>21</v>
       </c>
       <c r="C1743">
-        <v>1555</v>
+        <v>5144</v>
       </c>
       <c r="D1743" t="s">
-        <v>74</v>
+        <v>208</v>
       </c>
       <c r="F1743" t="s">
         <v>218</v>
@@ -49757,7 +49735,7 @@
         <v>10</v>
       </c>
       <c r="H1743" s="2">
-        <v>7.1990740740740739E-3</v>
+        <v>7.6851851851851855E-3</v>
       </c>
       <c r="I1743" s="1">
         <v>46122.600462962961</v>
@@ -49774,64 +49752,64 @@
         <v>21</v>
       </c>
       <c r="C1744">
-        <v>5269</v>
+        <v>1555</v>
       </c>
       <c r="D1744" t="s">
-        <v>216</v>
+        <v>74</v>
       </c>
       <c r="F1744" t="s">
         <v>218</v>
       </c>
       <c r="G1744" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1744" s="2">
+        <v>7.1990740740740739E-3</v>
+      </c>
+      <c r="I1744" s="1">
+        <v>46122.600462962961</v>
+      </c>
+      <c r="J1744">
+        <v>0</v>
+      </c>
+      <c r="K1744" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1745" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1745" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1745">
+        <v>5269</v>
+      </c>
+      <c r="D1745" t="s">
+        <v>216</v>
+      </c>
+      <c r="F1745" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1745" t="s">
         <v>34</v>
       </c>
-      <c r="H1744" s="2">
+      <c r="H1745" s="2">
         <v>8.1018518518518516E-5</v>
       </c>
-      <c r="I1744" s="1">
+      <c r="I1745" s="1">
         <v>46122.601157407407</v>
       </c>
-      <c r="J1744">
-        <v>0</v>
-      </c>
-      <c r="K1744" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1745" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1745" s="2"/>
-      <c r="I1745" s="1"/>
+      <c r="J1745">
+        <v>0</v>
+      </c>
       <c r="K1745" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1746" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1746" s="2"/>
+      <c r="I1746" s="1"/>
+      <c r="K1746" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="1746" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1746" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1746">
-        <v>2659</v>
-      </c>
-      <c r="D1746" t="s">
-        <v>126</v>
-      </c>
-      <c r="F1746" t="s">
-        <v>218</v>
-      </c>
-      <c r="G1746" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1746" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1746" s="1">
-        <v>46122.601157407407</v>
-      </c>
-      <c r="J1746">
-        <v>1</v>
-      </c>
-      <c r="K1746" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1747" spans="2:11" x14ac:dyDescent="0.25">
@@ -49839,10 +49817,10 @@
         <v>21</v>
       </c>
       <c r="C1747">
-        <v>5142</v>
+        <v>2659</v>
       </c>
       <c r="D1747" t="s">
-        <v>209</v>
+        <v>126</v>
       </c>
       <c r="F1747" t="s">
         <v>218</v>
@@ -49851,13 +49829,13 @@
         <v>10</v>
       </c>
       <c r="H1747" s="2">
-        <v>1.5625000000000001E-3</v>
+        <v>7.905092592592592E-3</v>
       </c>
       <c r="I1747" s="1">
-        <v>46122.601851851854</v>
+        <v>46122.601157407407</v>
       </c>
       <c r="J1747">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1747" t="s">
         <v>11</v>
@@ -49868,10 +49846,10 @@
         <v>21</v>
       </c>
       <c r="C1748">
-        <v>1572</v>
+        <v>5142</v>
       </c>
       <c r="D1748" t="s">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="F1748" t="s">
         <v>218</v>
@@ -49880,7 +49858,7 @@
         <v>10</v>
       </c>
       <c r="H1748" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>1.5625000000000001E-3</v>
       </c>
       <c r="I1748" s="1">
         <v>46122.601851851854</v>
@@ -49897,25 +49875,25 @@
         <v>21</v>
       </c>
       <c r="C1749">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="D1749" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F1749" t="s">
         <v>218</v>
       </c>
       <c r="G1749" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1749" s="2">
-        <v>0</v>
+        <v>7.8009259259259256E-3</v>
       </c>
       <c r="I1749" s="1">
-        <v>46122.602546296293</v>
+        <v>46122.601851851854</v>
       </c>
       <c r="J1749">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1749" t="s">
         <v>11</v>
@@ -49926,22 +49904,22 @@
         <v>21</v>
       </c>
       <c r="C1750">
-        <v>2867</v>
+        <v>1571</v>
       </c>
       <c r="D1750" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="F1750" t="s">
         <v>218</v>
       </c>
       <c r="G1750" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1750" s="2">
-        <v>0</v>
+        <v>8.1712962962962963E-3</v>
       </c>
       <c r="I1750" s="1">
-        <v>46122.60324074074</v>
+        <v>46122.602546296293</v>
       </c>
       <c r="J1750">
         <v>1</v>
@@ -49955,10 +49933,10 @@
         <v>21</v>
       </c>
       <c r="C1751">
-        <v>4797</v>
+        <v>2867</v>
       </c>
       <c r="D1751" t="s">
-        <v>197</v>
+        <v>131</v>
       </c>
       <c r="F1751" t="s">
         <v>218</v>
@@ -49967,13 +49945,13 @@
         <v>10</v>
       </c>
       <c r="H1751" s="2">
-        <v>7.7314814814814815E-3</v>
+        <v>9.5138888888888894E-3</v>
       </c>
       <c r="I1751" s="1">
         <v>46122.60324074074</v>
       </c>
       <c r="J1751">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1751" t="s">
         <v>11</v>
@@ -49984,64 +49962,64 @@
         <v>21</v>
       </c>
       <c r="C1752">
-        <v>5410</v>
+        <v>4797</v>
       </c>
       <c r="D1752" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="F1752" t="s">
         <v>218</v>
       </c>
       <c r="G1752" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1752" s="2">
+        <v>7.7314814814814815E-3</v>
+      </c>
+      <c r="I1752" s="1">
+        <v>46122.60324074074</v>
+      </c>
+      <c r="J1752">
+        <v>0</v>
+      </c>
+      <c r="K1752" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1753" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1753" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1753">
+        <v>5410</v>
+      </c>
+      <c r="D1753" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1753" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1753" t="s">
         <v>34</v>
       </c>
-      <c r="H1752" s="2">
+      <c r="H1753" s="2">
         <v>2.1145833333333332E-2</v>
       </c>
-      <c r="I1752" s="1">
+      <c r="I1753" s="1">
         <v>46122.603935185187</v>
       </c>
-      <c r="J1752">
-        <v>0</v>
-      </c>
-      <c r="K1752" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1753" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1753" s="2"/>
-      <c r="I1753" s="1"/>
+      <c r="J1753">
+        <v>0</v>
+      </c>
       <c r="K1753" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1754" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1754" s="2"/>
+      <c r="I1754" s="1"/>
+      <c r="K1754" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="1754" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1754" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1754">
-        <v>1596</v>
-      </c>
-      <c r="D1754" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1754" t="s">
-        <v>218</v>
-      </c>
-      <c r="G1754" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1754" s="2">
-        <v>9.0162037037037034E-3</v>
-      </c>
-      <c r="I1754" s="1">
-        <v>46122.585300925923</v>
-      </c>
-      <c r="J1754">
-        <v>0</v>
-      </c>
-      <c r="K1754" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1755" spans="2:11" x14ac:dyDescent="0.25">
@@ -50049,25 +50027,25 @@
         <v>21</v>
       </c>
       <c r="C1755">
-        <v>5203</v>
+        <v>1596</v>
       </c>
       <c r="D1755" t="s">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="F1755" t="s">
         <v>218</v>
       </c>
       <c r="G1755" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1755" s="2">
-        <v>0</v>
+        <v>9.0162037037037034E-3</v>
       </c>
       <c r="I1755" s="1">
-        <v>46122.585995370369</v>
+        <v>46122.585300925923</v>
       </c>
       <c r="J1755">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1755" t="s">
         <v>11</v>
@@ -50078,10 +50056,10 @@
         <v>21</v>
       </c>
       <c r="C1756">
-        <v>5444</v>
+        <v>5203</v>
       </c>
       <c r="D1756" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="F1756" t="s">
         <v>218</v>
@@ -50093,10 +50071,10 @@
         <v>0</v>
       </c>
       <c r="I1756" s="1">
-        <v>46122.586689814816</v>
+        <v>46122.585995370369</v>
       </c>
       <c r="J1756">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1756" t="s">
         <v>11</v>
@@ -50107,16 +50085,16 @@
         <v>21</v>
       </c>
       <c r="C1757">
-        <v>5317</v>
+        <v>5444</v>
       </c>
       <c r="D1757" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F1757" t="s">
         <v>218</v>
       </c>
       <c r="G1757" t="s">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="H1757" s="2">
         <v>0</v>
@@ -50125,46 +50103,46 @@
         <v>46122.586689814816</v>
       </c>
       <c r="J1757">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1757" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1758" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1758" s="2"/>
-      <c r="I1758" s="1"/>
+      <c r="B1758" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1758">
+        <v>5317</v>
+      </c>
+      <c r="D1758" t="s">
+        <v>223</v>
+      </c>
+      <c r="F1758" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1758" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1758" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1758" s="1">
+        <v>46122.586689814816</v>
+      </c>
+      <c r="J1758">
+        <v>0</v>
+      </c>
       <c r="K1758" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1759" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1759" s="2"/>
+      <c r="I1759" s="1"/>
+      <c r="K1759" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="1759" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1759" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1759">
-        <v>5140</v>
-      </c>
-      <c r="D1759" t="s">
-        <v>210</v>
-      </c>
-      <c r="F1759" t="s">
-        <v>218</v>
-      </c>
-      <c r="G1759" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1759" s="2">
-        <v>7.6041666666666671E-3</v>
-      </c>
-      <c r="I1759" s="1">
-        <v>46122.587384259263</v>
-      </c>
-      <c r="J1759">
-        <v>0</v>
-      </c>
-      <c r="K1759" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1760" spans="2:11" x14ac:dyDescent="0.25">
@@ -50172,10 +50150,10 @@
         <v>21</v>
       </c>
       <c r="C1760">
-        <v>3841</v>
+        <v>5140</v>
       </c>
       <c r="D1760" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="F1760" t="s">
         <v>218</v>
@@ -50184,10 +50162,10 @@
         <v>10</v>
       </c>
       <c r="H1760" s="2">
-        <v>1.4398148148148148E-2</v>
+        <v>7.6041666666666671E-3</v>
       </c>
       <c r="I1760" s="1">
-        <v>46122.588078703702</v>
+        <v>46122.587384259263</v>
       </c>
       <c r="J1760">
         <v>0</v>
@@ -50201,10 +50179,10 @@
         <v>21</v>
       </c>
       <c r="C1761">
-        <v>3047</v>
+        <v>3841</v>
       </c>
       <c r="D1761" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F1761" t="s">
         <v>218</v>
@@ -50213,13 +50191,13 @@
         <v>10</v>
       </c>
       <c r="H1761" s="2">
-        <v>6.898148148148148E-3</v>
+        <v>1.4398148148148148E-2</v>
       </c>
       <c r="I1761" s="1">
         <v>46122.588078703702</v>
       </c>
       <c r="J1761">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1761" t="s">
         <v>11</v>
@@ -50230,10 +50208,10 @@
         <v>21</v>
       </c>
       <c r="C1762">
-        <v>1552</v>
+        <v>3047</v>
       </c>
       <c r="D1762" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="F1762" t="s">
         <v>218</v>
@@ -50242,13 +50220,13 @@
         <v>10</v>
       </c>
       <c r="H1762" s="2">
-        <v>8.0208333333333329E-3</v>
+        <v>6.898148148148148E-3</v>
       </c>
       <c r="I1762" s="1">
-        <v>46122.588773148149</v>
+        <v>46122.588078703702</v>
       </c>
       <c r="J1762">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1762" t="s">
         <v>11</v>
@@ -50259,25 +50237,25 @@
         <v>21</v>
       </c>
       <c r="C1763">
-        <v>1588</v>
+        <v>1552</v>
       </c>
       <c r="D1763" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F1763" t="s">
         <v>218</v>
       </c>
       <c r="G1763" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1763" s="2">
-        <v>0</v>
+        <v>8.0208333333333329E-3</v>
       </c>
       <c r="I1763" s="1">
         <v>46122.588773148149</v>
       </c>
       <c r="J1763">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1763" t="s">
         <v>11</v>
@@ -50288,25 +50266,25 @@
         <v>21</v>
       </c>
       <c r="C1764">
-        <v>5228</v>
+        <v>1588</v>
       </c>
       <c r="D1764" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="F1764" t="s">
         <v>218</v>
       </c>
       <c r="G1764" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1764" s="2">
-        <v>9.8148148148148144E-3</v>
+        <v>0</v>
       </c>
       <c r="I1764" s="1">
-        <v>46122.589467592596</v>
+        <v>46122.588773148149</v>
       </c>
       <c r="J1764">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1764" t="s">
         <v>11</v>
@@ -50317,10 +50295,10 @@
         <v>21</v>
       </c>
       <c r="C1765">
-        <v>3659</v>
+        <v>5228</v>
       </c>
       <c r="D1765" t="s">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="F1765" t="s">
         <v>218</v>
@@ -50329,7 +50307,7 @@
         <v>10</v>
       </c>
       <c r="H1765" s="2">
-        <v>8.3217592592592596E-3</v>
+        <v>9.8148148148148144E-3</v>
       </c>
       <c r="I1765" s="1">
         <v>46122.589467592596</v>
@@ -50346,25 +50324,25 @@
         <v>21</v>
       </c>
       <c r="C1766">
-        <v>1551</v>
+        <v>3659</v>
       </c>
       <c r="D1766" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="F1766" t="s">
         <v>218</v>
       </c>
       <c r="G1766" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1766" s="2">
-        <v>0</v>
+        <v>8.3217592592592596E-3</v>
       </c>
       <c r="I1766" s="1">
-        <v>46122.590162037035</v>
+        <v>46122.589467592596</v>
       </c>
       <c r="J1766">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1766" t="s">
         <v>11</v>
@@ -50375,25 +50353,25 @@
         <v>21</v>
       </c>
       <c r="C1767">
-        <v>1581</v>
+        <v>1551</v>
       </c>
       <c r="D1767" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F1767" t="s">
         <v>218</v>
       </c>
       <c r="G1767" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1767" s="2">
-        <v>7.4652777777777781E-3</v>
+        <v>0</v>
       </c>
       <c r="I1767" s="1">
-        <v>46122.590856481482</v>
+        <v>46122.590162037035</v>
       </c>
       <c r="J1767">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1767" t="s">
         <v>11</v>
@@ -50404,19 +50382,19 @@
         <v>21</v>
       </c>
       <c r="C1768">
-        <v>1545</v>
+        <v>1581</v>
       </c>
       <c r="D1768" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F1768" t="s">
         <v>218</v>
       </c>
       <c r="G1768" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1768" s="2">
-        <v>0</v>
+        <v>7.4652777777777781E-3</v>
       </c>
       <c r="I1768" s="1">
         <v>46122.590856481482</v>
@@ -50433,22 +50411,22 @@
         <v>21</v>
       </c>
       <c r="C1769">
-        <v>1604</v>
+        <v>1545</v>
       </c>
       <c r="D1769" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F1769" t="s">
         <v>218</v>
       </c>
       <c r="G1769" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1769" s="2">
-        <v>0</v>
+        <v>7.3495370370370372E-3</v>
       </c>
       <c r="I1769" s="1">
-        <v>46122.591550925928</v>
+        <v>46122.590856481482</v>
       </c>
       <c r="J1769">
         <v>1</v>
@@ -50462,10 +50440,10 @@
         <v>21</v>
       </c>
       <c r="C1770">
-        <v>4726</v>
+        <v>1604</v>
       </c>
       <c r="D1770" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="F1770" t="s">
         <v>218</v>
@@ -50474,13 +50452,13 @@
         <v>10</v>
       </c>
       <c r="H1770" s="2">
-        <v>1.6724537037037038E-2</v>
+        <v>1.579861111111111E-2</v>
       </c>
       <c r="I1770" s="1">
         <v>46122.591550925928</v>
       </c>
       <c r="J1770">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1770" t="s">
         <v>11</v>
@@ -50491,10 +50469,10 @@
         <v>21</v>
       </c>
       <c r="C1771">
-        <v>1540</v>
+        <v>4726</v>
       </c>
       <c r="D1771" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="F1771" t="s">
         <v>218</v>
@@ -50503,10 +50481,10 @@
         <v>10</v>
       </c>
       <c r="H1771" s="2">
-        <v>9.3518518518518525E-3</v>
+        <v>1.6724537037037038E-2</v>
       </c>
       <c r="I1771" s="1">
-        <v>46122.592245370368</v>
+        <v>46122.591550925928</v>
       </c>
       <c r="J1771">
         <v>1</v>
@@ -50520,10 +50498,10 @@
         <v>21</v>
       </c>
       <c r="C1772">
-        <v>1601</v>
+        <v>1540</v>
       </c>
       <c r="D1772" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F1772" t="s">
         <v>218</v>
@@ -50532,21 +50510,46 @@
         <v>10</v>
       </c>
       <c r="H1772" s="2">
+        <v>9.3518518518518525E-3</v>
+      </c>
+      <c r="I1772" s="1">
+        <v>46122.592245370368</v>
+      </c>
+      <c r="J1772">
+        <v>1</v>
+      </c>
+      <c r="K1772" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1773" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1773" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1773">
+        <v>1601</v>
+      </c>
+      <c r="D1773" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1773" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1773" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1773" s="2">
         <v>7.6157407407407406E-3</v>
       </c>
-      <c r="I1772" s="1">
+      <c r="I1773" s="1">
         <v>46122.592939814815</v>
       </c>
-      <c r="J1772">
-        <v>0</v>
-      </c>
-      <c r="K1772" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1773" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1773" s="2"/>
-      <c r="I1773" s="1"/>
+      <c r="J1773">
+        <v>0</v>
+      </c>
+      <c r="K1773" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1774" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1774" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Panhandle Express\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2BFB19-7FEB-4F83-AC2F-B9A10BA60465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E1B61A-E376-407D-931D-9A04BC6E4BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8538" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8814" uniqueCount="228">
   <si>
     <t>Company Name</t>
   </si>
@@ -712,6 +712,18 @@
   <si>
     <t>Matthew Licon</t>
   </si>
+  <si>
+    <t>Derek Spriggs</t>
+  </si>
+  <si>
+    <t>Jeremy Ochoa</t>
+  </si>
+  <si>
+    <t>Olegario Contreras</t>
+  </si>
+  <si>
+    <t>Omar Rodriguez</t>
+  </si>
 </sst>
 </file>
 
@@ -48684,25 +48696,25 @@
         <v>21</v>
       </c>
       <c r="C1705">
-        <v>4858</v>
+        <v>5411</v>
       </c>
       <c r="D1705" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="F1705" t="s">
         <v>218</v>
       </c>
       <c r="G1705" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1705" s="2">
-        <v>0</v>
+        <v>7.1875000000000003E-3</v>
       </c>
       <c r="I1705" s="1">
         <v>46122.587268518517</v>
       </c>
       <c r="J1705">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1705" t="s">
         <v>11</v>
@@ -48713,25 +48725,28 @@
         <v>21</v>
       </c>
       <c r="C1706">
-        <v>5411</v>
+        <v>1873</v>
       </c>
       <c r="D1706" t="s">
-        <v>219</v>
+        <v>107</v>
+      </c>
+      <c r="E1706" t="s">
+        <v>25</v>
       </c>
       <c r="F1706" t="s">
         <v>218</v>
       </c>
       <c r="G1706" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1706" s="2">
-        <v>0</v>
+        <v>1.5787037037037037E-2</v>
       </c>
       <c r="I1706" s="1">
-        <v>46122.587268518517</v>
+        <v>46122.587962962964</v>
       </c>
       <c r="J1706">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1706" t="s">
         <v>11</v>
@@ -48742,13 +48757,10 @@
         <v>21</v>
       </c>
       <c r="C1707">
-        <v>1873</v>
+        <v>3245</v>
       </c>
       <c r="D1707" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1707" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="F1707" t="s">
         <v>218</v>
@@ -48757,13 +48769,13 @@
         <v>10</v>
       </c>
       <c r="H1707" s="2">
-        <v>1.5787037037037037E-2</v>
+        <v>9.7916666666666673E-3</v>
       </c>
       <c r="I1707" s="1">
-        <v>46122.587962962964</v>
+        <v>46122.58865740741</v>
       </c>
       <c r="J1707">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1707" t="s">
         <v>11</v>
@@ -48774,10 +48786,10 @@
         <v>21</v>
       </c>
       <c r="C1708">
-        <v>3245</v>
+        <v>5443</v>
       </c>
       <c r="D1708" t="s">
-        <v>154</v>
+        <v>220</v>
       </c>
       <c r="F1708" t="s">
         <v>218</v>
@@ -48786,13 +48798,13 @@
         <v>10</v>
       </c>
       <c r="H1708" s="2">
-        <v>9.7916666666666673E-3</v>
+        <v>7.4421296296296293E-3</v>
       </c>
       <c r="I1708" s="1">
-        <v>46122.58865740741</v>
+        <v>46122.58935185185</v>
       </c>
       <c r="J1708">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1708" t="s">
         <v>11</v>
@@ -48803,25 +48815,25 @@
         <v>21</v>
       </c>
       <c r="C1709">
-        <v>4977</v>
+        <v>4769</v>
       </c>
       <c r="D1709" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F1709" t="s">
         <v>218</v>
       </c>
       <c r="G1709" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1709" s="2">
-        <v>0</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="I1709" s="1">
-        <v>46122.58865740741</v>
+        <v>46122.590046296296</v>
       </c>
       <c r="J1709">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1709" t="s">
         <v>11</v>
@@ -48832,25 +48844,25 @@
         <v>21</v>
       </c>
       <c r="C1710">
-        <v>5443</v>
+        <v>3800</v>
       </c>
       <c r="D1710" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="F1710" t="s">
         <v>218</v>
       </c>
       <c r="G1710" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1710" s="2">
-        <v>0</v>
+        <v>8.4490740740740741E-3</v>
       </c>
       <c r="I1710" s="1">
-        <v>46122.58935185185</v>
+        <v>46122.590046296296</v>
       </c>
       <c r="J1710">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1710" t="s">
         <v>11</v>
@@ -48861,22 +48873,22 @@
         <v>21</v>
       </c>
       <c r="C1711">
-        <v>3802</v>
+        <v>1608</v>
       </c>
       <c r="D1711" t="s">
-        <v>170</v>
+        <v>39</v>
       </c>
       <c r="F1711" t="s">
         <v>218</v>
       </c>
       <c r="G1711" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1711" s="2">
-        <v>0</v>
+        <v>6.8865740740740745E-3</v>
       </c>
       <c r="I1711" s="1">
-        <v>46122.58935185185</v>
+        <v>46122.590740740743</v>
       </c>
       <c r="J1711">
         <v>2</v>
@@ -48890,10 +48902,10 @@
         <v>21</v>
       </c>
       <c r="C1712">
-        <v>4769</v>
+        <v>3185</v>
       </c>
       <c r="D1712" t="s">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="F1712" t="s">
         <v>218</v>
@@ -48902,10 +48914,10 @@
         <v>10</v>
       </c>
       <c r="H1712" s="2">
-        <v>7.4999999999999997E-3</v>
+        <v>6.3541666666666668E-3</v>
       </c>
       <c r="I1712" s="1">
-        <v>46122.590046296296</v>
+        <v>46122.590740740743</v>
       </c>
       <c r="J1712">
         <v>0</v>
@@ -48919,10 +48931,10 @@
         <v>21</v>
       </c>
       <c r="C1713">
-        <v>3800</v>
+        <v>1556</v>
       </c>
       <c r="D1713" t="s">
-        <v>171</v>
+        <v>40</v>
       </c>
       <c r="F1713" t="s">
         <v>218</v>
@@ -48931,13 +48943,13 @@
         <v>10</v>
       </c>
       <c r="H1713" s="2">
-        <v>8.4490740740740741E-3</v>
+        <v>9.571759259259259E-3</v>
       </c>
       <c r="I1713" s="1">
-        <v>46122.590046296296</v>
+        <v>46122.591435185182</v>
       </c>
       <c r="J1713">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1713" t="s">
         <v>11</v>
@@ -48948,10 +48960,10 @@
         <v>21</v>
       </c>
       <c r="C1714">
-        <v>1608</v>
+        <v>5133</v>
       </c>
       <c r="D1714" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="F1714" t="s">
         <v>218</v>
@@ -48960,13 +48972,13 @@
         <v>10</v>
       </c>
       <c r="H1714" s="2">
-        <v>6.8865740740740745E-3</v>
+        <v>3.8425925925925928E-3</v>
       </c>
       <c r="I1714" s="1">
-        <v>46122.590740740743</v>
+        <v>46122.591435185182</v>
       </c>
       <c r="J1714">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1714" t="s">
         <v>11</v>
@@ -48977,10 +48989,10 @@
         <v>21</v>
       </c>
       <c r="C1715">
-        <v>3185</v>
+        <v>1579</v>
       </c>
       <c r="D1715" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="F1715" t="s">
         <v>218</v>
@@ -48989,13 +49001,13 @@
         <v>10</v>
       </c>
       <c r="H1715" s="2">
-        <v>6.3541666666666668E-3</v>
+        <v>8.6226851851851846E-3</v>
       </c>
       <c r="I1715" s="1">
-        <v>46122.590740740743</v>
+        <v>46122.592129629629</v>
       </c>
       <c r="J1715">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1715" t="s">
         <v>11</v>
@@ -49006,10 +49018,10 @@
         <v>21</v>
       </c>
       <c r="C1716">
-        <v>1556</v>
+        <v>1576</v>
       </c>
       <c r="D1716" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F1716" t="s">
         <v>218</v>
@@ -49018,13 +49030,13 @@
         <v>10</v>
       </c>
       <c r="H1716" s="2">
-        <v>9.571759259259259E-3</v>
+        <v>0</v>
       </c>
       <c r="I1716" s="1">
-        <v>46122.591435185182</v>
+        <v>46122.592824074076</v>
       </c>
       <c r="J1716">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1716" t="s">
         <v>11</v>
@@ -49035,35 +49047,57 @@
         <v>21</v>
       </c>
       <c r="C1717">
-        <v>5133</v>
+        <v>1549</v>
       </c>
       <c r="D1717" t="s">
-        <v>205</v>
+        <v>52</v>
       </c>
       <c r="F1717" t="s">
         <v>218</v>
       </c>
       <c r="G1717" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H1717" s="2">
-        <v>3.6574074074074074E-3</v>
+        <v>7.7777777777777776E-3</v>
       </c>
       <c r="I1717" s="1">
-        <v>46122.591435185182</v>
+        <v>46122.592824074076</v>
       </c>
       <c r="J1717">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1717" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1718" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1718" s="2"/>
-      <c r="I1718" s="1"/>
+      <c r="B1718" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1718">
+        <v>3188</v>
+      </c>
+      <c r="D1718" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1718" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1718" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1718" s="2">
+        <v>7.8240740740740736E-3</v>
+      </c>
+      <c r="I1718" s="1">
+        <v>46122.593518518515</v>
+      </c>
+      <c r="J1718">
+        <v>3</v>
+      </c>
       <c r="K1718" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1719" spans="2:11" x14ac:dyDescent="0.25">
@@ -49071,10 +49105,10 @@
         <v>21</v>
       </c>
       <c r="C1719">
-        <v>1579</v>
+        <v>3181</v>
       </c>
       <c r="D1719" t="s">
-        <v>48</v>
+        <v>146</v>
       </c>
       <c r="F1719" t="s">
         <v>218</v>
@@ -49083,10 +49117,10 @@
         <v>10</v>
       </c>
       <c r="H1719" s="2">
-        <v>8.6226851851851846E-3</v>
+        <v>7.2800925925925923E-3</v>
       </c>
       <c r="I1719" s="1">
-        <v>46122.592129629629</v>
+        <v>46122.593518518515</v>
       </c>
       <c r="J1719">
         <v>1</v>
@@ -49100,25 +49134,25 @@
         <v>21</v>
       </c>
       <c r="C1720">
-        <v>1576</v>
+        <v>2670</v>
       </c>
       <c r="D1720" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F1720" t="s">
         <v>218</v>
       </c>
       <c r="G1720" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1720" s="2">
-        <v>0</v>
+        <v>6.7245370370370367E-3</v>
       </c>
       <c r="I1720" s="1">
-        <v>46122.592824074076</v>
+        <v>46122.594212962962</v>
       </c>
       <c r="J1720">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1720" t="s">
         <v>11</v>
@@ -49129,10 +49163,10 @@
         <v>21</v>
       </c>
       <c r="C1721">
-        <v>1549</v>
+        <v>1592</v>
       </c>
       <c r="D1721" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F1721" t="s">
         <v>218</v>
@@ -49141,10 +49175,10 @@
         <v>10</v>
       </c>
       <c r="H1721" s="2">
-        <v>7.7777777777777776E-3</v>
+        <v>8.3333333333333332E-3</v>
       </c>
       <c r="I1721" s="1">
-        <v>46122.592824074076</v>
+        <v>46122.594212962962</v>
       </c>
       <c r="J1721">
         <v>0</v>
@@ -49158,22 +49192,22 @@
         <v>21</v>
       </c>
       <c r="C1722">
-        <v>3188</v>
+        <v>1561</v>
       </c>
       <c r="D1722" t="s">
-        <v>145</v>
+        <v>57</v>
       </c>
       <c r="F1722" t="s">
         <v>218</v>
       </c>
       <c r="G1722" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1722" s="2">
-        <v>0</v>
+        <v>3.0439814814814813E-3</v>
       </c>
       <c r="I1722" s="1">
-        <v>46122.593518518515</v>
+        <v>46122.594907407409</v>
       </c>
       <c r="J1722">
         <v>2</v>
@@ -49187,10 +49221,10 @@
         <v>21</v>
       </c>
       <c r="C1723">
-        <v>3181</v>
+        <v>3187</v>
       </c>
       <c r="D1723" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F1723" t="s">
         <v>218</v>
@@ -49199,13 +49233,13 @@
         <v>10</v>
       </c>
       <c r="H1723" s="2">
-        <v>7.2800925925925923E-3</v>
+        <v>9.2245370370370363E-3</v>
       </c>
       <c r="I1723" s="1">
-        <v>46122.593518518515</v>
+        <v>46122.594907407409</v>
       </c>
       <c r="J1723">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1723" t="s">
         <v>11</v>
@@ -49216,10 +49250,10 @@
         <v>21</v>
       </c>
       <c r="C1724">
-        <v>2670</v>
+        <v>1597</v>
       </c>
       <c r="D1724" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="F1724" t="s">
         <v>218</v>
@@ -49228,13 +49262,13 @@
         <v>10</v>
       </c>
       <c r="H1724" s="2">
-        <v>6.7245370370370367E-3</v>
+        <v>1.2847222222222222E-2</v>
       </c>
       <c r="I1724" s="1">
-        <v>46122.594212962962</v>
+        <v>46122.595601851855</v>
       </c>
       <c r="J1724">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1724" t="s">
         <v>11</v>
@@ -49245,10 +49279,10 @@
         <v>21</v>
       </c>
       <c r="C1725">
-        <v>1592</v>
+        <v>1569</v>
       </c>
       <c r="D1725" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F1725" t="s">
         <v>218</v>
@@ -49257,10 +49291,10 @@
         <v>10</v>
       </c>
       <c r="H1725" s="2">
-        <v>8.3333333333333332E-3</v>
+        <v>8.4953703703703701E-3</v>
       </c>
       <c r="I1725" s="1">
-        <v>46122.594212962962</v>
+        <v>46122.595601851855</v>
       </c>
       <c r="J1725">
         <v>0</v>
@@ -49274,10 +49308,10 @@
         <v>21</v>
       </c>
       <c r="C1726">
-        <v>1561</v>
+        <v>1538</v>
       </c>
       <c r="D1726" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F1726" t="s">
         <v>218</v>
@@ -49286,13 +49320,13 @@
         <v>10</v>
       </c>
       <c r="H1726" s="2">
-        <v>3.0439814814814813E-3</v>
+        <v>8.3449074074074068E-3</v>
       </c>
       <c r="I1726" s="1">
-        <v>46122.594907407409</v>
+        <v>46122.596990740742</v>
       </c>
       <c r="J1726">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1726" t="s">
         <v>11</v>
@@ -49303,10 +49337,10 @@
         <v>21</v>
       </c>
       <c r="C1727">
-        <v>3187</v>
+        <v>1598</v>
       </c>
       <c r="D1727" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="F1727" t="s">
         <v>218</v>
@@ -49315,13 +49349,13 @@
         <v>10</v>
       </c>
       <c r="H1727" s="2">
-        <v>9.2245370370370363E-3</v>
+        <v>6.7708333333333336E-3</v>
       </c>
       <c r="I1727" s="1">
-        <v>46122.594907407409</v>
+        <v>46122.596990740742</v>
       </c>
       <c r="J1727">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1727" t="s">
         <v>11</v>
@@ -49332,25 +49366,25 @@
         <v>21</v>
       </c>
       <c r="C1728">
-        <v>1597</v>
+        <v>3182</v>
       </c>
       <c r="D1728" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="F1728" t="s">
         <v>218</v>
       </c>
       <c r="G1728" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1728" s="2">
-        <v>0</v>
+        <v>8.9467592592592585E-3</v>
       </c>
       <c r="I1728" s="1">
-        <v>46122.595601851855</v>
+        <v>46122.596990740742</v>
       </c>
       <c r="J1728">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1728" t="s">
         <v>11</v>
@@ -49361,10 +49395,10 @@
         <v>21</v>
       </c>
       <c r="C1729">
-        <v>1569</v>
+        <v>1553</v>
       </c>
       <c r="D1729" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F1729" t="s">
         <v>218</v>
@@ -49373,13 +49407,13 @@
         <v>10</v>
       </c>
       <c r="H1729" s="2">
-        <v>8.4953703703703701E-3</v>
+        <v>3.7152777777777778E-2</v>
       </c>
       <c r="I1729" s="1">
-        <v>46122.595601851855</v>
+        <v>46122.597685185188</v>
       </c>
       <c r="J1729">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1729" t="s">
         <v>11</v>
@@ -49390,22 +49424,22 @@
         <v>21</v>
       </c>
       <c r="C1730">
-        <v>5181</v>
+        <v>3803</v>
       </c>
       <c r="D1730" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="F1730" t="s">
         <v>218</v>
       </c>
       <c r="G1730" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H1730" s="2">
-        <v>1.0416666666666667E-4</v>
+        <v>7.5925925925925926E-3</v>
       </c>
       <c r="I1730" s="1">
-        <v>46122.596296296295</v>
+        <v>46122.597685185188</v>
       </c>
       <c r="J1730">
         <v>0</v>
@@ -49415,10 +49449,32 @@
       </c>
     </row>
     <row r="1731" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1731" s="2"/>
-      <c r="I1731" s="1"/>
+      <c r="B1731" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1731">
+        <v>4635</v>
+      </c>
+      <c r="D1731" t="s">
+        <v>187</v>
+      </c>
+      <c r="F1731" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1731" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1731" s="2">
+        <v>7.789351851851852E-3</v>
+      </c>
+      <c r="I1731" s="1">
+        <v>46122.598379629628</v>
+      </c>
+      <c r="J1731">
+        <v>0</v>
+      </c>
       <c r="K1731" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1732" spans="2:11" x14ac:dyDescent="0.25">
@@ -49426,10 +49482,10 @@
         <v>21</v>
       </c>
       <c r="C1732">
-        <v>1538</v>
+        <v>4825</v>
       </c>
       <c r="D1732" t="s">
-        <v>61</v>
+        <v>195</v>
       </c>
       <c r="F1732" t="s">
         <v>218</v>
@@ -49438,13 +49494,13 @@
         <v>10</v>
       </c>
       <c r="H1732" s="2">
-        <v>8.3449074074074068E-3</v>
+        <v>6.6550925925925927E-3</v>
       </c>
       <c r="I1732" s="1">
-        <v>46122.596990740742</v>
+        <v>46122.599074074074</v>
       </c>
       <c r="J1732">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1732" t="s">
         <v>11</v>
@@ -49455,10 +49511,10 @@
         <v>21</v>
       </c>
       <c r="C1733">
-        <v>1598</v>
+        <v>1578</v>
       </c>
       <c r="D1733" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F1733" t="s">
         <v>218</v>
@@ -49467,13 +49523,13 @@
         <v>10</v>
       </c>
       <c r="H1733" s="2">
-        <v>6.7708333333333336E-3</v>
+        <v>7.9745370370370369E-3</v>
       </c>
       <c r="I1733" s="1">
-        <v>46122.596990740742</v>
+        <v>46122.599074074074</v>
       </c>
       <c r="J1733">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1733" t="s">
         <v>11</v>
@@ -49484,10 +49540,10 @@
         <v>21</v>
       </c>
       <c r="C1734">
-        <v>3182</v>
+        <v>1599</v>
       </c>
       <c r="D1734" t="s">
-        <v>147</v>
+        <v>67</v>
       </c>
       <c r="F1734" t="s">
         <v>218</v>
@@ -49496,10 +49552,10 @@
         <v>10</v>
       </c>
       <c r="H1734" s="2">
-        <v>8.9467592592592585E-3</v>
+        <v>9.2939814814814812E-3</v>
       </c>
       <c r="I1734" s="1">
-        <v>46122.596990740742</v>
+        <v>46122.599768518521</v>
       </c>
       <c r="J1734">
         <v>1</v>
@@ -49513,25 +49569,25 @@
         <v>21</v>
       </c>
       <c r="C1735">
-        <v>1553</v>
+        <v>5144</v>
       </c>
       <c r="D1735" t="s">
-        <v>65</v>
+        <v>208</v>
       </c>
       <c r="F1735" t="s">
         <v>218</v>
       </c>
       <c r="G1735" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1735" s="2">
-        <v>0</v>
+        <v>7.6851851851851855E-3</v>
       </c>
       <c r="I1735" s="1">
-        <v>46122.597685185188</v>
+        <v>46122.600462962961</v>
       </c>
       <c r="J1735">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1735" t="s">
         <v>11</v>
@@ -49542,10 +49598,10 @@
         <v>21</v>
       </c>
       <c r="C1736">
-        <v>3803</v>
+        <v>1555</v>
       </c>
       <c r="D1736" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="F1736" t="s">
         <v>218</v>
@@ -49554,10 +49610,10 @@
         <v>10</v>
       </c>
       <c r="H1736" s="2">
-        <v>7.5925925925925926E-3</v>
+        <v>7.1990740740740739E-3</v>
       </c>
       <c r="I1736" s="1">
-        <v>46122.597685185188</v>
+        <v>46122.600462962961</v>
       </c>
       <c r="J1736">
         <v>0</v>
@@ -49571,10 +49627,10 @@
         <v>21</v>
       </c>
       <c r="C1737">
-        <v>4635</v>
+        <v>2659</v>
       </c>
       <c r="D1737" t="s">
-        <v>187</v>
+        <v>126</v>
       </c>
       <c r="F1737" t="s">
         <v>218</v>
@@ -49583,13 +49639,13 @@
         <v>10</v>
       </c>
       <c r="H1737" s="2">
-        <v>7.789351851851852E-3</v>
+        <v>7.905092592592592E-3</v>
       </c>
       <c r="I1737" s="1">
-        <v>46122.598379629628</v>
+        <v>46122.601157407407</v>
       </c>
       <c r="J1737">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1737" t="s">
         <v>11</v>
@@ -49600,25 +49656,25 @@
         <v>21</v>
       </c>
       <c r="C1738">
-        <v>5143</v>
+        <v>5142</v>
       </c>
       <c r="D1738" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F1738" t="s">
         <v>218</v>
       </c>
       <c r="G1738" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1738" s="2">
-        <v>0</v>
+        <v>1.5625000000000001E-3</v>
       </c>
       <c r="I1738" s="1">
-        <v>46122.598379629628</v>
+        <v>46122.601851851854</v>
       </c>
       <c r="J1738">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1738" t="s">
         <v>11</v>
@@ -49629,10 +49685,10 @@
         <v>21</v>
       </c>
       <c r="C1739">
-        <v>4825</v>
+        <v>1572</v>
       </c>
       <c r="D1739" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="F1739" t="s">
         <v>218</v>
@@ -49641,13 +49697,13 @@
         <v>10</v>
       </c>
       <c r="H1739" s="2">
-        <v>6.6550925925925927E-3</v>
+        <v>7.8009259259259256E-3</v>
       </c>
       <c r="I1739" s="1">
-        <v>46122.599074074074</v>
+        <v>46122.601851851854</v>
       </c>
       <c r="J1739">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1739" t="s">
         <v>11</v>
@@ -49658,35 +49714,57 @@
         <v>21</v>
       </c>
       <c r="C1740">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="D1740" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F1740" t="s">
         <v>218</v>
       </c>
       <c r="G1740" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H1740" s="2">
-        <v>1.7361111111111112E-4</v>
+        <v>8.1712962962962963E-3</v>
       </c>
       <c r="I1740" s="1">
-        <v>46122.599074074074</v>
+        <v>46122.602546296293</v>
       </c>
       <c r="J1740">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1740" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1741" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1741" s="2"/>
-      <c r="I1741" s="1"/>
+      <c r="B1741" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1741">
+        <v>2867</v>
+      </c>
+      <c r="D1741" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1741" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1741" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1741" s="2">
+        <v>9.5138888888888894E-3</v>
+      </c>
+      <c r="I1741" s="1">
+        <v>46122.60324074074</v>
+      </c>
+      <c r="J1741">
+        <v>2</v>
+      </c>
       <c r="K1741" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1742" spans="2:11" x14ac:dyDescent="0.25">
@@ -49694,10 +49772,10 @@
         <v>21</v>
       </c>
       <c r="C1742">
-        <v>1599</v>
+        <v>4797</v>
       </c>
       <c r="D1742" t="s">
-        <v>67</v>
+        <v>197</v>
       </c>
       <c r="F1742" t="s">
         <v>218</v>
@@ -49706,13 +49784,13 @@
         <v>10</v>
       </c>
       <c r="H1742" s="2">
-        <v>9.2939814814814812E-3</v>
+        <v>7.7314814814814815E-3</v>
       </c>
       <c r="I1742" s="1">
-        <v>46122.599768518521</v>
+        <v>46122.60324074074</v>
       </c>
       <c r="J1742">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1742" t="s">
         <v>11</v>
@@ -49723,10 +49801,10 @@
         <v>21</v>
       </c>
       <c r="C1743">
-        <v>5144</v>
+        <v>5410</v>
       </c>
       <c r="D1743" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="F1743" t="s">
         <v>218</v>
@@ -49735,10 +49813,10 @@
         <v>10</v>
       </c>
       <c r="H1743" s="2">
-        <v>7.6851851851851855E-3</v>
+        <v>2.1145833333333332E-2</v>
       </c>
       <c r="I1743" s="1">
-        <v>46122.600462962961</v>
+        <v>46122.603935185187</v>
       </c>
       <c r="J1743">
         <v>0</v>
@@ -49752,10 +49830,10 @@
         <v>21</v>
       </c>
       <c r="C1744">
-        <v>1555</v>
+        <v>1596</v>
       </c>
       <c r="D1744" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F1744" t="s">
         <v>218</v>
@@ -49764,10 +49842,10 @@
         <v>10</v>
       </c>
       <c r="H1744" s="2">
-        <v>7.1990740740740739E-3</v>
+        <v>9.0162037037037034E-3</v>
       </c>
       <c r="I1744" s="1">
-        <v>46122.600462962961</v>
+        <v>46122.585300925923</v>
       </c>
       <c r="J1744">
         <v>0</v>
@@ -49781,35 +49859,57 @@
         <v>21</v>
       </c>
       <c r="C1745">
-        <v>5269</v>
+        <v>5203</v>
       </c>
       <c r="D1745" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F1745" t="s">
         <v>218</v>
       </c>
       <c r="G1745" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H1745" s="2">
-        <v>8.1018518518518516E-5</v>
+        <v>8.8773148148148153E-3</v>
       </c>
       <c r="I1745" s="1">
-        <v>46122.601157407407</v>
+        <v>46122.585995370369</v>
       </c>
       <c r="J1745">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1745" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1746" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1746" s="2"/>
-      <c r="I1746" s="1"/>
+      <c r="B1746" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1746">
+        <v>5444</v>
+      </c>
+      <c r="D1746" t="s">
+        <v>222</v>
+      </c>
+      <c r="F1746" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1746" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1746" s="2">
+        <v>8.4490740740740741E-3</v>
+      </c>
+      <c r="I1746" s="1">
+        <v>46122.586689814816</v>
+      </c>
+      <c r="J1746">
+        <v>3</v>
+      </c>
       <c r="K1746" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1747" spans="2:11" x14ac:dyDescent="0.25">
@@ -49817,10 +49917,10 @@
         <v>21</v>
       </c>
       <c r="C1747">
-        <v>2659</v>
+        <v>5317</v>
       </c>
       <c r="D1747" t="s">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="F1747" t="s">
         <v>218</v>
@@ -49829,13 +49929,13 @@
         <v>10</v>
       </c>
       <c r="H1747" s="2">
-        <v>7.905092592592592E-3</v>
+        <v>2.650462962962963E-3</v>
       </c>
       <c r="I1747" s="1">
-        <v>46122.601157407407</v>
+        <v>46122.586689814816</v>
       </c>
       <c r="J1747">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1747" t="s">
         <v>11</v>
@@ -49846,10 +49946,10 @@
         <v>21</v>
       </c>
       <c r="C1748">
-        <v>5142</v>
+        <v>5140</v>
       </c>
       <c r="D1748" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F1748" t="s">
         <v>218</v>
@@ -49858,10 +49958,10 @@
         <v>10</v>
       </c>
       <c r="H1748" s="2">
-        <v>1.5625000000000001E-3</v>
+        <v>7.6041666666666671E-3</v>
       </c>
       <c r="I1748" s="1">
-        <v>46122.601851851854</v>
+        <v>46122.587384259263</v>
       </c>
       <c r="J1748">
         <v>0</v>
@@ -49875,10 +49975,10 @@
         <v>21</v>
       </c>
       <c r="C1749">
-        <v>1572</v>
+        <v>3841</v>
       </c>
       <c r="D1749" t="s">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="F1749" t="s">
         <v>218</v>
@@ -49887,10 +49987,10 @@
         <v>10</v>
       </c>
       <c r="H1749" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>1.4398148148148148E-2</v>
       </c>
       <c r="I1749" s="1">
-        <v>46122.601851851854</v>
+        <v>46122.588078703702</v>
       </c>
       <c r="J1749">
         <v>0</v>
@@ -49904,10 +50004,10 @@
         <v>21</v>
       </c>
       <c r="C1750">
-        <v>1571</v>
+        <v>3047</v>
       </c>
       <c r="D1750" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="F1750" t="s">
         <v>218</v>
@@ -49916,10 +50016,10 @@
         <v>10</v>
       </c>
       <c r="H1750" s="2">
-        <v>8.1712962962962963E-3</v>
+        <v>6.898148148148148E-3</v>
       </c>
       <c r="I1750" s="1">
-        <v>46122.602546296293</v>
+        <v>46122.588078703702</v>
       </c>
       <c r="J1750">
         <v>1</v>
@@ -49933,10 +50033,10 @@
         <v>21</v>
       </c>
       <c r="C1751">
-        <v>2867</v>
+        <v>1552</v>
       </c>
       <c r="D1751" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="F1751" t="s">
         <v>218</v>
@@ -49945,13 +50045,13 @@
         <v>10</v>
       </c>
       <c r="H1751" s="2">
-        <v>9.5138888888888894E-3</v>
+        <v>8.0208333333333329E-3</v>
       </c>
       <c r="I1751" s="1">
-        <v>46122.60324074074</v>
+        <v>46122.588773148149</v>
       </c>
       <c r="J1751">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1751" t="s">
         <v>11</v>
@@ -49962,10 +50062,10 @@
         <v>21</v>
       </c>
       <c r="C1752">
-        <v>4797</v>
+        <v>1588</v>
       </c>
       <c r="D1752" t="s">
-        <v>197</v>
+        <v>89</v>
       </c>
       <c r="F1752" t="s">
         <v>218</v>
@@ -49974,13 +50074,13 @@
         <v>10</v>
       </c>
       <c r="H1752" s="2">
-        <v>7.7314814814814815E-3</v>
+        <v>8.6226851851851846E-3</v>
       </c>
       <c r="I1752" s="1">
-        <v>46122.60324074074</v>
+        <v>46122.588773148149</v>
       </c>
       <c r="J1752">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1752" t="s">
         <v>11</v>
@@ -49991,22 +50091,22 @@
         <v>21</v>
       </c>
       <c r="C1753">
-        <v>5410</v>
+        <v>5228</v>
       </c>
       <c r="D1753" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F1753" t="s">
         <v>218</v>
       </c>
       <c r="G1753" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H1753" s="2">
-        <v>2.1145833333333332E-2</v>
+        <v>9.8148148148148144E-3</v>
       </c>
       <c r="I1753" s="1">
-        <v>46122.603935185187</v>
+        <v>46122.589467592596</v>
       </c>
       <c r="J1753">
         <v>0</v>
@@ -50016,10 +50116,32 @@
       </c>
     </row>
     <row r="1754" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1754" s="2"/>
-      <c r="I1754" s="1"/>
+      <c r="B1754" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1754">
+        <v>3659</v>
+      </c>
+      <c r="D1754" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1754" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1754" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1754" s="2">
+        <v>8.3217592592592596E-3</v>
+      </c>
+      <c r="I1754" s="1">
+        <v>46122.589467592596</v>
+      </c>
+      <c r="J1754">
+        <v>0</v>
+      </c>
       <c r="K1754" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1755" spans="2:11" x14ac:dyDescent="0.25">
@@ -50027,10 +50149,10 @@
         <v>21</v>
       </c>
       <c r="C1755">
-        <v>1596</v>
+        <v>1551</v>
       </c>
       <c r="D1755" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="F1755" t="s">
         <v>218</v>
@@ -50039,13 +50161,13 @@
         <v>10</v>
       </c>
       <c r="H1755" s="2">
-        <v>9.0162037037037034E-3</v>
+        <v>9.4560185185185181E-3</v>
       </c>
       <c r="I1755" s="1">
-        <v>46122.585300925923</v>
+        <v>46122.590162037035</v>
       </c>
       <c r="J1755">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1755" t="s">
         <v>11</v>
@@ -50056,25 +50178,25 @@
         <v>21</v>
       </c>
       <c r="C1756">
-        <v>5203</v>
+        <v>1581</v>
       </c>
       <c r="D1756" t="s">
-        <v>213</v>
+        <v>93</v>
       </c>
       <c r="F1756" t="s">
         <v>218</v>
       </c>
       <c r="G1756" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1756" s="2">
-        <v>0</v>
+        <v>7.4652777777777781E-3</v>
       </c>
       <c r="I1756" s="1">
-        <v>46122.585995370369</v>
+        <v>46122.590856481482</v>
       </c>
       <c r="J1756">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1756" t="s">
         <v>11</v>
@@ -50085,25 +50207,25 @@
         <v>21</v>
       </c>
       <c r="C1757">
-        <v>5444</v>
+        <v>1545</v>
       </c>
       <c r="D1757" t="s">
-        <v>222</v>
+        <v>94</v>
       </c>
       <c r="F1757" t="s">
         <v>218</v>
       </c>
       <c r="G1757" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1757" s="2">
-        <v>0</v>
+        <v>7.3495370370370372E-3</v>
       </c>
       <c r="I1757" s="1">
-        <v>46122.586689814816</v>
+        <v>46122.590856481482</v>
       </c>
       <c r="J1757">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1757" t="s">
         <v>11</v>
@@ -50114,35 +50236,57 @@
         <v>21</v>
       </c>
       <c r="C1758">
-        <v>5317</v>
+        <v>1604</v>
       </c>
       <c r="D1758" t="s">
-        <v>223</v>
+        <v>96</v>
       </c>
       <c r="F1758" t="s">
         <v>218</v>
       </c>
       <c r="G1758" t="s">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="H1758" s="2">
-        <v>0</v>
+        <v>1.579861111111111E-2</v>
       </c>
       <c r="I1758" s="1">
-        <v>46122.586689814816</v>
+        <v>46122.591550925928</v>
       </c>
       <c r="J1758">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1758" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1759" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1759" s="2"/>
-      <c r="I1759" s="1"/>
+      <c r="B1759" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1759">
+        <v>4726</v>
+      </c>
+      <c r="D1759" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1759" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1759" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1759" s="2">
+        <v>1.6724537037037038E-2</v>
+      </c>
+      <c r="I1759" s="1">
+        <v>46122.591550925928</v>
+      </c>
+      <c r="J1759">
+        <v>1</v>
+      </c>
       <c r="K1759" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1760" spans="2:11" x14ac:dyDescent="0.25">
@@ -50150,10 +50294,10 @@
         <v>21</v>
       </c>
       <c r="C1760">
-        <v>5140</v>
+        <v>1540</v>
       </c>
       <c r="D1760" t="s">
-        <v>210</v>
+        <v>97</v>
       </c>
       <c r="F1760" t="s">
         <v>218</v>
@@ -50162,13 +50306,13 @@
         <v>10</v>
       </c>
       <c r="H1760" s="2">
-        <v>7.6041666666666671E-3</v>
+        <v>9.3518518518518525E-3</v>
       </c>
       <c r="I1760" s="1">
-        <v>46122.587384259263</v>
+        <v>46122.592245370368</v>
       </c>
       <c r="J1760">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1760" t="s">
         <v>11</v>
@@ -50179,10 +50323,10 @@
         <v>21</v>
       </c>
       <c r="C1761">
-        <v>3841</v>
+        <v>1601</v>
       </c>
       <c r="D1761" t="s">
-        <v>184</v>
+        <v>100</v>
       </c>
       <c r="F1761" t="s">
         <v>218</v>
@@ -50191,10 +50335,10 @@
         <v>10</v>
       </c>
       <c r="H1761" s="2">
-        <v>1.4398148148148148E-2</v>
+        <v>7.6157407407407406E-3</v>
       </c>
       <c r="I1761" s="1">
-        <v>46122.588078703702</v>
+        <v>46122.592939814815</v>
       </c>
       <c r="J1761">
         <v>0</v>
@@ -50208,25 +50352,25 @@
         <v>21</v>
       </c>
       <c r="C1762">
-        <v>3047</v>
+        <v>4858</v>
       </c>
       <c r="D1762" t="s">
-        <v>141</v>
+        <v>194</v>
       </c>
       <c r="F1762" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="G1762" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1762" s="2">
-        <v>6.898148148148148E-3</v>
+        <v>0</v>
       </c>
       <c r="I1762" s="1">
-        <v>46122.588078703702</v>
+        <v>46146.67696759259</v>
       </c>
       <c r="J1762">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1762" t="s">
         <v>11</v>
@@ -50237,22 +50381,22 @@
         <v>21</v>
       </c>
       <c r="C1763">
-        <v>1552</v>
+        <v>5411</v>
       </c>
       <c r="D1763" t="s">
-        <v>87</v>
+        <v>219</v>
       </c>
       <c r="F1763" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="G1763" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1763" s="2">
-        <v>8.0208333333333329E-3</v>
+        <v>0</v>
       </c>
       <c r="I1763" s="1">
-        <v>46122.588773148149</v>
+        <v>46146.67696759259</v>
       </c>
       <c r="J1763">
         <v>0</v>
@@ -50266,13 +50410,16 @@
         <v>21</v>
       </c>
       <c r="C1764">
-        <v>1588</v>
+        <v>1873</v>
       </c>
       <c r="D1764" t="s">
-        <v>89</v>
+        <v>107</v>
+      </c>
+      <c r="E1764" t="s">
+        <v>25</v>
       </c>
       <c r="F1764" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="G1764" t="s">
         <v>12</v>
@@ -50281,10 +50428,10 @@
         <v>0</v>
       </c>
       <c r="I1764" s="1">
-        <v>46122.588773148149</v>
+        <v>46146.677662037036</v>
       </c>
       <c r="J1764">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1764" t="s">
         <v>11</v>
@@ -50295,22 +50442,22 @@
         <v>21</v>
       </c>
       <c r="C1765">
-        <v>5228</v>
+        <v>3245</v>
       </c>
       <c r="D1765" t="s">
-        <v>214</v>
+        <v>154</v>
       </c>
       <c r="F1765" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="G1765" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1765" s="2">
-        <v>9.8148148148148144E-3</v>
+        <v>0</v>
       </c>
       <c r="I1765" s="1">
-        <v>46122.589467592596</v>
+        <v>46146.678356481483</v>
       </c>
       <c r="J1765">
         <v>0</v>
@@ -50324,22 +50471,22 @@
         <v>21</v>
       </c>
       <c r="C1766">
-        <v>3659</v>
+        <v>5443</v>
       </c>
       <c r="D1766" t="s">
-        <v>166</v>
+        <v>220</v>
       </c>
       <c r="F1766" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="G1766" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1766" s="2">
-        <v>8.3217592592592596E-3</v>
+        <v>0</v>
       </c>
       <c r="I1766" s="1">
-        <v>46122.589467592596</v>
+        <v>46146.678356481483</v>
       </c>
       <c r="J1766">
         <v>0</v>
@@ -50353,13 +50500,13 @@
         <v>21</v>
       </c>
       <c r="C1767">
-        <v>1551</v>
+        <v>4769</v>
       </c>
       <c r="D1767" t="s">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="F1767" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="G1767" t="s">
         <v>12</v>
@@ -50368,10 +50515,10 @@
         <v>0</v>
       </c>
       <c r="I1767" s="1">
-        <v>46122.590162037035</v>
+        <v>46146.679050925923</v>
       </c>
       <c r="J1767">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1767" t="s">
         <v>11</v>
@@ -50382,25 +50529,25 @@
         <v>21</v>
       </c>
       <c r="C1768">
-        <v>1581</v>
+        <v>3800</v>
       </c>
       <c r="D1768" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="F1768" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="G1768" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1768" s="2">
-        <v>7.4652777777777781E-3</v>
+        <v>0</v>
       </c>
       <c r="I1768" s="1">
-        <v>46122.590856481482</v>
+        <v>46146.679745370369</v>
       </c>
       <c r="J1768">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1768" t="s">
         <v>11</v>
@@ -50411,25 +50558,25 @@
         <v>21</v>
       </c>
       <c r="C1769">
-        <v>1545</v>
+        <v>1608</v>
       </c>
       <c r="D1769" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="F1769" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="G1769" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1769" s="2">
-        <v>7.3495370370370372E-3</v>
+        <v>0</v>
       </c>
       <c r="I1769" s="1">
-        <v>46122.590856481482</v>
+        <v>46146.680439814816</v>
       </c>
       <c r="J1769">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1769" t="s">
         <v>11</v>
@@ -50440,25 +50587,25 @@
         <v>21</v>
       </c>
       <c r="C1770">
-        <v>1604</v>
+        <v>3185</v>
       </c>
       <c r="D1770" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="F1770" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="G1770" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1770" s="2">
-        <v>1.579861111111111E-2</v>
+        <v>0</v>
       </c>
       <c r="I1770" s="1">
-        <v>46122.591550925928</v>
+        <v>46146.680439814816</v>
       </c>
       <c r="J1770">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1770" t="s">
         <v>11</v>
@@ -50469,25 +50616,25 @@
         <v>21</v>
       </c>
       <c r="C1771">
-        <v>4726</v>
+        <v>1556</v>
       </c>
       <c r="D1771" t="s">
-        <v>189</v>
+        <v>40</v>
       </c>
       <c r="F1771" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="G1771" t="s">
         <v>10</v>
       </c>
       <c r="H1771" s="2">
-        <v>1.6724537037037038E-2</v>
+        <v>5.4166666666666669E-3</v>
       </c>
       <c r="I1771" s="1">
-        <v>46122.591550925928</v>
+        <v>46146.681134259263</v>
       </c>
       <c r="J1771">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1771" t="s">
         <v>11</v>
@@ -50498,25 +50645,25 @@
         <v>21</v>
       </c>
       <c r="C1772">
-        <v>1540</v>
+        <v>5133</v>
       </c>
       <c r="D1772" t="s">
-        <v>97</v>
+        <v>205</v>
       </c>
       <c r="F1772" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="G1772" t="s">
         <v>10</v>
       </c>
       <c r="H1772" s="2">
-        <v>9.3518518518518525E-3</v>
+        <v>4.9421296296296297E-3</v>
       </c>
       <c r="I1772" s="1">
-        <v>46122.592245370368</v>
+        <v>46146.681828703702</v>
       </c>
       <c r="J1772">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1772" t="s">
         <v>11</v>
@@ -50527,22 +50674,22 @@
         <v>21</v>
       </c>
       <c r="C1773">
-        <v>1601</v>
+        <v>5536</v>
       </c>
       <c r="D1773" t="s">
-        <v>100</v>
+        <v>224</v>
       </c>
       <c r="F1773" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="G1773" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1773" s="2">
-        <v>7.6157407407407406E-3</v>
+        <v>0</v>
       </c>
       <c r="I1773" s="1">
-        <v>46122.592939814815</v>
+        <v>46146.681828703702</v>
       </c>
       <c r="J1773">
         <v>0</v>
@@ -50552,200 +50699,1461 @@
       </c>
     </row>
     <row r="1774" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1774" s="2"/>
-      <c r="I1774" s="1"/>
+      <c r="B1774" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1774">
+        <v>1579</v>
+      </c>
+      <c r="D1774" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1774" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1774" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1774" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1774" s="1">
+        <v>46146.682523148149</v>
+      </c>
+      <c r="J1774">
+        <v>0</v>
+      </c>
+      <c r="K1774" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1775" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1775" s="2"/>
-      <c r="I1775" s="1"/>
+      <c r="B1775" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1775">
+        <v>1576</v>
+      </c>
+      <c r="D1775" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1775" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1775" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1775" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1775" s="1">
+        <v>46146.683217592596</v>
+      </c>
+      <c r="J1775">
+        <v>0</v>
+      </c>
+      <c r="K1775" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1776" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1776" s="2"/>
-      <c r="I1776" s="1"/>
-    </row>
-    <row r="1777" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1777" s="2"/>
-      <c r="I1777" s="1"/>
-    </row>
-    <row r="1778" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1778" s="2"/>
-      <c r="I1778" s="1"/>
-    </row>
-    <row r="1779" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1779" s="2"/>
-      <c r="I1779" s="1"/>
-    </row>
-    <row r="1780" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1780" s="2"/>
-      <c r="I1780" s="1"/>
-    </row>
-    <row r="1781" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1781" s="2"/>
-      <c r="I1781" s="1"/>
-    </row>
-    <row r="1782" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1782" s="2"/>
-      <c r="I1782" s="1"/>
-    </row>
-    <row r="1783" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1783" s="2"/>
-      <c r="I1783" s="1"/>
-    </row>
-    <row r="1784" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1784" s="2"/>
-      <c r="I1784" s="1"/>
-    </row>
-    <row r="1785" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1785" s="2"/>
-      <c r="I1785" s="1"/>
-    </row>
-    <row r="1786" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1786" s="2"/>
-      <c r="I1786" s="1"/>
-    </row>
-    <row r="1787" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1787" s="2"/>
-      <c r="I1787" s="1"/>
-    </row>
-    <row r="1788" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1788" s="2"/>
-      <c r="I1788" s="1"/>
-    </row>
-    <row r="1789" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1789" s="2"/>
-      <c r="I1789" s="1"/>
-    </row>
-    <row r="1790" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1790" s="2"/>
-      <c r="I1790" s="1"/>
-    </row>
-    <row r="1791" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1791" s="2"/>
-      <c r="I1791" s="1"/>
-    </row>
-    <row r="1792" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1792" s="2"/>
-      <c r="I1792" s="1"/>
-    </row>
-    <row r="1793" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1793" s="2"/>
-      <c r="I1793" s="1"/>
-    </row>
-    <row r="1794" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1794" s="2"/>
-      <c r="I1794" s="1"/>
-    </row>
-    <row r="1795" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1795" s="2"/>
-      <c r="I1795" s="1"/>
-    </row>
-    <row r="1796" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1796" s="2"/>
-      <c r="I1796" s="1"/>
-    </row>
-    <row r="1797" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1797" s="2"/>
-      <c r="I1797" s="1"/>
-    </row>
-    <row r="1798" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1798" s="2"/>
-      <c r="I1798" s="1"/>
-    </row>
-    <row r="1799" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1799" s="2"/>
-      <c r="I1799" s="1"/>
-    </row>
-    <row r="1800" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1800" s="2"/>
-      <c r="I1800" s="1"/>
-    </row>
-    <row r="1801" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1801" s="2"/>
-      <c r="I1801" s="1"/>
-    </row>
-    <row r="1802" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1802" s="2"/>
-      <c r="I1802" s="1"/>
-    </row>
-    <row r="1803" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B1776" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1776">
+        <v>1549</v>
+      </c>
+      <c r="D1776" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1776" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1776" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1776" s="2">
+        <v>5.7407407407407407E-3</v>
+      </c>
+      <c r="I1776" s="1">
+        <v>46146.683217592596</v>
+      </c>
+      <c r="J1776">
+        <v>0</v>
+      </c>
+      <c r="K1776" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1777" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1777" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1777">
+        <v>3188</v>
+      </c>
+      <c r="D1777" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1777" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1777" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1777" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1777" s="1">
+        <v>46146.683912037035</v>
+      </c>
+      <c r="J1777">
+        <v>0</v>
+      </c>
+      <c r="K1777" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1778" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1778" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1778">
+        <v>3181</v>
+      </c>
+      <c r="D1778" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1778" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1778" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1778" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1778" s="1">
+        <v>46146.684606481482</v>
+      </c>
+      <c r="J1778">
+        <v>0</v>
+      </c>
+      <c r="K1778" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1779" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1779" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1779">
+        <v>2670</v>
+      </c>
+      <c r="D1779" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1779" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1779" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1779" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1779" s="1">
+        <v>46146.684606481482</v>
+      </c>
+      <c r="J1779">
+        <v>0</v>
+      </c>
+      <c r="K1779" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1780" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1780" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1780">
+        <v>1592</v>
+      </c>
+      <c r="D1780" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1780" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1780" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1780" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1780" s="1">
+        <v>46146.685300925928</v>
+      </c>
+      <c r="J1780">
+        <v>0</v>
+      </c>
+      <c r="K1780" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1781" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1781" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1781">
+        <v>1561</v>
+      </c>
+      <c r="D1781" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1781" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1781" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1781" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1781" s="1">
+        <v>46146.685995370368</v>
+      </c>
+      <c r="J1781">
+        <v>0</v>
+      </c>
+      <c r="K1781" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1782" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1782" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1782">
+        <v>3187</v>
+      </c>
+      <c r="D1782" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1782" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1782" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1782" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1782" s="1">
+        <v>46146.685995370368</v>
+      </c>
+      <c r="J1782">
+        <v>0</v>
+      </c>
+      <c r="K1782" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1783" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1783" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1783">
+        <v>1597</v>
+      </c>
+      <c r="D1783" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1783" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1783" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1783" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1783" s="1">
+        <v>46146.686689814815</v>
+      </c>
+      <c r="J1783">
+        <v>0</v>
+      </c>
+      <c r="K1783" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1784" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1784" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1784">
+        <v>1569</v>
+      </c>
+      <c r="D1784" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1784" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1784" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1784" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1784" s="1">
+        <v>46146.687384259261</v>
+      </c>
+      <c r="J1784">
+        <v>0</v>
+      </c>
+      <c r="K1784" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1785" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1785" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1785">
+        <v>1538</v>
+      </c>
+      <c r="D1785" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1785" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1785" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1785" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1785" s="1">
+        <v>46146.687384259261</v>
+      </c>
+      <c r="J1785">
+        <v>0</v>
+      </c>
+      <c r="K1785" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1786" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1786" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1786">
+        <v>1598</v>
+      </c>
+      <c r="D1786" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1786" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1786" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1786" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1786" s="1">
+        <v>46146.688078703701</v>
+      </c>
+      <c r="J1786">
+        <v>0</v>
+      </c>
+      <c r="K1786" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1787" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1787" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1787">
+        <v>3182</v>
+      </c>
+      <c r="D1787" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1787" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1787" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1787" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1787" s="1">
+        <v>46146.688773148147</v>
+      </c>
+      <c r="J1787">
+        <v>0</v>
+      </c>
+      <c r="K1787" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1788" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1788" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1788">
+        <v>1553</v>
+      </c>
+      <c r="D1788" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1788" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1788" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1788" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1788" s="1">
+        <v>46146.688773148147</v>
+      </c>
+      <c r="J1788">
+        <v>0</v>
+      </c>
+      <c r="K1788" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1789" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1789" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1789">
+        <v>3803</v>
+      </c>
+      <c r="D1789" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1789" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1789" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1789" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1789" s="1">
+        <v>46146.689467592594</v>
+      </c>
+      <c r="J1789">
+        <v>0</v>
+      </c>
+      <c r="K1789" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1790" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1790" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1790">
+        <v>4635</v>
+      </c>
+      <c r="D1790" t="s">
+        <v>187</v>
+      </c>
+      <c r="F1790" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1790" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1790" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1790" s="1">
+        <v>46146.690162037034</v>
+      </c>
+      <c r="J1790">
+        <v>0</v>
+      </c>
+      <c r="K1790" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1791" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1791" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1791">
+        <v>4825</v>
+      </c>
+      <c r="D1791" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1791" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1791" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1791" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1791" s="1">
+        <v>46146.690162037034</v>
+      </c>
+      <c r="J1791">
+        <v>0</v>
+      </c>
+      <c r="K1791" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1792" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1792" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1792">
+        <v>1578</v>
+      </c>
+      <c r="D1792" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1792" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1792" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1792" s="2">
+        <v>8.4953703703703701E-3</v>
+      </c>
+      <c r="I1792" s="1">
+        <v>46146.69085648148</v>
+      </c>
+      <c r="J1792">
+        <v>0</v>
+      </c>
+      <c r="K1792" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1793" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1793" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1793">
+        <v>5534</v>
+      </c>
+      <c r="D1793" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1793" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1793" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1793" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1793" s="1">
+        <v>46146.691550925927</v>
+      </c>
+      <c r="J1793">
+        <v>0</v>
+      </c>
+      <c r="K1793" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1794" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1794" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1794">
+        <v>1599</v>
+      </c>
+      <c r="D1794" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1794" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1794" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1794" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1794" s="1">
+        <v>46146.691550925927</v>
+      </c>
+      <c r="J1794">
+        <v>0</v>
+      </c>
+      <c r="K1794" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1795" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1795" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1795">
+        <v>5144</v>
+      </c>
+      <c r="D1795" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1795" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1795" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1795" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1795" s="1">
+        <v>46146.692245370374</v>
+      </c>
+      <c r="J1795">
+        <v>0</v>
+      </c>
+      <c r="K1795" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1796" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1796" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1796">
+        <v>1555</v>
+      </c>
+      <c r="D1796" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1796" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1796" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1796" s="2">
+        <v>4.178240740740741E-3</v>
+      </c>
+      <c r="I1796" s="1">
+        <v>46146.709722222222</v>
+      </c>
+      <c r="J1796">
+        <v>0</v>
+      </c>
+      <c r="K1796" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1797" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1797" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1797">
+        <v>2659</v>
+      </c>
+      <c r="D1797" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1797" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1797" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1797" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1797" s="1">
+        <v>46146.710416666669</v>
+      </c>
+      <c r="J1797">
+        <v>0</v>
+      </c>
+      <c r="K1797" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1798" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1798" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1798">
+        <v>5142</v>
+      </c>
+      <c r="D1798" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1798" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1798" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1798" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1798" s="1">
+        <v>46146.711111111108</v>
+      </c>
+      <c r="J1798">
+        <v>0</v>
+      </c>
+      <c r="K1798" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1799" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1799" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1799">
+        <v>1572</v>
+      </c>
+      <c r="D1799" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1799" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1799" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1799" s="2">
+        <v>5.185185185185185E-3</v>
+      </c>
+      <c r="I1799" s="1">
+        <v>46146.711111111108</v>
+      </c>
+      <c r="J1799">
+        <v>0</v>
+      </c>
+      <c r="K1799" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1800" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1800" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1800">
+        <v>1571</v>
+      </c>
+      <c r="D1800" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1800" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1800" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1800" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1800" s="1">
+        <v>46146.711805555555</v>
+      </c>
+      <c r="J1800">
+        <v>0</v>
+      </c>
+      <c r="K1800" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1801" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1801" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1801">
+        <v>2867</v>
+      </c>
+      <c r="D1801" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1801" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1801" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1801" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1801" s="1">
+        <v>46146.712500000001</v>
+      </c>
+      <c r="J1801">
+        <v>0</v>
+      </c>
+      <c r="K1801" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1802" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1802" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1802">
+        <v>4797</v>
+      </c>
+      <c r="D1802" t="s">
+        <v>197</v>
+      </c>
+      <c r="F1802" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1802" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1802" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1802" s="1">
+        <v>46146.713194444441</v>
+      </c>
+      <c r="J1802">
+        <v>0</v>
+      </c>
+      <c r="K1802" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1803" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1803" s="2"/>
       <c r="I1803" s="1"/>
-    </row>
-    <row r="1804" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1804" s="2"/>
-      <c r="I1804" s="1"/>
-    </row>
-    <row r="1805" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1805" s="2"/>
-      <c r="I1805" s="1"/>
-    </row>
-    <row r="1806" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1806" s="2"/>
-      <c r="I1806" s="1"/>
-    </row>
-    <row r="1807" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1807" s="2"/>
-      <c r="I1807" s="1"/>
-    </row>
-    <row r="1808" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1808" s="2"/>
-      <c r="I1808" s="1"/>
-    </row>
-    <row r="1809" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1809" s="2"/>
-      <c r="I1809" s="1"/>
-    </row>
-    <row r="1810" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1810" s="1"/>
-    </row>
-    <row r="1811" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1811" s="1"/>
-    </row>
-    <row r="1812" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1812" s="2"/>
-      <c r="I1812" s="1"/>
-    </row>
-    <row r="1813" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1813" s="1"/>
-    </row>
-    <row r="1814" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1814" s="1"/>
-    </row>
-    <row r="1815" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1815" s="1"/>
-    </row>
-    <row r="1816" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1816" s="2"/>
-      <c r="I1816" s="1"/>
-    </row>
-    <row r="1817" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1817" s="2"/>
-      <c r="I1817" s="1"/>
-    </row>
-    <row r="1818" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1818" s="1"/>
-    </row>
-    <row r="1819" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1819" s="1"/>
-    </row>
-    <row r="1820" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1820" s="2"/>
-      <c r="I1820" s="1"/>
-    </row>
-    <row r="1821" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1821" s="1"/>
-    </row>
-    <row r="1822" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1822" s="2"/>
-      <c r="I1822" s="1"/>
-    </row>
-    <row r="1823" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1823" s="2"/>
-      <c r="I1823" s="1"/>
-    </row>
-    <row r="1824" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1824" s="2"/>
-      <c r="I1824" s="1"/>
+      <c r="K1803" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1804" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1804" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1804">
+        <v>5410</v>
+      </c>
+      <c r="D1804" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1804" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1804" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1804" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1804" s="1">
+        <v>46146.713194444441</v>
+      </c>
+      <c r="J1804">
+        <v>0</v>
+      </c>
+      <c r="K1804" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1805" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1805" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1805">
+        <v>1596</v>
+      </c>
+      <c r="D1805" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1805" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1805" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1805" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1805" s="1">
+        <v>46146.713888888888</v>
+      </c>
+      <c r="J1805">
+        <v>0</v>
+      </c>
+      <c r="K1805" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1806" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1806" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1806">
+        <v>5203</v>
+      </c>
+      <c r="D1806" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1806" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1806" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1806" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1806" s="1">
+        <v>46146.714583333334</v>
+      </c>
+      <c r="J1806">
+        <v>0</v>
+      </c>
+      <c r="K1806" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1807" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1807" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1807">
+        <v>5444</v>
+      </c>
+      <c r="D1807" t="s">
+        <v>222</v>
+      </c>
+      <c r="F1807" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1807" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1807" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1807" s="1">
+        <v>46146.714583333334</v>
+      </c>
+      <c r="J1807">
+        <v>0</v>
+      </c>
+      <c r="K1807" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1808" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1808" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1808">
+        <v>5317</v>
+      </c>
+      <c r="D1808" t="s">
+        <v>223</v>
+      </c>
+      <c r="F1808" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1808" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1808" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1808" s="1">
+        <v>46146.715277777781</v>
+      </c>
+      <c r="J1808">
+        <v>0</v>
+      </c>
+      <c r="K1808" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1809" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1809" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1809">
+        <v>5140</v>
+      </c>
+      <c r="D1809" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1809" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1809" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1809" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1809" s="1">
+        <v>46146.715277777781</v>
+      </c>
+      <c r="J1809">
+        <v>0</v>
+      </c>
+      <c r="K1809" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1810" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1810" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1810">
+        <v>3841</v>
+      </c>
+      <c r="D1810" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1810" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1810" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1810" s="2">
+        <v>9.3518518518518525E-3</v>
+      </c>
+      <c r="I1810" s="1">
+        <v>46146.71597222222</v>
+      </c>
+      <c r="J1810">
+        <v>0</v>
+      </c>
+      <c r="K1810" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1811" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1811" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1811">
+        <v>5535</v>
+      </c>
+      <c r="D1811" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1811" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1811" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1811">
+        <v>0</v>
+      </c>
+      <c r="I1811" s="1">
+        <v>46146.716666666667</v>
+      </c>
+      <c r="J1811">
+        <v>0</v>
+      </c>
+      <c r="K1811" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1812" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1812" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1812">
+        <v>3047</v>
+      </c>
+      <c r="D1812" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1812" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1812" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1812" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1812" s="1">
+        <v>46146.717361111114</v>
+      </c>
+      <c r="J1812">
+        <v>0</v>
+      </c>
+      <c r="K1812" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1813" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1813" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1813">
+        <v>5533</v>
+      </c>
+      <c r="D1813" t="s">
+        <v>227</v>
+      </c>
+      <c r="F1813" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1813" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1813">
+        <v>0</v>
+      </c>
+      <c r="I1813" s="1">
+        <v>46146.717361111114</v>
+      </c>
+      <c r="J1813">
+        <v>0</v>
+      </c>
+      <c r="K1813" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1814" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1814" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1814">
+        <v>1552</v>
+      </c>
+      <c r="D1814" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1814" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1814" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1814">
+        <v>0</v>
+      </c>
+      <c r="I1814" s="1">
+        <v>46146.718055555553</v>
+      </c>
+      <c r="J1814">
+        <v>0</v>
+      </c>
+      <c r="K1814" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1815" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1815" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1815">
+        <v>1588</v>
+      </c>
+      <c r="D1815" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1815" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1815" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1815">
+        <v>0</v>
+      </c>
+      <c r="I1815" s="1">
+        <v>46146.718055555553</v>
+      </c>
+      <c r="J1815">
+        <v>0</v>
+      </c>
+      <c r="K1815" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1816" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1816" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1816">
+        <v>5228</v>
+      </c>
+      <c r="D1816" t="s">
+        <v>214</v>
+      </c>
+      <c r="F1816" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1816" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1816" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1816" s="1">
+        <v>46146.71875</v>
+      </c>
+      <c r="J1816">
+        <v>0</v>
+      </c>
+      <c r="K1816" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1817" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1817" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1817">
+        <v>3659</v>
+      </c>
+      <c r="D1817" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1817" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1817" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1817" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1817" s="1">
+        <v>46146.719444444447</v>
+      </c>
+      <c r="J1817">
+        <v>0</v>
+      </c>
+      <c r="K1817" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1818" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1818" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1818">
+        <v>1551</v>
+      </c>
+      <c r="D1818" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1818" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1818" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1818">
+        <v>0</v>
+      </c>
+      <c r="I1818" s="1">
+        <v>46146.719444444447</v>
+      </c>
+      <c r="J1818">
+        <v>0</v>
+      </c>
+      <c r="K1818" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1819" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1819" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1819">
+        <v>1581</v>
+      </c>
+      <c r="D1819" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1819" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1819" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1819">
+        <v>0</v>
+      </c>
+      <c r="I1819" s="1">
+        <v>46146.720138888886</v>
+      </c>
+      <c r="J1819">
+        <v>0</v>
+      </c>
+      <c r="K1819" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1820" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1820" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1820">
+        <v>1545</v>
+      </c>
+      <c r="D1820" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1820" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1820" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1820" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1820" s="1">
+        <v>46146.720833333333</v>
+      </c>
+      <c r="J1820">
+        <v>0</v>
+      </c>
+      <c r="K1820" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1821" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1821" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1821">
+        <v>1604</v>
+      </c>
+      <c r="D1821" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1821" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1821" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1821">
+        <v>0</v>
+      </c>
+      <c r="I1821" s="1">
+        <v>46146.720833333333</v>
+      </c>
+      <c r="J1821">
+        <v>0</v>
+      </c>
+      <c r="K1821" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1822" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1822" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1822">
+        <v>4726</v>
+      </c>
+      <c r="D1822" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1822" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1822" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1822" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1822" s="1">
+        <v>46146.72152777778</v>
+      </c>
+      <c r="J1822">
+        <v>0</v>
+      </c>
+      <c r="K1822" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1823" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1823" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1823">
+        <v>1540</v>
+      </c>
+      <c r="D1823" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1823" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1823" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1823" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1823" s="1">
+        <v>46146.722222222219</v>
+      </c>
+      <c r="J1823">
+        <v>0</v>
+      </c>
+      <c r="K1823" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1824" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1824" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1824">
+        <v>1601</v>
+      </c>
+      <c r="D1824" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1824" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1824" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1824" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1824" s="1">
+        <v>46146.722222222219</v>
+      </c>
+      <c r="J1824">
+        <v>0</v>
+      </c>
+      <c r="K1824" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1825" spans="8:9" x14ac:dyDescent="0.25">
       <c r="I1825" s="1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Panhandle Express\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E1B61A-E376-407D-931D-9A04BC6E4BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC3F92E-0FD8-4B8C-BFFB-D98AA0C9481E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8814" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8815" uniqueCount="228">
   <si>
     <t>Company Name</t>
   </si>
@@ -50422,10 +50422,10 @@
         <v>15</v>
       </c>
       <c r="G1764" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1764" s="2">
-        <v>0</v>
+        <v>5.5555555555555558E-3</v>
       </c>
       <c r="I1764" s="1">
         <v>46146.677662037036</v>
@@ -50451,10 +50451,10 @@
         <v>15</v>
       </c>
       <c r="G1765" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1765" s="2">
-        <v>0</v>
+        <v>4.5254629629629629E-3</v>
       </c>
       <c r="I1765" s="1">
         <v>46146.678356481483</v>
@@ -50509,10 +50509,10 @@
         <v>15</v>
       </c>
       <c r="G1767" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1767" s="2">
-        <v>0</v>
+        <v>0.38383101851851853</v>
       </c>
       <c r="I1767" s="1">
         <v>46146.679050925923</v>
@@ -50538,10 +50538,10 @@
         <v>15</v>
       </c>
       <c r="G1768" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1768" s="2">
-        <v>0</v>
+        <v>6.1805555555555555E-3</v>
       </c>
       <c r="I1768" s="1">
         <v>46146.679745370369</v>
@@ -50596,10 +50596,10 @@
         <v>15</v>
       </c>
       <c r="G1770" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1770" s="2">
-        <v>0</v>
+        <v>4.4560185185185189E-3</v>
       </c>
       <c r="I1770" s="1">
         <v>46146.680439814816</v>
@@ -50683,10 +50683,10 @@
         <v>15</v>
       </c>
       <c r="G1773" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1773" s="2">
-        <v>0</v>
+        <v>5.6828703703703702E-3</v>
       </c>
       <c r="I1773" s="1">
         <v>46146.681828703702</v>
@@ -50915,10 +50915,10 @@
         <v>15</v>
       </c>
       <c r="G1781" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1781" s="2">
-        <v>0</v>
+        <v>4.7800925925925927E-3</v>
       </c>
       <c r="I1781" s="1">
         <v>46146.685995370368</v>
@@ -50944,10 +50944,10 @@
         <v>15</v>
       </c>
       <c r="G1782" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1782" s="2">
-        <v>0</v>
+        <v>6.2037037037037035E-3</v>
       </c>
       <c r="I1782" s="1">
         <v>46146.685995370368</v>
@@ -51002,10 +51002,10 @@
         <v>15</v>
       </c>
       <c r="G1784" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="H1784" s="2">
-        <v>0</v>
+        <v>5.8680555555555552E-3</v>
       </c>
       <c r="I1784" s="1">
         <v>46146.687384259261</v>
@@ -51018,32 +51018,10 @@
       </c>
     </row>
     <row r="1785" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1785" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1785">
-        <v>1538</v>
-      </c>
-      <c r="D1785" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1785" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1785" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1785" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1785" s="1">
-        <v>46146.687384259261</v>
-      </c>
-      <c r="J1785">
-        <v>0</v>
-      </c>
+      <c r="H1785" s="2"/>
+      <c r="I1785" s="1"/>
       <c r="K1785" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1786" spans="2:11" x14ac:dyDescent="0.25">
@@ -51051,10 +51029,10 @@
         <v>21</v>
       </c>
       <c r="C1786">
-        <v>1598</v>
+        <v>1538</v>
       </c>
       <c r="D1786" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F1786" t="s">
         <v>15</v>
@@ -51066,7 +51044,7 @@
         <v>0</v>
       </c>
       <c r="I1786" s="1">
-        <v>46146.688078703701</v>
+        <v>46146.687384259261</v>
       </c>
       <c r="J1786">
         <v>0</v>
@@ -51080,22 +51058,22 @@
         <v>21</v>
       </c>
       <c r="C1787">
-        <v>3182</v>
+        <v>1598</v>
       </c>
       <c r="D1787" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="F1787" t="s">
         <v>15</v>
       </c>
       <c r="G1787" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1787" s="2">
-        <v>0</v>
+        <v>5.6944444444444447E-3</v>
       </c>
       <c r="I1787" s="1">
-        <v>46146.688773148147</v>
+        <v>46146.688078703701</v>
       </c>
       <c r="J1787">
         <v>0</v>
@@ -51109,19 +51087,19 @@
         <v>21</v>
       </c>
       <c r="C1788">
-        <v>1553</v>
+        <v>3182</v>
       </c>
       <c r="D1788" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="F1788" t="s">
         <v>15</v>
       </c>
       <c r="G1788" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1788" s="2">
-        <v>0</v>
+        <v>6.1574074074074074E-3</v>
       </c>
       <c r="I1788" s="1">
         <v>46146.688773148147</v>
@@ -51138,10 +51116,10 @@
         <v>21</v>
       </c>
       <c r="C1789">
-        <v>3803</v>
+        <v>1553</v>
       </c>
       <c r="D1789" t="s">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c r="F1789" t="s">
         <v>15</v>
@@ -51153,7 +51131,7 @@
         <v>0</v>
       </c>
       <c r="I1789" s="1">
-        <v>46146.689467592594</v>
+        <v>46146.688773148147</v>
       </c>
       <c r="J1789">
         <v>0</v>
@@ -51167,22 +51145,22 @@
         <v>21</v>
       </c>
       <c r="C1790">
-        <v>4635</v>
+        <v>3803</v>
       </c>
       <c r="D1790" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="F1790" t="s">
         <v>15</v>
       </c>
       <c r="G1790" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1790" s="2">
-        <v>0</v>
+        <v>4.7337962962962967E-3</v>
       </c>
       <c r="I1790" s="1">
-        <v>46146.690162037034</v>
+        <v>46146.689467592594</v>
       </c>
       <c r="J1790">
         <v>0</v>
@@ -51196,19 +51174,19 @@
         <v>21</v>
       </c>
       <c r="C1791">
-        <v>4825</v>
+        <v>4635</v>
       </c>
       <c r="D1791" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F1791" t="s">
         <v>15</v>
       </c>
       <c r="G1791" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1791" s="2">
-        <v>0</v>
+        <v>5.2662037037037035E-3</v>
       </c>
       <c r="I1791" s="1">
         <v>46146.690162037034</v>
@@ -51225,22 +51203,22 @@
         <v>21</v>
       </c>
       <c r="C1792">
-        <v>1578</v>
+        <v>4825</v>
       </c>
       <c r="D1792" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="F1792" t="s">
         <v>15</v>
       </c>
       <c r="G1792" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1792" s="2">
-        <v>8.4953703703703701E-3</v>
+        <v>0</v>
       </c>
       <c r="I1792" s="1">
-        <v>46146.69085648148</v>
+        <v>46146.690162037034</v>
       </c>
       <c r="J1792">
         <v>0</v>
@@ -51254,22 +51232,22 @@
         <v>21</v>
       </c>
       <c r="C1793">
-        <v>5534</v>
+        <v>1578</v>
       </c>
       <c r="D1793" t="s">
-        <v>225</v>
+        <v>66</v>
       </c>
       <c r="F1793" t="s">
         <v>15</v>
       </c>
       <c r="G1793" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1793" s="2">
-        <v>0</v>
+        <v>8.4953703703703701E-3</v>
       </c>
       <c r="I1793" s="1">
-        <v>46146.691550925927</v>
+        <v>46146.69085648148</v>
       </c>
       <c r="J1793">
         <v>0</v>
@@ -51283,10 +51261,10 @@
         <v>21</v>
       </c>
       <c r="C1794">
-        <v>1599</v>
+        <v>5534</v>
       </c>
       <c r="D1794" t="s">
-        <v>67</v>
+        <v>225</v>
       </c>
       <c r="F1794" t="s">
         <v>15</v>
@@ -51312,10 +51290,10 @@
         <v>21</v>
       </c>
       <c r="C1795">
-        <v>5144</v>
+        <v>1599</v>
       </c>
       <c r="D1795" t="s">
-        <v>208</v>
+        <v>67</v>
       </c>
       <c r="F1795" t="s">
         <v>15</v>
@@ -51327,7 +51305,7 @@
         <v>0</v>
       </c>
       <c r="I1795" s="1">
-        <v>46146.692245370374</v>
+        <v>46146.691550925927</v>
       </c>
       <c r="J1795">
         <v>0</v>
@@ -51341,10 +51319,10 @@
         <v>21</v>
       </c>
       <c r="C1796">
-        <v>1555</v>
+        <v>5144</v>
       </c>
       <c r="D1796" t="s">
-        <v>74</v>
+        <v>208</v>
       </c>
       <c r="F1796" t="s">
         <v>15</v>
@@ -51353,10 +51331,10 @@
         <v>10</v>
       </c>
       <c r="H1796" s="2">
-        <v>4.178240740740741E-3</v>
+        <v>6.0185185185185185E-3</v>
       </c>
       <c r="I1796" s="1">
-        <v>46146.709722222222</v>
+        <v>46146.692245370374</v>
       </c>
       <c r="J1796">
         <v>0</v>
@@ -51370,22 +51348,22 @@
         <v>21</v>
       </c>
       <c r="C1797">
-        <v>2659</v>
+        <v>1555</v>
       </c>
       <c r="D1797" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="F1797" t="s">
         <v>15</v>
       </c>
       <c r="G1797" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1797" s="2">
-        <v>0</v>
+        <v>4.178240740740741E-3</v>
       </c>
       <c r="I1797" s="1">
-        <v>46146.710416666669</v>
+        <v>46146.709722222222</v>
       </c>
       <c r="J1797">
         <v>0</v>
@@ -51399,10 +51377,10 @@
         <v>21</v>
       </c>
       <c r="C1798">
-        <v>5142</v>
+        <v>2659</v>
       </c>
       <c r="D1798" t="s">
-        <v>209</v>
+        <v>126</v>
       </c>
       <c r="F1798" t="s">
         <v>15</v>
@@ -51414,7 +51392,7 @@
         <v>0</v>
       </c>
       <c r="I1798" s="1">
-        <v>46146.711111111108</v>
+        <v>46146.710416666669</v>
       </c>
       <c r="J1798">
         <v>0</v>
@@ -51428,10 +51406,10 @@
         <v>21</v>
       </c>
       <c r="C1799">
-        <v>1572</v>
+        <v>5142</v>
       </c>
       <c r="D1799" t="s">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="F1799" t="s">
         <v>15</v>
@@ -51440,7 +51418,7 @@
         <v>10</v>
       </c>
       <c r="H1799" s="2">
-        <v>5.185185185185185E-3</v>
+        <v>4.7685185185185183E-3</v>
       </c>
       <c r="I1799" s="1">
         <v>46146.711111111108</v>
@@ -51457,22 +51435,22 @@
         <v>21</v>
       </c>
       <c r="C1800">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="D1800" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F1800" t="s">
         <v>15</v>
       </c>
       <c r="G1800" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1800" s="2">
-        <v>0</v>
+        <v>5.185185185185185E-3</v>
       </c>
       <c r="I1800" s="1">
-        <v>46146.711805555555</v>
+        <v>46146.711111111108</v>
       </c>
       <c r="J1800">
         <v>0</v>
@@ -51486,22 +51464,22 @@
         <v>21</v>
       </c>
       <c r="C1801">
-        <v>2867</v>
+        <v>1571</v>
       </c>
       <c r="D1801" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="F1801" t="s">
         <v>15</v>
       </c>
       <c r="G1801" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1801" s="2">
-        <v>0</v>
+        <v>6.4351851851851853E-3</v>
       </c>
       <c r="I1801" s="1">
-        <v>46146.712500000001</v>
+        <v>46146.711805555555</v>
       </c>
       <c r="J1801">
         <v>0</v>
@@ -51515,64 +51493,64 @@
         <v>21</v>
       </c>
       <c r="C1802">
-        <v>4797</v>
+        <v>2867</v>
       </c>
       <c r="D1802" t="s">
-        <v>197</v>
+        <v>131</v>
       </c>
       <c r="F1802" t="s">
         <v>15</v>
       </c>
       <c r="G1802" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1802" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1802" s="1">
+        <v>46146.712500000001</v>
+      </c>
+      <c r="J1802">
+        <v>0</v>
+      </c>
+      <c r="K1802" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1803" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1803" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1803">
+        <v>4797</v>
+      </c>
+      <c r="D1803" t="s">
+        <v>197</v>
+      </c>
+      <c r="F1803" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1803" t="s">
         <v>102</v>
       </c>
-      <c r="H1802" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1802" s="1">
+      <c r="H1803" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1803" s="1">
         <v>46146.713194444441</v>
       </c>
-      <c r="J1802">
-        <v>0</v>
-      </c>
-      <c r="K1802" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1803" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1803" s="2"/>
-      <c r="I1803" s="1"/>
+      <c r="J1803">
+        <v>0</v>
+      </c>
       <c r="K1803" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1804" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1804" s="2"/>
+      <c r="I1804" s="1"/>
+      <c r="K1804" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="1804" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1804" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1804">
-        <v>5410</v>
-      </c>
-      <c r="D1804" t="s">
-        <v>221</v>
-      </c>
-      <c r="F1804" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1804" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1804" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1804" s="1">
-        <v>46146.713194444441</v>
-      </c>
-      <c r="J1804">
-        <v>0</v>
-      </c>
-      <c r="K1804" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1805" spans="2:11" x14ac:dyDescent="0.25">
@@ -51580,10 +51558,10 @@
         <v>21</v>
       </c>
       <c r="C1805">
-        <v>1596</v>
+        <v>5410</v>
       </c>
       <c r="D1805" t="s">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="F1805" t="s">
         <v>15</v>
@@ -51595,7 +51573,7 @@
         <v>0</v>
       </c>
       <c r="I1805" s="1">
-        <v>46146.713888888888</v>
+        <v>46146.713194444441</v>
       </c>
       <c r="J1805">
         <v>0</v>
@@ -51609,10 +51587,10 @@
         <v>21</v>
       </c>
       <c r="C1806">
-        <v>5203</v>
+        <v>1596</v>
       </c>
       <c r="D1806" t="s">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="F1806" t="s">
         <v>15</v>
@@ -51624,7 +51602,7 @@
         <v>0</v>
       </c>
       <c r="I1806" s="1">
-        <v>46146.714583333334</v>
+        <v>46146.713888888888</v>
       </c>
       <c r="J1806">
         <v>0</v>
@@ -51638,10 +51616,10 @@
         <v>21</v>
       </c>
       <c r="C1807">
-        <v>5444</v>
+        <v>5203</v>
       </c>
       <c r="D1807" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="F1807" t="s">
         <v>15</v>
@@ -51667,22 +51645,22 @@
         <v>21</v>
       </c>
       <c r="C1808">
-        <v>5317</v>
+        <v>5444</v>
       </c>
       <c r="D1808" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F1808" t="s">
         <v>15</v>
       </c>
       <c r="G1808" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1808" s="2">
-        <v>0</v>
+        <v>9.1666666666666667E-3</v>
       </c>
       <c r="I1808" s="1">
-        <v>46146.715277777781</v>
+        <v>46146.714583333334</v>
       </c>
       <c r="J1808">
         <v>0</v>
@@ -51696,10 +51674,10 @@
         <v>21</v>
       </c>
       <c r="C1809">
-        <v>5140</v>
+        <v>5317</v>
       </c>
       <c r="D1809" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="F1809" t="s">
         <v>15</v>
@@ -51725,10 +51703,10 @@
         <v>21</v>
       </c>
       <c r="C1810">
-        <v>3841</v>
+        <v>5140</v>
       </c>
       <c r="D1810" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="F1810" t="s">
         <v>15</v>
@@ -51737,10 +51715,10 @@
         <v>10</v>
       </c>
       <c r="H1810" s="2">
-        <v>9.3518518518518525E-3</v>
+        <v>5.8333333333333336E-3</v>
       </c>
       <c r="I1810" s="1">
-        <v>46146.71597222222</v>
+        <v>46146.715277777781</v>
       </c>
       <c r="J1810">
         <v>0</v>
@@ -51754,22 +51732,22 @@
         <v>21</v>
       </c>
       <c r="C1811">
-        <v>5535</v>
+        <v>3841</v>
       </c>
       <c r="D1811" t="s">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="F1811" t="s">
         <v>15</v>
       </c>
       <c r="G1811" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1811">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1811" s="2">
+        <v>9.3518518518518525E-3</v>
       </c>
       <c r="I1811" s="1">
-        <v>46146.716666666667</v>
+        <v>46146.71597222222</v>
       </c>
       <c r="J1811">
         <v>0</v>
@@ -51783,10 +51761,10 @@
         <v>21</v>
       </c>
       <c r="C1812">
-        <v>3047</v>
+        <v>5535</v>
       </c>
       <c r="D1812" t="s">
-        <v>141</v>
+        <v>226</v>
       </c>
       <c r="F1812" t="s">
         <v>15</v>
@@ -51798,7 +51776,7 @@
         <v>0</v>
       </c>
       <c r="I1812" s="1">
-        <v>46146.717361111114</v>
+        <v>46146.716666666667</v>
       </c>
       <c r="J1812">
         <v>0</v>
@@ -51812,19 +51790,19 @@
         <v>21</v>
       </c>
       <c r="C1813">
-        <v>5533</v>
+        <v>3047</v>
       </c>
       <c r="D1813" t="s">
-        <v>227</v>
+        <v>141</v>
       </c>
       <c r="F1813" t="s">
         <v>15</v>
       </c>
       <c r="G1813" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1813">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1813" s="2">
+        <v>4.9074074074074072E-3</v>
       </c>
       <c r="I1813" s="1">
         <v>46146.717361111114</v>
@@ -51841,10 +51819,10 @@
         <v>21</v>
       </c>
       <c r="C1814">
-        <v>1552</v>
+        <v>5533</v>
       </c>
       <c r="D1814" t="s">
-        <v>87</v>
+        <v>227</v>
       </c>
       <c r="F1814" t="s">
         <v>15</v>
@@ -51856,7 +51834,7 @@
         <v>0</v>
       </c>
       <c r="I1814" s="1">
-        <v>46146.718055555553</v>
+        <v>46146.717361111114</v>
       </c>
       <c r="J1814">
         <v>0</v>
@@ -51870,19 +51848,19 @@
         <v>21</v>
       </c>
       <c r="C1815">
-        <v>1588</v>
+        <v>1552</v>
       </c>
       <c r="D1815" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F1815" t="s">
         <v>15</v>
       </c>
       <c r="G1815" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1815">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1815" s="2">
+        <v>5.7754629629629631E-3</v>
       </c>
       <c r="I1815" s="1">
         <v>46146.718055555553</v>
@@ -51899,10 +51877,10 @@
         <v>21</v>
       </c>
       <c r="C1816">
-        <v>5228</v>
+        <v>1588</v>
       </c>
       <c r="D1816" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="F1816" t="s">
         <v>15</v>
@@ -51914,7 +51892,7 @@
         <v>0</v>
       </c>
       <c r="I1816" s="1">
-        <v>46146.71875</v>
+        <v>46146.718055555553</v>
       </c>
       <c r="J1816">
         <v>0</v>
@@ -51928,10 +51906,10 @@
         <v>21</v>
       </c>
       <c r="C1817">
-        <v>3659</v>
+        <v>5228</v>
       </c>
       <c r="D1817" t="s">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="F1817" t="s">
         <v>15</v>
@@ -51943,7 +51921,7 @@
         <v>0</v>
       </c>
       <c r="I1817" s="1">
-        <v>46146.719444444447</v>
+        <v>46146.71875</v>
       </c>
       <c r="J1817">
         <v>0</v>
@@ -51957,19 +51935,19 @@
         <v>21</v>
       </c>
       <c r="C1818">
-        <v>1551</v>
+        <v>3659</v>
       </c>
       <c r="D1818" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="F1818" t="s">
         <v>15</v>
       </c>
       <c r="G1818" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1818">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1818" s="2">
+        <v>6.851851851851852E-3</v>
       </c>
       <c r="I1818" s="1">
         <v>46146.719444444447</v>
@@ -51986,10 +51964,10 @@
         <v>21</v>
       </c>
       <c r="C1819">
-        <v>1581</v>
+        <v>1551</v>
       </c>
       <c r="D1819" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F1819" t="s">
         <v>15</v>
@@ -52001,7 +51979,7 @@
         <v>0</v>
       </c>
       <c r="I1819" s="1">
-        <v>46146.720138888886</v>
+        <v>46146.719444444447</v>
       </c>
       <c r="J1819">
         <v>0</v>
@@ -52015,10 +51993,10 @@
         <v>21</v>
       </c>
       <c r="C1820">
-        <v>1545</v>
+        <v>1581</v>
       </c>
       <c r="D1820" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F1820" t="s">
         <v>15</v>
@@ -52030,7 +52008,7 @@
         <v>0</v>
       </c>
       <c r="I1820" s="1">
-        <v>46146.720833333333</v>
+        <v>46146.720138888886</v>
       </c>
       <c r="J1820">
         <v>0</v>
@@ -52044,10 +52022,10 @@
         <v>21</v>
       </c>
       <c r="C1821">
-        <v>1604</v>
+        <v>1545</v>
       </c>
       <c r="D1821" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F1821" t="s">
         <v>15</v>
@@ -52073,22 +52051,22 @@
         <v>21</v>
       </c>
       <c r="C1822">
-        <v>4726</v>
+        <v>1604</v>
       </c>
       <c r="D1822" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="F1822" t="s">
         <v>15</v>
       </c>
       <c r="G1822" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1822" s="2">
-        <v>0</v>
+        <v>8.4259259259259253E-3</v>
       </c>
       <c r="I1822" s="1">
-        <v>46146.72152777778</v>
+        <v>46146.720833333333</v>
       </c>
       <c r="J1822">
         <v>0</v>
@@ -52102,10 +52080,10 @@
         <v>21</v>
       </c>
       <c r="C1823">
-        <v>1540</v>
+        <v>4726</v>
       </c>
       <c r="D1823" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="F1823" t="s">
         <v>15</v>
@@ -52117,7 +52095,7 @@
         <v>0</v>
       </c>
       <c r="I1823" s="1">
-        <v>46146.722222222219</v>
+        <v>46146.72152777778</v>
       </c>
       <c r="J1823">
         <v>0</v>
@@ -52131,19 +52109,19 @@
         <v>21</v>
       </c>
       <c r="C1824">
-        <v>1601</v>
+        <v>1540</v>
       </c>
       <c r="D1824" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F1824" t="s">
         <v>15</v>
       </c>
       <c r="G1824" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1824" s="2">
-        <v>0</v>
+        <v>5.5787037037037038E-3</v>
       </c>
       <c r="I1824" s="1">
         <v>46146.722222222219</v>
@@ -52155,56 +52133,82 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1825" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1825" s="1"/>
-    </row>
-    <row r="1826" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1825" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1825" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1825">
+        <v>1601</v>
+      </c>
+      <c r="D1825" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1825" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1825" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1825" s="2">
+        <v>5.2546296296296299E-3</v>
+      </c>
+      <c r="I1825" s="1">
+        <v>46146.722222222219</v>
+      </c>
+      <c r="J1825">
+        <v>0</v>
+      </c>
+      <c r="K1825" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1826" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1826" s="1"/>
     </row>
-    <row r="1827" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1827" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1827" s="1"/>
     </row>
-    <row r="1828" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1828" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1828" s="2"/>
       <c r="I1828" s="1"/>
     </row>
-    <row r="1829" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1829" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1829" s="1"/>
     </row>
-    <row r="1830" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1830" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1830" s="1"/>
     </row>
-    <row r="1831" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1831" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1831" s="1"/>
     </row>
-    <row r="1832" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1832" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1832" s="1"/>
     </row>
-    <row r="1833" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1833" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1833" s="1"/>
     </row>
-    <row r="1834" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1834" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1834" s="1"/>
     </row>
-    <row r="1835" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1835" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1835" s="2"/>
       <c r="I1835" s="1"/>
     </row>
-    <row r="1836" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1836" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1836" s="2"/>
       <c r="I1836" s="1"/>
     </row>
-    <row r="1837" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1837" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1837" s="1"/>
     </row>
-    <row r="1838" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1838" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1838" s="1"/>
     </row>
-    <row r="1839" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1839" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1839" s="2"/>
       <c r="I1839" s="1"/>
     </row>
-    <row r="1840" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1840" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1840" s="1"/>
     </row>
     <row r="1841" spans="8:9" x14ac:dyDescent="0.25">

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Panhandle Express\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18E2629-35BC-41C0-996E-0B1E7C7C5006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22A7D8B-E7D0-47EE-9148-984E887F5B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8816" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8815" uniqueCount="228">
   <si>
     <t>Company Name</t>
   </si>
@@ -50370,7 +50370,7 @@
         <v>46146.67696759259</v>
       </c>
       <c r="J1762">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1762" t="s">
         <v>11</v>
@@ -50399,7 +50399,7 @@
         <v>46146.67696759259</v>
       </c>
       <c r="J1763">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1763" t="s">
         <v>11</v>
@@ -50489,7 +50489,7 @@
         <v>46146.678356481483</v>
       </c>
       <c r="J1766">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1766" t="s">
         <v>11</v>
@@ -50599,7 +50599,7 @@
         <v>10</v>
       </c>
       <c r="H1770" s="2">
-        <v>4.4560185185185189E-3</v>
+        <v>4.8379629629629632E-3</v>
       </c>
       <c r="I1770" s="1">
         <v>46146.680439814816</v>
@@ -50750,7 +50750,7 @@
         <v>46146.683217592596</v>
       </c>
       <c r="J1775">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1775" t="s">
         <v>11</v>
@@ -50773,7 +50773,7 @@
         <v>10</v>
       </c>
       <c r="H1776" s="2">
-        <v>5.7407407407407407E-3</v>
+        <v>5.9143518518518521E-3</v>
       </c>
       <c r="I1776" s="1">
         <v>46146.683217592596</v>
@@ -50799,16 +50799,16 @@
         <v>15</v>
       </c>
       <c r="G1777" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1777" s="2">
-        <v>0</v>
+        <v>4.9189814814814816E-3</v>
       </c>
       <c r="I1777" s="1">
         <v>46146.683912037035</v>
       </c>
       <c r="J1777">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1777" t="s">
         <v>11</v>
@@ -50837,7 +50837,7 @@
         <v>46146.684606481482</v>
       </c>
       <c r="J1778">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1778" t="s">
         <v>11</v>
@@ -50886,16 +50886,16 @@
         <v>15</v>
       </c>
       <c r="G1780" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1780" s="2">
-        <v>0</v>
+        <v>5.0462962962962961E-3</v>
       </c>
       <c r="I1780" s="1">
         <v>46146.685300925928</v>
       </c>
       <c r="J1780">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1780" t="s">
         <v>11</v>
@@ -50982,7 +50982,7 @@
         <v>46146.686689814815</v>
       </c>
       <c r="J1783">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1783" t="s">
         <v>11</v>
@@ -51038,16 +51038,16 @@
         <v>15</v>
       </c>
       <c r="G1786" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1786" s="2">
-        <v>0</v>
+        <v>7.1527777777777779E-3</v>
       </c>
       <c r="I1786" s="1">
         <v>46146.687384259261</v>
       </c>
       <c r="J1786">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1786" t="s">
         <v>11</v>
@@ -51134,7 +51134,7 @@
         <v>46146.688773148147</v>
       </c>
       <c r="J1789">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1789" t="s">
         <v>11</v>
@@ -51157,7 +51157,7 @@
         <v>10</v>
       </c>
       <c r="H1790" s="2">
-        <v>4.7337962962962967E-3</v>
+        <v>4.9305555555555552E-3</v>
       </c>
       <c r="I1790" s="1">
         <v>46146.689467592594</v>
@@ -51221,7 +51221,7 @@
         <v>46146.690162037034</v>
       </c>
       <c r="J1792">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1792" t="s">
         <v>11</v>
@@ -51279,7 +51279,7 @@
         <v>46146.691550925927</v>
       </c>
       <c r="J1794">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1794" t="s">
         <v>11</v>
@@ -51386,10 +51386,10 @@
         <v>15</v>
       </c>
       <c r="G1798" t="s">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="H1798" s="2">
-        <v>0</v>
+        <v>4.8726851851851848E-3</v>
       </c>
       <c r="I1798" s="1">
         <v>46146.710416666669</v>
@@ -51402,10 +51402,32 @@
       </c>
     </row>
     <row r="1799" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H1799" s="2"/>
-      <c r="I1799" s="1"/>
+      <c r="B1799" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1799">
+        <v>5142</v>
+      </c>
+      <c r="D1799" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1799" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1799" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1799" s="2">
+        <v>4.7685185185185183E-3</v>
+      </c>
+      <c r="I1799" s="1">
+        <v>46146.711111111108</v>
+      </c>
+      <c r="J1799">
+        <v>0</v>
+      </c>
       <c r="K1799" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1800" spans="2:11" x14ac:dyDescent="0.3">
@@ -51413,10 +51435,10 @@
         <v>21</v>
       </c>
       <c r="C1800">
-        <v>5142</v>
+        <v>1572</v>
       </c>
       <c r="D1800" t="s">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="F1800" t="s">
         <v>15</v>
@@ -51425,7 +51447,7 @@
         <v>10</v>
       </c>
       <c r="H1800" s="2">
-        <v>4.7685185185185183E-3</v>
+        <v>5.185185185185185E-3</v>
       </c>
       <c r="I1800" s="1">
         <v>46146.711111111108</v>
@@ -51442,10 +51464,10 @@
         <v>21</v>
       </c>
       <c r="C1801">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="D1801" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F1801" t="s">
         <v>15</v>
@@ -51454,10 +51476,10 @@
         <v>10</v>
       </c>
       <c r="H1801" s="2">
-        <v>5.185185185185185E-3</v>
+        <v>6.4351851851851853E-3</v>
       </c>
       <c r="I1801" s="1">
-        <v>46146.711111111108</v>
+        <v>46146.711805555555</v>
       </c>
       <c r="J1801">
         <v>0</v>
@@ -51471,10 +51493,10 @@
         <v>21</v>
       </c>
       <c r="C1802">
-        <v>1571</v>
+        <v>2867</v>
       </c>
       <c r="D1802" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="F1802" t="s">
         <v>15</v>
@@ -51483,13 +51505,13 @@
         <v>10</v>
       </c>
       <c r="H1802" s="2">
-        <v>6.4351851851851853E-3</v>
+        <v>5.5555555555555558E-3</v>
       </c>
       <c r="I1802" s="1">
-        <v>46146.711805555555</v>
+        <v>46146.712500000001</v>
       </c>
       <c r="J1802">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1802" t="s">
         <v>11</v>
@@ -51500,64 +51522,64 @@
         <v>21</v>
       </c>
       <c r="C1803">
-        <v>2867</v>
+        <v>4797</v>
       </c>
       <c r="D1803" t="s">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="F1803" t="s">
         <v>15</v>
       </c>
       <c r="G1803" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="H1803" s="2">
-        <v>5.5555555555555558E-3</v>
+        <v>0</v>
       </c>
       <c r="I1803" s="1">
-        <v>46146.712500000001</v>
+        <v>46146.713194444441</v>
       </c>
       <c r="J1803">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1803" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1804" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B1804" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1804">
-        <v>4797</v>
-      </c>
-      <c r="D1804" t="s">
-        <v>197</v>
-      </c>
-      <c r="F1804" t="s">
+      <c r="H1804" s="2"/>
+      <c r="I1804" s="1"/>
+      <c r="K1804" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1805" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1805" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1805">
+        <v>5410</v>
+      </c>
+      <c r="D1805" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1805" t="s">
         <v>15</v>
       </c>
-      <c r="G1804" t="s">
-        <v>102</v>
-      </c>
-      <c r="H1804" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1804" s="1">
+      <c r="G1805" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1805" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1805" s="1">
         <v>46146.713194444441</v>
       </c>
-      <c r="J1804">
-        <v>0</v>
-      </c>
-      <c r="K1804" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1805" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H1805" s="2"/>
-      <c r="I1805" s="1"/>
+      <c r="J1805">
+        <v>2</v>
+      </c>
       <c r="K1805" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1806" spans="2:11" x14ac:dyDescent="0.3">
@@ -51565,22 +51587,22 @@
         <v>21</v>
       </c>
       <c r="C1806">
-        <v>5410</v>
+        <v>1596</v>
       </c>
       <c r="D1806" t="s">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="F1806" t="s">
         <v>15</v>
       </c>
       <c r="G1806" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1806" s="2">
-        <v>0</v>
+        <v>5.6018518518518518E-3</v>
       </c>
       <c r="I1806" s="1">
-        <v>46146.713194444441</v>
+        <v>46146.713888888888</v>
       </c>
       <c r="J1806">
         <v>1</v>
@@ -51594,25 +51616,25 @@
         <v>21</v>
       </c>
       <c r="C1807">
-        <v>1596</v>
+        <v>5203</v>
       </c>
       <c r="D1807" t="s">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="F1807" t="s">
         <v>15</v>
       </c>
       <c r="G1807" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1807" s="2">
-        <v>5.6018518518518518E-3</v>
+        <v>0</v>
       </c>
       <c r="I1807" s="1">
-        <v>46146.713888888888</v>
+        <v>46146.714583333334</v>
       </c>
       <c r="J1807">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1807" t="s">
         <v>11</v>
@@ -51623,25 +51645,25 @@
         <v>21</v>
       </c>
       <c r="C1808">
-        <v>5203</v>
+        <v>5444</v>
       </c>
       <c r="D1808" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="F1808" t="s">
         <v>15</v>
       </c>
       <c r="G1808" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1808" s="2">
-        <v>0</v>
+        <v>9.1666666666666667E-3</v>
       </c>
       <c r="I1808" s="1">
         <v>46146.714583333334</v>
       </c>
       <c r="J1808">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1808" t="s">
         <v>11</v>
@@ -51652,10 +51674,10 @@
         <v>21</v>
       </c>
       <c r="C1809">
-        <v>5444</v>
+        <v>5317</v>
       </c>
       <c r="D1809" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F1809" t="s">
         <v>15</v>
@@ -51664,13 +51686,13 @@
         <v>10</v>
       </c>
       <c r="H1809" s="2">
-        <v>9.1666666666666667E-3</v>
+        <v>5.0578703703703706E-3</v>
       </c>
       <c r="I1809" s="1">
-        <v>46146.714583333334</v>
+        <v>46146.715277777781</v>
       </c>
       <c r="J1809">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1809" t="s">
         <v>11</v>
@@ -51681,10 +51703,10 @@
         <v>21</v>
       </c>
       <c r="C1810">
-        <v>5317</v>
+        <v>5140</v>
       </c>
       <c r="D1810" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="F1810" t="s">
         <v>15</v>
@@ -51693,13 +51715,13 @@
         <v>10</v>
       </c>
       <c r="H1810" s="2">
-        <v>5.0578703703703706E-3</v>
+        <v>5.8333333333333336E-3</v>
       </c>
       <c r="I1810" s="1">
         <v>46146.715277777781</v>
       </c>
       <c r="J1810">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1810" t="s">
         <v>11</v>
@@ -51710,10 +51732,10 @@
         <v>21</v>
       </c>
       <c r="C1811">
-        <v>5140</v>
+        <v>3841</v>
       </c>
       <c r="D1811" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="F1811" t="s">
         <v>15</v>
@@ -51722,10 +51744,10 @@
         <v>10</v>
       </c>
       <c r="H1811" s="2">
-        <v>5.8333333333333336E-3</v>
+        <v>9.3518518518518525E-3</v>
       </c>
       <c r="I1811" s="1">
-        <v>46146.715277777781</v>
+        <v>46146.71597222222</v>
       </c>
       <c r="J1811">
         <v>0</v>
@@ -51739,10 +51761,10 @@
         <v>21</v>
       </c>
       <c r="C1812">
-        <v>3841</v>
+        <v>5535</v>
       </c>
       <c r="D1812" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="F1812" t="s">
         <v>15</v>
@@ -51751,13 +51773,13 @@
         <v>10</v>
       </c>
       <c r="H1812" s="2">
-        <v>9.3518518518518525E-3</v>
+        <v>1.8692129629629628E-2</v>
       </c>
       <c r="I1812" s="1">
-        <v>46146.71597222222</v>
+        <v>46146.716666666667</v>
       </c>
       <c r="J1812">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1812" t="s">
         <v>11</v>
@@ -51768,25 +51790,25 @@
         <v>21</v>
       </c>
       <c r="C1813">
-        <v>5535</v>
+        <v>3047</v>
       </c>
       <c r="D1813" t="s">
-        <v>226</v>
+        <v>141</v>
       </c>
       <c r="F1813" t="s">
         <v>15</v>
       </c>
       <c r="G1813" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1813" s="2">
-        <v>0</v>
+        <v>4.9074074074074072E-3</v>
       </c>
       <c r="I1813" s="1">
-        <v>46146.716666666667</v>
+        <v>46146.717361111114</v>
       </c>
       <c r="J1813">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1813" t="s">
         <v>11</v>
@@ -51797,10 +51819,10 @@
         <v>21</v>
       </c>
       <c r="C1814">
-        <v>3047</v>
+        <v>5533</v>
       </c>
       <c r="D1814" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="F1814" t="s">
         <v>15</v>
@@ -51809,13 +51831,13 @@
         <v>10</v>
       </c>
       <c r="H1814" s="2">
-        <v>4.9074074074074072E-3</v>
+        <v>5.4745370370370373E-3</v>
       </c>
       <c r="I1814" s="1">
         <v>46146.717361111114</v>
       </c>
       <c r="J1814">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1814" t="s">
         <v>11</v>
@@ -51826,25 +51848,25 @@
         <v>21</v>
       </c>
       <c r="C1815">
-        <v>5533</v>
+        <v>1552</v>
       </c>
       <c r="D1815" t="s">
-        <v>227</v>
+        <v>87</v>
       </c>
       <c r="F1815" t="s">
         <v>15</v>
       </c>
       <c r="G1815" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1815" s="2">
-        <v>0</v>
+        <v>5.7754629629629631E-3</v>
       </c>
       <c r="I1815" s="1">
-        <v>46146.717361111114</v>
+        <v>46146.718055555553</v>
       </c>
       <c r="J1815">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1815" t="s">
         <v>11</v>
@@ -51855,10 +51877,10 @@
         <v>21</v>
       </c>
       <c r="C1816">
-        <v>1552</v>
+        <v>1588</v>
       </c>
       <c r="D1816" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F1816" t="s">
         <v>15</v>
@@ -51867,13 +51889,13 @@
         <v>10</v>
       </c>
       <c r="H1816" s="2">
-        <v>5.7754629629629631E-3</v>
+        <v>5.1041666666666666E-3</v>
       </c>
       <c r="I1816" s="1">
         <v>46146.718055555553</v>
       </c>
       <c r="J1816">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1816" t="s">
         <v>11</v>
@@ -51884,10 +51906,10 @@
         <v>21</v>
       </c>
       <c r="C1817">
-        <v>1588</v>
+        <v>5228</v>
       </c>
       <c r="D1817" t="s">
-        <v>89</v>
+        <v>214</v>
       </c>
       <c r="F1817" t="s">
         <v>15</v>
@@ -51899,10 +51921,10 @@
         <v>0</v>
       </c>
       <c r="I1817" s="1">
-        <v>46146.718055555553</v>
+        <v>46146.71875</v>
       </c>
       <c r="J1817">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1817" t="s">
         <v>11</v>
@@ -51913,25 +51935,25 @@
         <v>21</v>
       </c>
       <c r="C1818">
-        <v>5228</v>
+        <v>3659</v>
       </c>
       <c r="D1818" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F1818" t="s">
         <v>15</v>
       </c>
       <c r="G1818" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1818" s="2">
-        <v>0</v>
+        <v>6.851851851851852E-3</v>
       </c>
       <c r="I1818" s="1">
-        <v>46146.71875</v>
+        <v>46146.719444444447</v>
       </c>
       <c r="J1818">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1818" t="s">
         <v>11</v>
@@ -51942,25 +51964,25 @@
         <v>21</v>
       </c>
       <c r="C1819">
-        <v>3659</v>
+        <v>1551</v>
       </c>
       <c r="D1819" t="s">
-        <v>166</v>
+        <v>91</v>
       </c>
       <c r="F1819" t="s">
         <v>15</v>
       </c>
       <c r="G1819" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1819" s="2">
-        <v>6.851851851851852E-3</v>
+        <v>0</v>
       </c>
       <c r="I1819" s="1">
         <v>46146.719444444447</v>
       </c>
       <c r="J1819">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1819" t="s">
         <v>11</v>
@@ -51971,10 +51993,10 @@
         <v>21</v>
       </c>
       <c r="C1820">
-        <v>1551</v>
+        <v>1581</v>
       </c>
       <c r="D1820" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F1820" t="s">
         <v>15</v>
@@ -51986,10 +52008,10 @@
         <v>0</v>
       </c>
       <c r="I1820" s="1">
-        <v>46146.719444444447</v>
+        <v>46146.720138888886</v>
       </c>
       <c r="J1820">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1820" t="s">
         <v>11</v>
@@ -52000,22 +52022,22 @@
         <v>21</v>
       </c>
       <c r="C1821">
-        <v>1581</v>
+        <v>1545</v>
       </c>
       <c r="D1821" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F1821" t="s">
         <v>15</v>
       </c>
       <c r="G1821" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1821">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1821" s="2">
+        <v>5.3356481481481484E-3</v>
       </c>
       <c r="I1821" s="1">
-        <v>46146.720138888886</v>
+        <v>46146.720833333333</v>
       </c>
       <c r="J1821">
         <v>1</v>
@@ -52029,10 +52051,10 @@
         <v>21</v>
       </c>
       <c r="C1822">
-        <v>1545</v>
+        <v>1604</v>
       </c>
       <c r="D1822" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F1822" t="s">
         <v>15</v>
@@ -52041,13 +52063,13 @@
         <v>10</v>
       </c>
       <c r="H1822" s="2">
-        <v>5.3356481481481484E-3</v>
+        <v>8.4259259259259253E-3</v>
       </c>
       <c r="I1822" s="1">
         <v>46146.720833333333</v>
       </c>
       <c r="J1822">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1822" t="s">
         <v>11</v>
@@ -52058,10 +52080,10 @@
         <v>21</v>
       </c>
       <c r="C1823">
-        <v>1604</v>
+        <v>4726</v>
       </c>
       <c r="D1823" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="F1823" t="s">
         <v>15</v>
@@ -52070,13 +52092,13 @@
         <v>10</v>
       </c>
       <c r="H1823" s="2">
-        <v>8.4259259259259253E-3</v>
+        <v>5.5439814814814813E-3</v>
       </c>
       <c r="I1823" s="1">
-        <v>46146.720833333333</v>
+        <v>46146.72152777778</v>
       </c>
       <c r="J1823">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1823" t="s">
         <v>11</v>
@@ -52087,10 +52109,10 @@
         <v>21</v>
       </c>
       <c r="C1824">
-        <v>4726</v>
+        <v>1540</v>
       </c>
       <c r="D1824" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="F1824" t="s">
         <v>15</v>
@@ -52099,13 +52121,13 @@
         <v>10</v>
       </c>
       <c r="H1824" s="2">
-        <v>5.5439814814814813E-3</v>
+        <v>5.5787037037037038E-3</v>
       </c>
       <c r="I1824" s="1">
-        <v>46146.72152777778</v>
+        <v>46146.722222222219</v>
       </c>
       <c r="J1824">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1824" t="s">
         <v>11</v>
@@ -52116,10 +52138,10 @@
         <v>21</v>
       </c>
       <c r="C1825">
-        <v>1540</v>
+        <v>1601</v>
       </c>
       <c r="D1825" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F1825" t="s">
         <v>15</v>
@@ -52128,7 +52150,7 @@
         <v>10</v>
       </c>
       <c r="H1825" s="2">
-        <v>5.5787037037037038E-3</v>
+        <v>5.2546296296296299E-3</v>
       </c>
       <c r="I1825" s="1">
         <v>46146.722222222219</v>
@@ -52141,33 +52163,8 @@
       </c>
     </row>
     <row r="1826" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B1826" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1826">
-        <v>1601</v>
-      </c>
-      <c r="D1826" t="s">
-        <v>100</v>
-      </c>
-      <c r="F1826" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1826" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1826" s="2">
-        <v>5.2546296296296299E-3</v>
-      </c>
-      <c r="I1826" s="1">
-        <v>46146.722222222219</v>
-      </c>
-      <c r="J1826">
-        <v>0</v>
-      </c>
-      <c r="K1826" t="s">
-        <v>11</v>
-      </c>
+      <c r="H1826" s="2"/>
+      <c r="I1826" s="1"/>
     </row>
     <row r="1827" spans="2:11" x14ac:dyDescent="0.3">
       <c r="I1827" s="1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Panhandle Express- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\panhandle-express\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10784C2C-0CEB-4A99-855A-78827FC96BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B38A844-5424-4A87-8807-A08B66264ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52909,7 +52909,7 @@
         <v>46176.429050925923</v>
       </c>
       <c r="J1845">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1845" t="s">
         <v>11</v>
@@ -52961,10 +52961,10 @@
         <v>25</v>
       </c>
       <c r="G1847" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1847" s="2">
-        <v>0</v>
+        <v>8.9699074074074073E-3</v>
       </c>
       <c r="I1847" s="1">
         <v>46176.429745370369</v>
@@ -53248,7 +53248,7 @@
         <v>46176.431828703702</v>
       </c>
       <c r="J1858">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1858" t="s">
         <v>11</v>
@@ -53277,7 +53277,7 @@
         <v>46176.432523148149</v>
       </c>
       <c r="J1859">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1859" t="s">
         <v>11</v>
@@ -53306,7 +53306,7 @@
         <v>46176.432523148149</v>
       </c>
       <c r="J1860">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1860" t="s">
         <v>11</v>
@@ -53488,16 +53488,16 @@
         <v>25</v>
       </c>
       <c r="G1868" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1868" s="2">
-        <v>0</v>
+        <v>6.7824074074074071E-3</v>
       </c>
       <c r="I1868" s="1">
         <v>46176.462500000001</v>
       </c>
       <c r="J1868">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1868" t="s">
         <v>11</v>
@@ -53555,7 +53555,7 @@
         <v>46176.463194444441</v>
       </c>
       <c r="J1870">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1870" t="s">
         <v>11</v>
@@ -53671,7 +53671,7 @@
         <v>46176.464583333334</v>
       </c>
       <c r="J1874">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1874" t="s">
         <v>11</v>
@@ -53729,7 +53729,7 @@
         <v>46176.46597222222</v>
       </c>
       <c r="J1876">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1876" t="s">
         <v>11</v>
@@ -53778,16 +53778,16 @@
         <v>25</v>
       </c>
       <c r="G1878" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1878" s="2">
-        <v>0</v>
+        <v>7.8240740740740736E-3</v>
       </c>
       <c r="I1878" s="1">
         <v>46176.466666666667</v>
       </c>
       <c r="J1878">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1878" t="s">
         <v>11</v>
@@ -53816,7 +53816,7 @@
         <v>46176.466666666667</v>
       </c>
       <c r="J1879">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1879" t="s">
         <v>11</v>
@@ -53874,7 +53874,7 @@
         <v>46176.467361111114</v>
       </c>
       <c r="J1881">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1881" t="s">
         <v>11</v>
@@ -53961,7 +53961,7 @@
         <v>46176.468055555553</v>
       </c>
       <c r="J1884">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1884" t="s">
         <v>11</v>
@@ -53990,7 +53990,7 @@
         <v>46176.46875</v>
       </c>
       <c r="J1885">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1885" t="s">
         <v>11</v>
@@ -54048,7 +54048,7 @@
         <v>46176.469444444447</v>
       </c>
       <c r="J1887">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1887" t="s">
         <v>11</v>
